--- a/youzi/王海祥/index.xlsx
+++ b/youzi/王海祥/index.xlsx
@@ -39,13 +39,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFCC2E3D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -99,7 +93,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,7 +123,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -135,19 +141,559 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE3626E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDD3D4D"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF57BA6E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF62BE77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47B460"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3A49"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE3626E"/>
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCEEBD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3747"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -159,25 +705,1057 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE3626E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C1C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF5F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC380"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3B4A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6707C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA7"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -189,115 +1767,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF57BA6E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF47B460"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF62BE77"/>
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -309,829 +1851,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3A49"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3747"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCEEBD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C1C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF5F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0EBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF72C585"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208838"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCFEFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF48B460"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF50B768"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC380"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1143,829 +1959,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC380"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3B4A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6707C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF72C585"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0EBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208838"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
+        <fgColor rgb="FF23943D"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC380"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF48B460"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCFEFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF50B768"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -5562,7 +5562,7 @@
       <c r="C2" t="str">
         <v>002276</v>
       </c>
-      <c r="D2" s="10" t="str">
+      <c r="D2" s="9" t="str">
         <v>净卖: -3245.54万</v>
       </c>
       <c r="E2">
@@ -5577,40 +5577,40 @@
       <c r="H2">
         <v>3.37</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="1">
         <v>6.43</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="10">
         <v>17.1</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="2">
         <v>11.56</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="3">
         <v>22.72</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="4">
         <v>30.54</v>
       </c>
-      <c r="N2" s="13">
+      <c r="N2" s="5">
         <v>43.57</v>
       </c>
-      <c r="O2" s="9">
+      <c r="O2" s="6">
         <v>42.1</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="12">
         <v>40.15</v>
       </c>
-      <c r="Q2" s="3">
+      <c r="Q2" s="7">
         <v>33.31</v>
       </c>
-      <c r="R2" s="4">
+      <c r="R2" s="8">
         <v>34.45</v>
       </c>
-      <c r="S2" s="8">
+      <c r="S2" s="11">
         <v>40.8</v>
       </c>
-      <c r="T2" s="5">
+      <c r="T2" s="13">
         <v>17.92</v>
       </c>
     </row>
@@ -5624,7 +5624,7 @@
       <c r="C3" t="str">
         <v>601279</v>
       </c>
-      <c r="D3" s="18" t="str">
+      <c r="D3" s="15" t="str">
         <v>净卖: -85.25万</v>
       </c>
       <c r="E3">
@@ -5639,40 +5639,40 @@
       <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3" s="23">
+      <c r="I3" s="22">
         <v>10.15</v>
       </c>
-      <c r="J3" s="20">
+      <c r="J3" s="23">
         <v>5.97</v>
       </c>
       <c r="K3" s="24">
         <v>4.48</v>
       </c>
-      <c r="L3" s="21">
+      <c r="L3" s="16">
         <v>3.88</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="17">
         <v>4.18</v>
       </c>
-      <c r="N3" s="19">
+      <c r="N3" s="18">
         <v>3.88</v>
       </c>
       <c r="O3" s="25">
         <v>5.67</v>
       </c>
-      <c r="P3" s="22">
+      <c r="P3" s="21">
         <v>5.07</v>
       </c>
-      <c r="Q3" s="17">
+      <c r="Q3" s="26">
         <v>4.78</v>
       </c>
-      <c r="R3" s="26">
+      <c r="R3" s="19">
         <v>2.09</v>
       </c>
       <c r="S3" s="14">
         <v>4.18</v>
       </c>
-      <c r="T3" s="15">
+      <c r="T3" s="20">
         <v>17.31</v>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
       <c r="C4" t="str">
         <v>003020</v>
       </c>
-      <c r="D4" s="28" t="str">
+      <c r="D4" s="32" t="str">
         <v>净买: 1240.36万</v>
       </c>
       <c r="E4">
@@ -5701,40 +5701,40 @@
       <c r="H4">
         <v>-3.75</v>
       </c>
-      <c r="I4" s="29">
+      <c r="I4" s="27">
         <v>-6.49</v>
       </c>
-      <c r="J4" s="32">
+      <c r="J4" s="30">
         <v>-15.84</v>
       </c>
       <c r="K4" s="33">
         <v>-23.08</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="34">
         <v>-24.06</v>
       </c>
-      <c r="M4" s="34">
+      <c r="M4" s="35">
         <v>-21.79</v>
       </c>
-      <c r="N4" s="37">
+      <c r="N4" s="28">
         <v>-20.71</v>
       </c>
-      <c r="O4" s="38">
+      <c r="O4" s="29">
         <v>-22.89</v>
       </c>
-      <c r="P4" s="39">
+      <c r="P4" s="38">
         <v>-24.61</v>
       </c>
-      <c r="Q4" s="30">
+      <c r="Q4" s="39">
         <v>-23.38</v>
       </c>
-      <c r="R4" s="35">
+      <c r="R4" s="31">
         <v>-24.35</v>
       </c>
-      <c r="S4" s="27">
+      <c r="S4" s="36">
         <v>-22.4</v>
       </c>
-      <c r="T4" s="31">
+      <c r="T4" s="37">
         <v>-21.43</v>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
       <c r="C5" t="str">
         <v>003020</v>
       </c>
-      <c r="D5" s="48" t="str">
+      <c r="D5" s="52" t="str">
         <v>净买: 1925.03万</v>
       </c>
       <c r="E5">
@@ -5766,37 +5766,37 @@
       <c r="I5" s="40">
         <v>-3.89</v>
       </c>
-      <c r="J5" s="49">
+      <c r="J5" s="47">
         <v>-5.11</v>
       </c>
-      <c r="K5" s="43">
+      <c r="K5" s="50">
         <v>-2.27</v>
       </c>
-      <c r="L5" s="50">
+      <c r="L5" s="51">
         <v>-0.93</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="41">
         <v>-3.65</v>
       </c>
-      <c r="N5" s="51">
+      <c r="N5" s="42">
         <v>-5.8</v>
       </c>
-      <c r="O5" s="41">
+      <c r="O5" s="43">
         <v>-4.26</v>
       </c>
-      <c r="P5" s="45">
+      <c r="P5" s="48">
         <v>-5.48</v>
       </c>
-      <c r="Q5" s="47">
+      <c r="Q5" s="44">
         <v>-3.04</v>
       </c>
-      <c r="R5" s="46">
+      <c r="R5" s="45">
         <v>-2.07</v>
       </c>
-      <c r="S5" s="42">
+      <c r="S5" s="49">
         <v>-0.97</v>
       </c>
-      <c r="T5" s="52">
+      <c r="T5" s="46">
         <v>-1.83</v>
       </c>
     </row>
@@ -5825,40 +5825,40 @@
       <c r="H6">
         <v>9.92</v>
       </c>
-      <c r="I6" s="65">
+      <c r="I6" s="53">
         <v>0.06</v>
       </c>
-      <c r="J6" s="57">
+      <c r="J6" s="60">
         <v>4.62</v>
       </c>
-      <c r="K6" s="53">
+      <c r="K6" s="57">
         <v>4.87</v>
       </c>
-      <c r="L6" s="60">
+      <c r="L6" s="61">
         <v>-5.62</v>
       </c>
-      <c r="M6" s="61">
+      <c r="M6" s="62">
         <v>-15.05</v>
       </c>
-      <c r="N6" s="58">
+      <c r="N6" s="63">
         <v>-13.34</v>
       </c>
-      <c r="O6" s="54">
+      <c r="O6" s="64">
         <v>-18.49</v>
       </c>
-      <c r="P6" s="63">
+      <c r="P6" s="56">
         <v>-19.11</v>
       </c>
-      <c r="Q6" s="62">
+      <c r="Q6" s="54">
         <v>-16.36</v>
       </c>
       <c r="R6" s="55">
         <v>-15.71</v>
       </c>
-      <c r="S6" s="56">
+      <c r="S6" s="65">
         <v>-10.68</v>
       </c>
-      <c r="T6" s="64">
+      <c r="T6" s="58">
         <v>-27.48</v>
       </c>
     </row>
@@ -5872,7 +5872,7 @@
       <c r="C7" t="str">
         <v>603607</v>
       </c>
-      <c r="D7" s="67" t="str">
+      <c r="D7" s="70" t="str">
         <v>净卖: -2523.15万</v>
       </c>
       <c r="E7">
@@ -5887,40 +5887,40 @@
       <c r="H7">
         <v>1.49</v>
       </c>
-      <c r="I7" s="68">
+      <c r="I7" s="71">
         <v>-1.24</v>
       </c>
-      <c r="J7" s="75">
+      <c r="J7" s="74">
         <v>-11.12</v>
       </c>
-      <c r="K7" s="71">
+      <c r="K7" s="75">
         <v>-20</v>
       </c>
       <c r="L7" s="72">
         <v>-18.38</v>
       </c>
-      <c r="M7" s="77">
+      <c r="M7" s="68">
         <v>-23.24</v>
       </c>
-      <c r="N7" s="73">
+      <c r="N7" s="77">
         <v>-23.82</v>
       </c>
-      <c r="O7" s="74">
+      <c r="O7" s="76">
         <v>-21.24</v>
       </c>
-      <c r="P7" s="69">
+      <c r="P7" s="78">
         <v>-20.62</v>
       </c>
-      <c r="Q7" s="76">
+      <c r="Q7" s="69">
         <v>-15.88</v>
       </c>
-      <c r="R7" s="70">
+      <c r="R7" s="73">
         <v>-18.09</v>
       </c>
-      <c r="S7" s="78">
+      <c r="S7" s="66">
         <v>-25.41</v>
       </c>
-      <c r="T7" s="66">
+      <c r="T7" s="67">
         <v>-31.71</v>
       </c>
     </row>
@@ -5934,7 +5934,7 @@
       <c r="C8" t="str">
         <v>603823</v>
       </c>
-      <c r="D8" s="84" t="str">
+      <c r="D8" s="91" t="str">
         <v>净卖: -577.99万</v>
       </c>
       <c r="E8">
@@ -5949,40 +5949,40 @@
       <c r="H8">
         <v>-1.03</v>
       </c>
-      <c r="I8" s="81">
+      <c r="I8" s="79">
         <v>11.19</v>
       </c>
-      <c r="J8" s="85">
+      <c r="J8" s="87">
         <v>10.49</v>
       </c>
-      <c r="K8" s="82">
+      <c r="K8" s="80">
         <v>7.03</v>
       </c>
-      <c r="L8" s="83">
+      <c r="L8" s="81">
         <v>2.34</v>
       </c>
-      <c r="M8" s="86">
+      <c r="M8" s="88">
         <v>4.94</v>
       </c>
-      <c r="N8" s="87">
+      <c r="N8" s="82">
         <v>-1.13</v>
       </c>
-      <c r="O8" s="88">
+      <c r="O8" s="83">
         <v>-2.6</v>
       </c>
       <c r="P8" s="89">
         <v>7.11</v>
       </c>
-      <c r="Q8" s="90">
+      <c r="Q8" s="84">
         <v>11.71</v>
       </c>
-      <c r="R8" s="91">
+      <c r="R8" s="85">
         <v>17.52</v>
       </c>
-      <c r="S8" s="79">
+      <c r="S8" s="86">
         <v>17.43</v>
       </c>
-      <c r="T8" s="80">
+      <c r="T8" s="90">
         <v>40.16</v>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       <c r="C9" t="str">
         <v>601279</v>
       </c>
-      <c r="D9" s="92" t="str">
+      <c r="D9" s="95" t="str">
         <v>净卖: -624.00万</v>
       </c>
       <c r="E9">
@@ -6014,37 +6014,37 @@
       <c r="I9" s="96">
         <v>0</v>
       </c>
-      <c r="J9" s="98">
+      <c r="J9" s="99">
         <v>-8.75</v>
       </c>
       <c r="K9" s="97">
         <v>-17.92</v>
       </c>
-      <c r="L9" s="103">
+      <c r="L9" s="100">
         <v>-22.08</v>
       </c>
-      <c r="M9" s="99">
+      <c r="M9" s="101">
         <v>-23.12</v>
       </c>
       <c r="N9" s="93">
         <v>-21.88</v>
       </c>
-      <c r="O9" s="100">
+      <c r="O9" s="102">
         <v>-22.29</v>
       </c>
-      <c r="P9" s="101">
+      <c r="P9" s="104">
         <v>-21.25</v>
       </c>
-      <c r="Q9" s="102">
+      <c r="Q9" s="103">
         <v>-20.62</v>
       </c>
-      <c r="R9" s="94">
+      <c r="R9" s="98">
         <v>-21.25</v>
       </c>
-      <c r="S9" s="95">
+      <c r="S9" s="94">
         <v>-19.37</v>
       </c>
-      <c r="T9" s="104">
+      <c r="T9" s="92">
         <v>-18.12</v>
       </c>
     </row>
@@ -6058,7 +6058,7 @@
       <c r="C10" t="str">
         <v>600980</v>
       </c>
-      <c r="D10" s="106" t="str">
+      <c r="D10" s="108" t="str">
         <v>净卖: -1981.34万</v>
       </c>
       <c r="E10">
@@ -6076,34 +6076,34 @@
       <c r="I10" s="111">
         <v>5.96</v>
       </c>
-      <c r="J10" s="115">
+      <c r="J10" s="112">
         <v>-4.64</v>
       </c>
-      <c r="K10" s="107">
+      <c r="K10" s="115">
         <v>-14.14</v>
       </c>
-      <c r="L10" s="112">
+      <c r="L10" s="113">
         <v>-19.62</v>
       </c>
-      <c r="M10" s="109">
+      <c r="M10" s="106">
         <v>-20.09</v>
       </c>
-      <c r="N10" s="113">
+      <c r="N10" s="114">
         <v>-18.71</v>
       </c>
-      <c r="O10" s="114">
+      <c r="O10" s="109">
         <v>-18.89</v>
       </c>
       <c r="P10" s="116">
         <v>-19.15</v>
       </c>
-      <c r="Q10" s="110">
+      <c r="Q10" s="117">
         <v>-20.42</v>
       </c>
-      <c r="R10" s="108">
+      <c r="R10" s="107">
         <v>-17.25</v>
       </c>
-      <c r="S10" s="117">
+      <c r="S10" s="110">
         <v>-11.14</v>
       </c>
       <c r="T10" s="105">
@@ -6120,7 +6120,7 @@
       <c r="C11" t="str">
         <v>600330</v>
       </c>
-      <c r="D11" s="123" t="str">
+      <c r="D11" s="129" t="str">
         <v>净卖: -6191.34万</v>
       </c>
       <c r="E11">
@@ -6135,40 +6135,40 @@
       <c r="H11">
         <v>10</v>
       </c>
-      <c r="I11" s="119">
+      <c r="I11" s="118">
         <v>-5.66</v>
       </c>
-      <c r="J11" s="127">
+      <c r="J11" s="124">
         <v>3.77</v>
       </c>
-      <c r="K11" s="124">
+      <c r="K11" s="125">
         <v>-0.51</v>
       </c>
-      <c r="L11" s="125">
+      <c r="L11" s="119">
         <v>-7.72</v>
       </c>
-      <c r="M11" s="120">
+      <c r="M11" s="130">
         <v>-10.89</v>
       </c>
-      <c r="N11" s="121">
+      <c r="N11" s="120">
         <v>-6.43</v>
       </c>
-      <c r="O11" s="128">
+      <c r="O11" s="121">
         <v>-8.23</v>
       </c>
-      <c r="P11" s="129">
+      <c r="P11" s="122">
         <v>-3.77</v>
       </c>
-      <c r="Q11" s="130">
+      <c r="Q11" s="123">
         <v>-2.23</v>
       </c>
-      <c r="R11" s="122">
+      <c r="R11" s="126">
         <v>-1.63</v>
       </c>
-      <c r="S11" s="118">
+      <c r="S11" s="127">
         <v>-0.77</v>
       </c>
-      <c r="T11" s="126">
+      <c r="T11" s="128">
         <v>86.36</v>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       <c r="C12" t="str">
         <v>600635</v>
       </c>
-      <c r="D12" s="138" t="str">
+      <c r="D12" s="140" t="str">
         <v>净买: 2557.50万</v>
       </c>
       <c r="E12">
@@ -6197,40 +6197,40 @@
       <c r="H12">
         <v>2.91</v>
       </c>
-      <c r="I12" s="134">
+      <c r="I12" s="141">
         <v>6.98</v>
       </c>
-      <c r="J12" s="141">
+      <c r="J12" s="138">
         <v>10.75</v>
       </c>
-      <c r="K12" s="135">
+      <c r="K12" s="136">
         <v>21.89</v>
       </c>
-      <c r="L12" s="142">
+      <c r="L12" s="131">
         <v>34.15</v>
       </c>
-      <c r="M12" s="143">
+      <c r="M12" s="132">
         <v>34.15</v>
       </c>
-      <c r="N12" s="131">
+      <c r="N12" s="142">
         <v>30.38</v>
       </c>
-      <c r="O12" s="140">
+      <c r="O12" s="143">
         <v>28.49</v>
       </c>
-      <c r="P12" s="139">
+      <c r="P12" s="133">
         <v>23.58</v>
       </c>
-      <c r="Q12" s="136">
+      <c r="Q12" s="134">
         <v>17.74</v>
       </c>
-      <c r="R12" s="132">
+      <c r="R12" s="137">
         <v>29.43</v>
       </c>
-      <c r="S12" s="137">
+      <c r="S12" s="139">
         <v>33.77</v>
       </c>
-      <c r="T12" s="133">
+      <c r="T12" s="135">
         <v>1.51</v>
       </c>
     </row>
@@ -6244,7 +6244,7 @@
       <c r="C13" t="str">
         <v>002488</v>
       </c>
-      <c r="D13" s="146" t="str">
+      <c r="D13" s="150" t="str">
         <v>净卖: -1403.24万</v>
       </c>
       <c r="E13">
@@ -6259,40 +6259,40 @@
       <c r="H13">
         <v>-0.57</v>
       </c>
-      <c r="I13" s="156">
+      <c r="I13" s="151">
         <v>-9.51</v>
       </c>
-      <c r="J13" s="151">
+      <c r="J13" s="152">
         <v>-0.49</v>
       </c>
-      <c r="K13" s="150">
+      <c r="K13" s="153">
         <v>-8.7</v>
       </c>
-      <c r="L13" s="152">
+      <c r="L13" s="156">
         <v>-14.88</v>
       </c>
-      <c r="M13" s="153">
+      <c r="M13" s="144">
         <v>-14.96</v>
       </c>
-      <c r="N13" s="147">
+      <c r="N13" s="146">
         <v>-18.86</v>
       </c>
-      <c r="O13" s="154">
+      <c r="O13" s="145">
         <v>-19.92</v>
       </c>
-      <c r="P13" s="144">
+      <c r="P13" s="147">
         <v>-18.54</v>
       </c>
-      <c r="Q13" s="155">
+      <c r="Q13" s="148">
         <v>-17.24</v>
       </c>
-      <c r="R13" s="148">
+      <c r="R13" s="154">
         <v>-15.93</v>
       </c>
-      <c r="S13" s="149">
+      <c r="S13" s="155">
         <v>-17.15</v>
       </c>
-      <c r="T13" s="145">
+      <c r="T13" s="149">
         <v>2.03</v>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       <c r="C14" t="str">
         <v>301246</v>
       </c>
-      <c r="D14" s="159" t="str">
+      <c r="D14" s="158" t="str">
         <v>净卖: -752.38万</v>
       </c>
       <c r="E14">
@@ -6321,40 +6321,40 @@
       <c r="H14">
         <v>-2.99</v>
       </c>
-      <c r="I14" s="160">
+      <c r="I14" s="168">
         <v>23.71</v>
       </c>
-      <c r="J14" s="167">
+      <c r="J14" s="159">
         <v>15.87</v>
       </c>
-      <c r="K14" s="157">
+      <c r="K14" s="160">
         <v>21.68</v>
       </c>
-      <c r="L14" s="168">
+      <c r="L14" s="163">
         <v>20.7</v>
       </c>
-      <c r="M14" s="161">
+      <c r="M14" s="164">
         <v>16.22</v>
       </c>
       <c r="N14" s="165">
         <v>18.95</v>
       </c>
-      <c r="O14" s="162">
+      <c r="O14" s="161">
         <v>19.79</v>
       </c>
-      <c r="P14" s="169">
+      <c r="P14" s="167">
         <v>17.41</v>
       </c>
-      <c r="Q14" s="163">
+      <c r="Q14" s="166">
         <v>19.79</v>
       </c>
-      <c r="R14" s="164">
+      <c r="R14" s="169">
         <v>15.38</v>
       </c>
-      <c r="S14" s="166">
+      <c r="S14" s="162">
         <v>18.25</v>
       </c>
-      <c r="T14" s="158">
+      <c r="T14" s="157">
         <v>69.93</v>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       <c r="C15" t="str">
         <v>002198</v>
       </c>
-      <c r="D15" s="181" t="str">
+      <c r="D15" s="175" t="str">
         <v>净买: 1396.06万</v>
       </c>
       <c r="E15">
@@ -6383,40 +6383,40 @@
       <c r="H15">
         <v>9.79</v>
       </c>
-      <c r="I15" s="182">
+      <c r="I15" s="176">
         <v>0.24</v>
       </c>
-      <c r="J15" s="173">
+      <c r="J15" s="177">
         <v>-9.75</v>
       </c>
-      <c r="K15" s="170">
+      <c r="K15" s="172">
         <v>-16.17</v>
       </c>
-      <c r="L15" s="176">
+      <c r="L15" s="178">
         <v>-16.77</v>
       </c>
-      <c r="M15" s="174">
+      <c r="M15" s="173">
         <v>-20.33</v>
       </c>
-      <c r="N15" s="177">
+      <c r="N15" s="181">
         <v>-17.72</v>
       </c>
-      <c r="O15" s="178">
+      <c r="O15" s="179">
         <v>-12.72</v>
       </c>
-      <c r="P15" s="175">
+      <c r="P15" s="174">
         <v>-11.18</v>
       </c>
-      <c r="Q15" s="171">
+      <c r="Q15" s="182">
         <v>-10.7</v>
       </c>
-      <c r="R15" s="172">
+      <c r="R15" s="170">
         <v>-10.23</v>
       </c>
       <c r="S15" s="180">
         <v>-11.77</v>
       </c>
-      <c r="T15" s="179">
+      <c r="T15" s="171">
         <v>-6.78</v>
       </c>
     </row>
@@ -6430,7 +6430,7 @@
       <c r="C16" t="str">
         <v>002114</v>
       </c>
-      <c r="D16" s="193" t="str">
+      <c r="D16" s="194" t="str">
         <v>净卖: -121.61万</v>
       </c>
       <c r="E16">
@@ -6445,40 +6445,40 @@
       <c r="H16">
         <v>9.95</v>
       </c>
-      <c r="I16" s="186">
+      <c r="I16" s="185">
         <v>0</v>
       </c>
-      <c r="J16" s="194">
+      <c r="J16" s="186">
         <v>-9.98</v>
       </c>
-      <c r="K16" s="195">
+      <c r="K16" s="187">
         <v>-15.64</v>
       </c>
       <c r="L16" s="191">
         <v>-7.2</v>
       </c>
-      <c r="M16" s="192">
+      <c r="M16" s="188">
         <v>-9.16</v>
       </c>
-      <c r="N16" s="187">
+      <c r="N16" s="183">
         <v>-5.66</v>
       </c>
-      <c r="O16" s="183">
+      <c r="O16" s="192">
         <v>-7.3</v>
       </c>
-      <c r="P16" s="188">
+      <c r="P16" s="189">
         <v>-3.4</v>
       </c>
-      <c r="Q16" s="184">
+      <c r="Q16" s="193">
         <v>-6.17</v>
       </c>
-      <c r="R16" s="189">
+      <c r="R16" s="195">
         <v>-11.73</v>
       </c>
       <c r="S16" s="190">
         <v>-10.7</v>
       </c>
-      <c r="T16" s="185">
+      <c r="T16" s="184">
         <v>-8.33</v>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       <c r="C17" t="str">
         <v>603815</v>
       </c>
-      <c r="D17" s="206" t="str">
+      <c r="D17" s="198" t="str">
         <v>净卖: -1097.64万</v>
       </c>
       <c r="E17">
@@ -6507,40 +6507,40 @@
       <c r="H17">
         <v>0.09</v>
       </c>
-      <c r="I17" s="197">
+      <c r="I17" s="207">
         <v>9.95</v>
       </c>
-      <c r="J17" s="207">
+      <c r="J17" s="202">
         <v>12.93</v>
       </c>
-      <c r="K17" s="198">
+      <c r="K17" s="199">
         <v>12.57</v>
       </c>
-      <c r="L17" s="208">
+      <c r="L17" s="197">
         <v>17.45</v>
       </c>
-      <c r="M17" s="203">
+      <c r="M17" s="200">
         <v>9.76</v>
       </c>
-      <c r="N17" s="204">
+      <c r="N17" s="203">
         <v>9.22</v>
       </c>
-      <c r="O17" s="200">
+      <c r="O17" s="208">
         <v>-1.72</v>
       </c>
-      <c r="P17" s="199">
+      <c r="P17" s="204">
         <v>-11.57</v>
       </c>
-      <c r="Q17" s="196">
+      <c r="Q17" s="201">
         <v>-15.01</v>
       </c>
-      <c r="R17" s="205">
+      <c r="R17" s="196">
         <v>-21.52</v>
       </c>
-      <c r="S17" s="201">
+      <c r="S17" s="205">
         <v>-23.87</v>
       </c>
-      <c r="T17" s="202">
+      <c r="T17" s="206">
         <v>-40.6</v>
       </c>
     </row>
@@ -6569,40 +6569,40 @@
       <c r="H18">
         <v>10.05</v>
       </c>
-      <c r="I18" s="217">
+      <c r="I18" s="209">
         <v>0</v>
       </c>
-      <c r="J18" s="212">
+      <c r="J18" s="210">
         <v>10.06</v>
       </c>
-      <c r="K18" s="215">
+      <c r="K18" s="220">
         <v>11.46</v>
       </c>
-      <c r="L18" s="209">
+      <c r="L18" s="211">
         <v>0.31</v>
       </c>
-      <c r="M18" s="218">
+      <c r="M18" s="221">
         <v>-9.75</v>
       </c>
-      <c r="N18" s="219">
+      <c r="N18" s="212">
         <v>-9.6</v>
       </c>
-      <c r="O18" s="210">
+      <c r="O18" s="217">
         <v>-16.41</v>
       </c>
-      <c r="P18" s="211">
+      <c r="P18" s="213">
         <v>-14.24</v>
       </c>
-      <c r="Q18" s="220">
+      <c r="Q18" s="218">
         <v>-15.63</v>
       </c>
-      <c r="R18" s="221">
+      <c r="R18" s="219">
         <v>-16.87</v>
       </c>
-      <c r="S18" s="213">
+      <c r="S18" s="214">
         <v>-19.81</v>
       </c>
-      <c r="T18" s="214">
+      <c r="T18" s="215">
         <v>92.11</v>
       </c>
     </row>
@@ -6616,7 +6616,7 @@
       <c r="C19" t="str">
         <v>603067</v>
       </c>
-      <c r="D19" s="229" t="str">
+      <c r="D19" s="224" t="str">
         <v>净买: 1179.50万</v>
       </c>
       <c r="E19">
@@ -6631,40 +6631,40 @@
       <c r="H19">
         <v>-3.07</v>
       </c>
-      <c r="I19" s="224">
+      <c r="I19" s="225">
         <v>-5.37</v>
       </c>
-      <c r="J19" s="230">
+      <c r="J19" s="227">
         <v>-2.17</v>
       </c>
-      <c r="K19" s="227">
+      <c r="K19" s="228">
         <v>6.55</v>
       </c>
-      <c r="L19" s="231">
+      <c r="L19" s="229">
         <v>4.84</v>
       </c>
-      <c r="M19" s="228">
+      <c r="M19" s="232">
         <v>11.14</v>
       </c>
-      <c r="N19" s="225">
+      <c r="N19" s="223">
         <v>10.82</v>
       </c>
-      <c r="O19" s="226">
+      <c r="O19" s="230">
         <v>9.93</v>
       </c>
       <c r="P19" s="233">
         <v>6.01</v>
       </c>
-      <c r="Q19" s="232">
+      <c r="Q19" s="234">
         <v>3.17</v>
       </c>
-      <c r="R19" s="234">
+      <c r="R19" s="222">
         <v>2.53</v>
       </c>
-      <c r="S19" s="222">
+      <c r="S19" s="231">
         <v>12.78</v>
       </c>
-      <c r="T19" s="223">
+      <c r="T19" s="226">
         <v>27.01</v>
       </c>
     </row>
@@ -6678,7 +6678,7 @@
       <c r="C20" t="str">
         <v>000890</v>
       </c>
-      <c r="D20" s="239" t="str">
+      <c r="D20" s="243" t="str">
         <v>净买: 1030.64万</v>
       </c>
       <c r="E20">
@@ -6693,40 +6693,40 @@
       <c r="H20">
         <v>-9.72</v>
       </c>
-      <c r="I20" s="240">
+      <c r="I20" s="238">
         <v>-0.31</v>
       </c>
-      <c r="J20" s="235">
+      <c r="J20" s="239">
         <v>-10.31</v>
       </c>
-      <c r="K20" s="241">
+      <c r="K20" s="236">
         <v>-10.15</v>
       </c>
-      <c r="L20" s="242">
+      <c r="L20" s="244">
         <v>-16.92</v>
       </c>
-      <c r="M20" s="245">
+      <c r="M20" s="240">
         <v>-14.77</v>
       </c>
-      <c r="N20" s="246">
+      <c r="N20" s="245">
         <v>-16.15</v>
       </c>
-      <c r="O20" s="236">
+      <c r="O20" s="246">
         <v>-17.38</v>
       </c>
-      <c r="P20" s="247">
+      <c r="P20" s="237">
         <v>-20.31</v>
       </c>
-      <c r="Q20" s="237">
+      <c r="Q20" s="241">
         <v>-20.62</v>
       </c>
-      <c r="R20" s="243">
+      <c r="R20" s="247">
         <v>-22</v>
       </c>
-      <c r="S20" s="238">
+      <c r="S20" s="235">
         <v>-21.69</v>
       </c>
-      <c r="T20" s="244">
+      <c r="T20" s="242">
         <v>90.92</v>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       <c r="C21" t="str">
         <v>000890</v>
       </c>
-      <c r="D21" s="260" t="str">
+      <c r="D21" s="250" t="str">
         <v>净卖: -1045.40万</v>
       </c>
       <c r="E21">
@@ -6755,40 +6755,40 @@
       <c r="H21">
         <v>-4.94</v>
       </c>
-      <c r="I21" s="258">
+      <c r="I21" s="251">
         <v>-5.36</v>
       </c>
       <c r="J21" s="256">
         <v>-5.19</v>
       </c>
-      <c r="K21" s="259">
+      <c r="K21" s="257">
         <v>-12.34</v>
       </c>
-      <c r="L21" s="248">
+      <c r="L21" s="252">
         <v>-10.06</v>
       </c>
-      <c r="M21" s="254">
+      <c r="M21" s="253">
         <v>-11.53</v>
       </c>
-      <c r="N21" s="257">
+      <c r="N21" s="249">
         <v>-12.82</v>
       </c>
-      <c r="O21" s="249">
+      <c r="O21" s="260">
         <v>-15.91</v>
       </c>
-      <c r="P21" s="250">
+      <c r="P21" s="254">
         <v>-16.23</v>
       </c>
-      <c r="Q21" s="251">
+      <c r="Q21" s="258">
         <v>-17.69</v>
       </c>
-      <c r="R21" s="252">
+      <c r="R21" s="255">
         <v>-17.37</v>
       </c>
-      <c r="S21" s="255">
+      <c r="S21" s="259">
         <v>-16.23</v>
       </c>
-      <c r="T21" s="253">
+      <c r="T21" s="248">
         <v>101.46</v>
       </c>
     </row>
@@ -6802,7 +6802,7 @@
       <c r="C22" t="str">
         <v>300409</v>
       </c>
-      <c r="D22" s="273" t="str">
+      <c r="D22" s="268" t="str">
         <v>净卖: -3259.20万</v>
       </c>
       <c r="E22">
@@ -6817,40 +6817,40 @@
       <c r="H22">
         <v>4.54</v>
       </c>
-      <c r="I22" s="268">
+      <c r="I22" s="270">
         <v>14.8</v>
       </c>
-      <c r="J22" s="261">
+      <c r="J22" s="271">
         <v>31.48</v>
       </c>
-      <c r="K22" s="264">
+      <c r="K22" s="266">
         <v>32.5</v>
       </c>
-      <c r="L22" s="265">
+      <c r="L22" s="272">
         <v>30.84</v>
       </c>
-      <c r="M22" s="262">
+      <c r="M22" s="273">
         <v>23.86</v>
       </c>
       <c r="N22" s="269">
         <v>48.62</v>
       </c>
-      <c r="O22" s="271">
+      <c r="O22" s="261">
         <v>46.11</v>
       </c>
-      <c r="P22" s="270">
+      <c r="P22" s="262">
         <v>41.64</v>
       </c>
-      <c r="Q22" s="266">
+      <c r="Q22" s="263">
         <v>42.15</v>
       </c>
-      <c r="R22" s="267">
+      <c r="R22" s="264">
         <v>36.03</v>
       </c>
-      <c r="S22" s="263">
+      <c r="S22" s="265">
         <v>31.9</v>
       </c>
-      <c r="T22" s="272">
+      <c r="T22" s="267">
         <v>13.36</v>
       </c>
     </row>
@@ -6864,7 +6864,7 @@
       <c r="C23" t="str">
         <v>300409</v>
       </c>
-      <c r="D23" s="280" t="str">
+      <c r="D23" s="277" t="str">
         <v>净卖: -3736.61万</v>
       </c>
       <c r="E23">
@@ -6879,40 +6879,40 @@
       <c r="H23">
         <v>4.22</v>
       </c>
-      <c r="I23" s="281">
+      <c r="I23" s="282">
         <v>9.88</v>
       </c>
-      <c r="J23" s="282">
+      <c r="J23" s="274">
         <v>10.74</v>
       </c>
-      <c r="K23" s="284">
+      <c r="K23" s="283">
         <v>9.35</v>
       </c>
-      <c r="L23" s="285">
+      <c r="L23" s="278">
         <v>3.52</v>
       </c>
-      <c r="M23" s="286">
+      <c r="M23" s="275">
         <v>24.21</v>
       </c>
-      <c r="N23" s="277">
+      <c r="N23" s="286">
         <v>22.11</v>
       </c>
-      <c r="O23" s="279">
+      <c r="O23" s="284">
         <v>18.38</v>
       </c>
-      <c r="P23" s="274">
+      <c r="P23" s="285">
         <v>18.81</v>
       </c>
-      <c r="Q23" s="275">
+      <c r="Q23" s="279">
         <v>13.69</v>
       </c>
-      <c r="R23" s="283">
+      <c r="R23" s="280">
         <v>10.24</v>
       </c>
-      <c r="S23" s="278">
+      <c r="S23" s="276">
         <v>8</v>
       </c>
-      <c r="T23" s="276">
+      <c r="T23" s="281">
         <v>-5.26</v>
       </c>
     </row>
@@ -6941,40 +6941,40 @@
       <c r="H24">
         <v>1.68</v>
       </c>
-      <c r="I24" s="289">
+      <c r="I24" s="296">
         <v>18</v>
       </c>
-      <c r="J24" s="292">
+      <c r="J24" s="297">
         <v>16.01</v>
       </c>
-      <c r="K24" s="295">
+      <c r="K24" s="293">
         <v>12.46</v>
       </c>
-      <c r="L24" s="296">
+      <c r="L24" s="298">
         <v>12.87</v>
       </c>
-      <c r="M24" s="297">
+      <c r="M24" s="294">
         <v>8</v>
       </c>
-      <c r="N24" s="299">
+      <c r="N24" s="289">
         <v>4.73</v>
       </c>
-      <c r="O24" s="293">
+      <c r="O24" s="290">
         <v>2.6</v>
       </c>
-      <c r="P24" s="287">
+      <c r="P24" s="299">
         <v>1.82</v>
       </c>
-      <c r="Q24" s="290">
+      <c r="Q24" s="287">
         <v>2.36</v>
       </c>
-      <c r="R24" s="288">
+      <c r="R24" s="295">
         <v>8.11</v>
       </c>
-      <c r="S24" s="294">
+      <c r="S24" s="288">
         <v>5.67</v>
       </c>
-      <c r="T24" s="298">
+      <c r="T24" s="292">
         <v>-10</v>
       </c>
     </row>
@@ -7037,40 +7037,40 @@
       <c r="F26" t="str"/>
       <c r="G26" t="str"/>
       <c r="H26" t="str"/>
-      <c r="I26" s="311">
+      <c r="I26" s="300">
         <v>52.17</v>
       </c>
-      <c r="J26" s="307">
+      <c r="J26" s="304">
         <v>52.17</v>
       </c>
-      <c r="K26" s="308">
+      <c r="K26" s="301">
         <v>52.17</v>
       </c>
-      <c r="L26" s="309">
+      <c r="L26" s="305">
         <v>47.83</v>
       </c>
-      <c r="M26" s="300">
+      <c r="M26" s="306">
         <v>43.48</v>
       </c>
-      <c r="N26" s="304">
+      <c r="N26" s="307">
         <v>39.13</v>
       </c>
-      <c r="O26" s="310">
+      <c r="O26" s="308">
         <v>34.78</v>
       </c>
-      <c r="P26" s="301">
+      <c r="P26" s="309">
         <v>39.13</v>
       </c>
-      <c r="Q26" s="305">
+      <c r="Q26" s="302">
         <v>39.13</v>
       </c>
       <c r="R26" s="303">
         <v>39.13</v>
       </c>
-      <c r="S26" s="302">
+      <c r="S26" s="310">
         <v>39.13</v>
       </c>
-      <c r="T26" s="306">
+      <c r="T26" s="311">
         <v>52.17</v>
       </c>
     </row>
@@ -7085,40 +7085,40 @@
       <c r="F27" t="str"/>
       <c r="G27" t="str"/>
       <c r="H27" t="str"/>
-      <c r="I27" s="318">
+      <c r="I27" s="315">
         <v>3.46</v>
       </c>
-      <c r="J27" s="313">
+      <c r="J27" s="322">
         <v>2.89</v>
       </c>
       <c r="K27" s="323">
         <v>0.67</v>
       </c>
-      <c r="L27" s="314">
+      <c r="L27" s="316">
         <v>-0.46</v>
       </c>
-      <c r="M27" s="316">
+      <c r="M27" s="319">
         <v>-1.36</v>
       </c>
-      <c r="N27" s="319">
+      <c r="N27" s="312">
         <v>-0.02</v>
       </c>
-      <c r="O27" s="320">
+      <c r="O27" s="317">
         <v>-1.62</v>
       </c>
-      <c r="P27" s="312">
+      <c r="P27" s="318">
         <v>-2.08</v>
       </c>
-      <c r="Q27" s="315">
+      <c r="Q27" s="320">
         <v>-2.45</v>
       </c>
       <c r="R27" s="321">
         <v>-2.62</v>
       </c>
-      <c r="S27" s="317">
+      <c r="S27" s="313">
         <v>-1.7</v>
       </c>
-      <c r="T27" s="322">
+      <c r="T27" s="314">
         <v>16.19</v>
       </c>
     </row>

--- a/youzi/王海祥/index.xlsx
+++ b/youzi/王海祥/index.xlsx
@@ -39,6 +39,66 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFCC2E3D"/>
         <bgColor/>
       </patternFill>
@@ -57,31 +117,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFE3626E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -93,25 +183,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFE3626E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,49 +195,499 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF57BA6E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF62BE77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47B460"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3A49"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE3626E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCEEBD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3747"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -177,7 +699,1105 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C1C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF5F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC380"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3B4A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6707C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -189,133 +1809,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF57BA6E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF62BE77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF47B460"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -327,841 +1839,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD5EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3A49"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCEEBD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3747"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C1C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF5F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
+        <fgColor rgb="FF208838"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0EBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF72C585"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCFEFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF50B768"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1173,744 +1953,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3B4A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF27A444"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6707C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0EBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF72C585"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208838"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCFEFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF48B460"/>
         <bgColor/>
       </patternFill>
@@ -1924,54 +1972,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF50B768"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC380"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -5562,7 +5562,7 @@
       <c r="C2" t="str">
         <v>002276</v>
       </c>
-      <c r="D2" s="9" t="str">
+      <c r="D2" s="1" t="str">
         <v>净卖: -3245.54万</v>
       </c>
       <c r="E2">
@@ -5577,40 +5577,40 @@
       <c r="H2">
         <v>3.37</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="11">
         <v>6.43</v>
       </c>
-      <c r="J2" s="10">
+      <c r="J2" s="2">
         <v>17.1</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="5">
         <v>11.56</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="9">
         <v>22.72</v>
       </c>
-      <c r="M2" s="4">
+      <c r="M2" s="6">
         <v>30.54</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="12">
         <v>43.57</v>
       </c>
-      <c r="O2" s="6">
+      <c r="O2" s="13">
         <v>42.1</v>
       </c>
-      <c r="P2" s="12">
+      <c r="P2" s="3">
         <v>40.15</v>
       </c>
-      <c r="Q2" s="7">
+      <c r="Q2" s="10">
         <v>33.31</v>
       </c>
-      <c r="R2" s="8">
+      <c r="R2" s="7">
         <v>34.45</v>
       </c>
-      <c r="S2" s="11">
+      <c r="S2" s="4">
         <v>40.8</v>
       </c>
-      <c r="T2" s="13">
+      <c r="T2" s="8">
         <v>17.92</v>
       </c>
     </row>
@@ -5624,7 +5624,7 @@
       <c r="C3" t="str">
         <v>601279</v>
       </c>
-      <c r="D3" s="15" t="str">
+      <c r="D3" s="24" t="str">
         <v>净卖: -85.25万</v>
       </c>
       <c r="E3">
@@ -5639,40 +5639,40 @@
       <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="19">
         <v>10.15</v>
       </c>
-      <c r="J3" s="23">
+      <c r="J3" s="15">
         <v>5.97</v>
       </c>
-      <c r="K3" s="24">
+      <c r="K3" s="16">
         <v>4.48</v>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="25">
         <v>3.88</v>
       </c>
-      <c r="M3" s="17">
+      <c r="M3" s="26">
         <v>4.18</v>
       </c>
-      <c r="N3" s="18">
+      <c r="N3" s="14">
         <v>3.88</v>
       </c>
-      <c r="O3" s="25">
+      <c r="O3" s="22">
         <v>5.67</v>
       </c>
-      <c r="P3" s="21">
+      <c r="P3" s="20">
         <v>5.07</v>
       </c>
-      <c r="Q3" s="26">
+      <c r="Q3" s="23">
         <v>4.78</v>
       </c>
-      <c r="R3" s="19">
+      <c r="R3" s="21">
         <v>2.09</v>
       </c>
-      <c r="S3" s="14">
+      <c r="S3" s="17">
         <v>4.18</v>
       </c>
-      <c r="T3" s="20">
+      <c r="T3" s="18">
         <v>17.31</v>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
       <c r="C4" t="str">
         <v>003020</v>
       </c>
-      <c r="D4" s="32" t="str">
+      <c r="D4" s="30" t="str">
         <v>净买: 1240.36万</v>
       </c>
       <c r="E4">
@@ -5701,40 +5701,40 @@
       <c r="H4">
         <v>-3.75</v>
       </c>
-      <c r="I4" s="27">
+      <c r="I4" s="34">
         <v>-6.49</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="28">
         <v>-15.84</v>
       </c>
-      <c r="K4" s="33">
+      <c r="K4" s="36">
         <v>-23.08</v>
       </c>
-      <c r="L4" s="34">
+      <c r="L4" s="31">
         <v>-24.06</v>
       </c>
-      <c r="M4" s="35">
+      <c r="M4" s="37">
         <v>-21.79</v>
       </c>
-      <c r="N4" s="28">
+      <c r="N4" s="38">
         <v>-20.71</v>
       </c>
-      <c r="O4" s="29">
+      <c r="O4" s="32">
         <v>-22.89</v>
       </c>
-      <c r="P4" s="38">
+      <c r="P4" s="39">
         <v>-24.61</v>
       </c>
-      <c r="Q4" s="39">
+      <c r="Q4" s="29">
         <v>-23.38</v>
       </c>
-      <c r="R4" s="31">
+      <c r="R4" s="33">
         <v>-24.35</v>
       </c>
-      <c r="S4" s="36">
+      <c r="S4" s="27">
         <v>-22.4</v>
       </c>
-      <c r="T4" s="37">
+      <c r="T4" s="35">
         <v>-21.43</v>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
       <c r="C5" t="str">
         <v>003020</v>
       </c>
-      <c r="D5" s="52" t="str">
+      <c r="D5" s="42" t="str">
         <v>净买: 1925.03万</v>
       </c>
       <c r="E5">
@@ -5763,40 +5763,40 @@
       <c r="H5">
         <v>-4.9</v>
       </c>
-      <c r="I5" s="40">
+      <c r="I5" s="43">
         <v>-3.89</v>
       </c>
-      <c r="J5" s="47">
+      <c r="J5" s="48">
         <v>-5.11</v>
       </c>
-      <c r="K5" s="50">
+      <c r="K5" s="45">
         <v>-2.27</v>
       </c>
-      <c r="L5" s="51">
+      <c r="L5" s="44">
         <v>-0.93</v>
       </c>
-      <c r="M5" s="41">
+      <c r="M5" s="49">
         <v>-3.65</v>
       </c>
-      <c r="N5" s="42">
+      <c r="N5" s="46">
         <v>-5.8</v>
       </c>
-      <c r="O5" s="43">
+      <c r="O5" s="50">
         <v>-4.26</v>
       </c>
-      <c r="P5" s="48">
+      <c r="P5" s="51">
         <v>-5.48</v>
       </c>
-      <c r="Q5" s="44">
+      <c r="Q5" s="47">
         <v>-3.04</v>
       </c>
-      <c r="R5" s="45">
+      <c r="R5" s="52">
         <v>-2.07</v>
       </c>
-      <c r="S5" s="49">
+      <c r="S5" s="40">
         <v>-0.97</v>
       </c>
-      <c r="T5" s="46">
+      <c r="T5" s="41">
         <v>-1.83</v>
       </c>
     </row>
@@ -5810,7 +5810,7 @@
       <c r="C6" t="str">
         <v>603607</v>
       </c>
-      <c r="D6" s="59" t="str">
+      <c r="D6" s="57" t="str">
         <v>净卖: -1819.82万</v>
       </c>
       <c r="E6">
@@ -5825,40 +5825,40 @@
       <c r="H6">
         <v>9.92</v>
       </c>
-      <c r="I6" s="53">
+      <c r="I6" s="64">
         <v>0.06</v>
       </c>
-      <c r="J6" s="60">
+      <c r="J6" s="61">
         <v>4.62</v>
       </c>
-      <c r="K6" s="57">
+      <c r="K6" s="53">
         <v>4.87</v>
       </c>
-      <c r="L6" s="61">
+      <c r="L6" s="62">
         <v>-5.62</v>
       </c>
-      <c r="M6" s="62">
+      <c r="M6" s="58">
         <v>-15.05</v>
       </c>
-      <c r="N6" s="63">
+      <c r="N6" s="65">
         <v>-13.34</v>
       </c>
-      <c r="O6" s="64">
+      <c r="O6" s="54">
         <v>-18.49</v>
       </c>
-      <c r="P6" s="56">
+      <c r="P6" s="55">
         <v>-19.11</v>
       </c>
-      <c r="Q6" s="54">
+      <c r="Q6" s="59">
         <v>-16.36</v>
       </c>
-      <c r="R6" s="55">
+      <c r="R6" s="56">
         <v>-15.71</v>
       </c>
-      <c r="S6" s="65">
+      <c r="S6" s="60">
         <v>-10.68</v>
       </c>
-      <c r="T6" s="58">
+      <c r="T6" s="63">
         <v>-27.48</v>
       </c>
     </row>
@@ -5872,7 +5872,7 @@
       <c r="C7" t="str">
         <v>603607</v>
       </c>
-      <c r="D7" s="70" t="str">
+      <c r="D7" s="66" t="str">
         <v>净卖: -2523.15万</v>
       </c>
       <c r="E7">
@@ -5887,40 +5887,40 @@
       <c r="H7">
         <v>1.49</v>
       </c>
-      <c r="I7" s="71">
+      <c r="I7" s="73">
         <v>-1.24</v>
       </c>
       <c r="J7" s="74">
         <v>-11.12</v>
       </c>
-      <c r="K7" s="75">
+      <c r="K7" s="69">
         <v>-20</v>
       </c>
-      <c r="L7" s="72">
+      <c r="L7" s="78">
         <v>-18.38</v>
       </c>
-      <c r="M7" s="68">
+      <c r="M7" s="67">
         <v>-23.24</v>
       </c>
-      <c r="N7" s="77">
+      <c r="N7" s="75">
         <v>-23.82</v>
       </c>
-      <c r="O7" s="76">
+      <c r="O7" s="70">
         <v>-21.24</v>
       </c>
-      <c r="P7" s="78">
+      <c r="P7" s="76">
         <v>-20.62</v>
       </c>
-      <c r="Q7" s="69">
+      <c r="Q7" s="71">
         <v>-15.88</v>
       </c>
-      <c r="R7" s="73">
+      <c r="R7" s="68">
         <v>-18.09</v>
       </c>
-      <c r="S7" s="66">
+      <c r="S7" s="77">
         <v>-25.41</v>
       </c>
-      <c r="T7" s="67">
+      <c r="T7" s="72">
         <v>-31.71</v>
       </c>
     </row>
@@ -5934,7 +5934,7 @@
       <c r="C8" t="str">
         <v>603823</v>
       </c>
-      <c r="D8" s="91" t="str">
+      <c r="D8" s="79" t="str">
         <v>净卖: -577.99万</v>
       </c>
       <c r="E8">
@@ -5949,40 +5949,40 @@
       <c r="H8">
         <v>-1.03</v>
       </c>
-      <c r="I8" s="79">
+      <c r="I8" s="80">
         <v>11.19</v>
       </c>
-      <c r="J8" s="87">
+      <c r="J8" s="85">
         <v>10.49</v>
       </c>
-      <c r="K8" s="80">
+      <c r="K8" s="84">
         <v>7.03</v>
       </c>
       <c r="L8" s="81">
         <v>2.34</v>
       </c>
-      <c r="M8" s="88">
+      <c r="M8" s="89">
         <v>4.94</v>
       </c>
       <c r="N8" s="82">
         <v>-1.13</v>
       </c>
-      <c r="O8" s="83">
+      <c r="O8" s="86">
         <v>-2.6</v>
       </c>
-      <c r="P8" s="89">
+      <c r="P8" s="83">
         <v>7.11</v>
       </c>
-      <c r="Q8" s="84">
+      <c r="Q8" s="90">
         <v>11.71</v>
       </c>
-      <c r="R8" s="85">
+      <c r="R8" s="87">
         <v>17.52</v>
       </c>
-      <c r="S8" s="86">
+      <c r="S8" s="88">
         <v>17.43</v>
       </c>
-      <c r="T8" s="90">
+      <c r="T8" s="91">
         <v>40.16</v>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       <c r="C9" t="str">
         <v>601279</v>
       </c>
-      <c r="D9" s="95" t="str">
+      <c r="D9" s="97" t="str">
         <v>净卖: -624.00万</v>
       </c>
       <c r="E9">
@@ -6011,37 +6011,37 @@
       <c r="H9">
         <v>10.09</v>
       </c>
-      <c r="I9" s="96">
+      <c r="I9" s="93">
         <v>0</v>
       </c>
-      <c r="J9" s="99">
+      <c r="J9" s="103">
         <v>-8.75</v>
       </c>
-      <c r="K9" s="97">
+      <c r="K9" s="101">
         <v>-17.92</v>
       </c>
-      <c r="L9" s="100">
+      <c r="L9" s="98">
         <v>-22.08</v>
       </c>
-      <c r="M9" s="101">
+      <c r="M9" s="102">
         <v>-23.12</v>
       </c>
-      <c r="N9" s="93">
+      <c r="N9" s="94">
         <v>-21.88</v>
       </c>
-      <c r="O9" s="102">
+      <c r="O9" s="99">
         <v>-22.29</v>
       </c>
-      <c r="P9" s="104">
+      <c r="P9" s="95">
         <v>-21.25</v>
       </c>
-      <c r="Q9" s="103">
+      <c r="Q9" s="96">
         <v>-20.62</v>
       </c>
-      <c r="R9" s="98">
+      <c r="R9" s="100">
         <v>-21.25</v>
       </c>
-      <c r="S9" s="94">
+      <c r="S9" s="104">
         <v>-19.37</v>
       </c>
       <c r="T9" s="92">
@@ -6058,7 +6058,7 @@
       <c r="C10" t="str">
         <v>600980</v>
       </c>
-      <c r="D10" s="108" t="str">
+      <c r="D10" s="107" t="str">
         <v>净卖: -1981.34万</v>
       </c>
       <c r="E10">
@@ -6073,40 +6073,40 @@
       <c r="H10">
         <v>-0.58</v>
       </c>
-      <c r="I10" s="111">
+      <c r="I10" s="110">
         <v>5.96</v>
       </c>
       <c r="J10" s="112">
         <v>-4.64</v>
       </c>
-      <c r="K10" s="115">
+      <c r="K10" s="116">
         <v>-14.14</v>
       </c>
       <c r="L10" s="113">
         <v>-19.62</v>
       </c>
-      <c r="M10" s="106">
+      <c r="M10" s="117">
         <v>-20.09</v>
       </c>
       <c r="N10" s="114">
         <v>-18.71</v>
       </c>
-      <c r="O10" s="109">
+      <c r="O10" s="111">
         <v>-18.89</v>
       </c>
-      <c r="P10" s="116">
+      <c r="P10" s="105">
         <v>-19.15</v>
       </c>
-      <c r="Q10" s="117">
+      <c r="Q10" s="115">
         <v>-20.42</v>
       </c>
-      <c r="R10" s="107">
+      <c r="R10" s="106">
         <v>-17.25</v>
       </c>
-      <c r="S10" s="110">
+      <c r="S10" s="108">
         <v>-11.14</v>
       </c>
-      <c r="T10" s="105">
+      <c r="T10" s="109">
         <v>-16.22</v>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       <c r="C11" t="str">
         <v>600330</v>
       </c>
-      <c r="D11" s="129" t="str">
+      <c r="D11" s="119" t="str">
         <v>净卖: -6191.34万</v>
       </c>
       <c r="E11">
@@ -6135,25 +6135,25 @@
       <c r="H11">
         <v>10</v>
       </c>
-      <c r="I11" s="118">
+      <c r="I11" s="120">
         <v>-5.66</v>
       </c>
-      <c r="J11" s="124">
+      <c r="J11" s="125">
         <v>3.77</v>
       </c>
-      <c r="K11" s="125">
+      <c r="K11" s="126">
         <v>-0.51</v>
       </c>
-      <c r="L11" s="119">
+      <c r="L11" s="121">
         <v>-7.72</v>
       </c>
-      <c r="M11" s="130">
+      <c r="M11" s="118">
         <v>-10.89</v>
       </c>
-      <c r="N11" s="120">
+      <c r="N11" s="127">
         <v>-6.43</v>
       </c>
-      <c r="O11" s="121">
+      <c r="O11" s="128">
         <v>-8.23</v>
       </c>
       <c r="P11" s="122">
@@ -6162,13 +6162,13 @@
       <c r="Q11" s="123">
         <v>-2.23</v>
       </c>
-      <c r="R11" s="126">
+      <c r="R11" s="129">
         <v>-1.63</v>
       </c>
-      <c r="S11" s="127">
+      <c r="S11" s="124">
         <v>-0.77</v>
       </c>
-      <c r="T11" s="128">
+      <c r="T11" s="130">
         <v>86.36</v>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       <c r="C12" t="str">
         <v>600635</v>
       </c>
-      <c r="D12" s="140" t="str">
+      <c r="D12" s="135" t="str">
         <v>净买: 2557.50万</v>
       </c>
       <c r="E12">
@@ -6197,19 +6197,19 @@
       <c r="H12">
         <v>2.91</v>
       </c>
-      <c r="I12" s="141">
+      <c r="I12" s="140">
         <v>6.98</v>
       </c>
-      <c r="J12" s="138">
+      <c r="J12" s="136">
         <v>10.75</v>
       </c>
-      <c r="K12" s="136">
+      <c r="K12" s="141">
         <v>21.89</v>
       </c>
-      <c r="L12" s="131">
+      <c r="L12" s="132">
         <v>34.15</v>
       </c>
-      <c r="M12" s="132">
+      <c r="M12" s="137">
         <v>34.15</v>
       </c>
       <c r="N12" s="142">
@@ -6221,16 +6221,16 @@
       <c r="P12" s="133">
         <v>23.58</v>
       </c>
-      <c r="Q12" s="134">
+      <c r="Q12" s="138">
         <v>17.74</v>
       </c>
-      <c r="R12" s="137">
+      <c r="R12" s="131">
         <v>29.43</v>
       </c>
       <c r="S12" s="139">
         <v>33.77</v>
       </c>
-      <c r="T12" s="135">
+      <c r="T12" s="134">
         <v>1.51</v>
       </c>
     </row>
@@ -6244,7 +6244,7 @@
       <c r="C13" t="str">
         <v>002488</v>
       </c>
-      <c r="D13" s="150" t="str">
+      <c r="D13" s="146" t="str">
         <v>净卖: -1403.24万</v>
       </c>
       <c r="E13">
@@ -6259,40 +6259,40 @@
       <c r="H13">
         <v>-0.57</v>
       </c>
-      <c r="I13" s="151">
+      <c r="I13" s="144">
         <v>-9.51</v>
       </c>
-      <c r="J13" s="152">
+      <c r="J13" s="154">
         <v>-0.49</v>
       </c>
-      <c r="K13" s="153">
+      <c r="K13" s="155">
         <v>-8.7</v>
       </c>
-      <c r="L13" s="156">
+      <c r="L13" s="147">
         <v>-14.88</v>
       </c>
-      <c r="M13" s="144">
+      <c r="M13" s="148">
         <v>-14.96</v>
       </c>
-      <c r="N13" s="146">
+      <c r="N13" s="156">
         <v>-18.86</v>
       </c>
       <c r="O13" s="145">
         <v>-19.92</v>
       </c>
-      <c r="P13" s="147">
+      <c r="P13" s="152">
         <v>-18.54</v>
       </c>
-      <c r="Q13" s="148">
+      <c r="Q13" s="153">
         <v>-17.24</v>
       </c>
-      <c r="R13" s="154">
+      <c r="R13" s="149">
         <v>-15.93</v>
       </c>
-      <c r="S13" s="155">
+      <c r="S13" s="150">
         <v>-17.15</v>
       </c>
-      <c r="T13" s="149">
+      <c r="T13" s="151">
         <v>2.03</v>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       <c r="C14" t="str">
         <v>301246</v>
       </c>
-      <c r="D14" s="158" t="str">
+      <c r="D14" s="166" t="str">
         <v>净卖: -752.38万</v>
       </c>
       <c r="E14">
@@ -6321,40 +6321,40 @@
       <c r="H14">
         <v>-2.99</v>
       </c>
-      <c r="I14" s="168">
+      <c r="I14" s="164">
         <v>23.71</v>
       </c>
       <c r="J14" s="159">
         <v>15.87</v>
       </c>
-      <c r="K14" s="160">
+      <c r="K14" s="169">
         <v>21.68</v>
       </c>
-      <c r="L14" s="163">
+      <c r="L14" s="160">
         <v>20.7</v>
       </c>
-      <c r="M14" s="164">
+      <c r="M14" s="161">
         <v>16.22</v>
       </c>
-      <c r="N14" s="165">
+      <c r="N14" s="157">
         <v>18.95</v>
       </c>
-      <c r="O14" s="161">
+      <c r="O14" s="162">
         <v>19.79</v>
       </c>
       <c r="P14" s="167">
         <v>17.41</v>
       </c>
-      <c r="Q14" s="166">
+      <c r="Q14" s="158">
         <v>19.79</v>
       </c>
-      <c r="R14" s="169">
+      <c r="R14" s="168">
         <v>15.38</v>
       </c>
-      <c r="S14" s="162">
+      <c r="S14" s="165">
         <v>18.25</v>
       </c>
-      <c r="T14" s="157">
+      <c r="T14" s="163">
         <v>69.93</v>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       <c r="C15" t="str">
         <v>002198</v>
       </c>
-      <c r="D15" s="175" t="str">
+      <c r="D15" s="171" t="str">
         <v>净买: 1396.06万</v>
       </c>
       <c r="E15">
@@ -6383,40 +6383,40 @@
       <c r="H15">
         <v>9.79</v>
       </c>
-      <c r="I15" s="176">
+      <c r="I15" s="182">
         <v>0.24</v>
       </c>
       <c r="J15" s="177">
         <v>-9.75</v>
       </c>
-      <c r="K15" s="172">
+      <c r="K15" s="179">
         <v>-16.17</v>
       </c>
-      <c r="L15" s="178">
+      <c r="L15" s="172">
         <v>-16.77</v>
       </c>
       <c r="M15" s="173">
         <v>-20.33</v>
       </c>
-      <c r="N15" s="181">
+      <c r="N15" s="174">
         <v>-17.72</v>
       </c>
-      <c r="O15" s="179">
+      <c r="O15" s="180">
         <v>-12.72</v>
       </c>
-      <c r="P15" s="174">
+      <c r="P15" s="175">
         <v>-11.18</v>
       </c>
-      <c r="Q15" s="182">
+      <c r="Q15" s="181">
         <v>-10.7</v>
       </c>
       <c r="R15" s="170">
         <v>-10.23</v>
       </c>
-      <c r="S15" s="180">
+      <c r="S15" s="176">
         <v>-11.77</v>
       </c>
-      <c r="T15" s="171">
+      <c r="T15" s="178">
         <v>-6.78</v>
       </c>
     </row>
@@ -6430,7 +6430,7 @@
       <c r="C16" t="str">
         <v>002114</v>
       </c>
-      <c r="D16" s="194" t="str">
+      <c r="D16" s="191" t="str">
         <v>净卖: -121.61万</v>
       </c>
       <c r="E16">
@@ -6445,34 +6445,34 @@
       <c r="H16">
         <v>9.95</v>
       </c>
-      <c r="I16" s="185">
+      <c r="I16" s="186">
         <v>0</v>
       </c>
-      <c r="J16" s="186">
+      <c r="J16" s="187">
         <v>-9.98</v>
       </c>
-      <c r="K16" s="187">
+      <c r="K16" s="192">
         <v>-15.64</v>
       </c>
-      <c r="L16" s="191">
+      <c r="L16" s="185">
         <v>-7.2</v>
       </c>
       <c r="M16" s="188">
         <v>-9.16</v>
       </c>
-      <c r="N16" s="183">
+      <c r="N16" s="193">
         <v>-5.66</v>
       </c>
-      <c r="O16" s="192">
+      <c r="O16" s="183">
         <v>-7.3</v>
       </c>
-      <c r="P16" s="189">
+      <c r="P16" s="194">
         <v>-3.4</v>
       </c>
-      <c r="Q16" s="193">
+      <c r="Q16" s="195">
         <v>-6.17</v>
       </c>
-      <c r="R16" s="195">
+      <c r="R16" s="189">
         <v>-11.73</v>
       </c>
       <c r="S16" s="190">
@@ -6492,7 +6492,7 @@
       <c r="C17" t="str">
         <v>603815</v>
       </c>
-      <c r="D17" s="198" t="str">
+      <c r="D17" s="204" t="str">
         <v>净卖: -1097.64万</v>
       </c>
       <c r="E17">
@@ -6507,40 +6507,40 @@
       <c r="H17">
         <v>0.09</v>
       </c>
-      <c r="I17" s="207">
+      <c r="I17" s="200">
         <v>9.95</v>
       </c>
-      <c r="J17" s="202">
+      <c r="J17" s="198">
         <v>12.93</v>
       </c>
       <c r="K17" s="199">
         <v>12.57</v>
       </c>
-      <c r="L17" s="197">
+      <c r="L17" s="201">
         <v>17.45</v>
       </c>
-      <c r="M17" s="200">
+      <c r="M17" s="205">
         <v>9.76</v>
       </c>
-      <c r="N17" s="203">
+      <c r="N17" s="206">
         <v>9.22</v>
       </c>
       <c r="O17" s="208">
         <v>-1.72</v>
       </c>
-      <c r="P17" s="204">
+      <c r="P17" s="196">
         <v>-11.57</v>
       </c>
-      <c r="Q17" s="201">
+      <c r="Q17" s="202">
         <v>-15.01</v>
       </c>
-      <c r="R17" s="196">
+      <c r="R17" s="203">
         <v>-21.52</v>
       </c>
-      <c r="S17" s="205">
+      <c r="S17" s="197">
         <v>-23.87</v>
       </c>
-      <c r="T17" s="206">
+      <c r="T17" s="207">
         <v>-40.6</v>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       <c r="C18" t="str">
         <v>000890</v>
       </c>
-      <c r="D18" s="216" t="str">
+      <c r="D18" s="220" t="str">
         <v>净买: 1092.74万</v>
       </c>
       <c r="E18">
@@ -6569,40 +6569,40 @@
       <c r="H18">
         <v>10.05</v>
       </c>
-      <c r="I18" s="209">
+      <c r="I18" s="214">
         <v>0</v>
       </c>
-      <c r="J18" s="210">
+      <c r="J18" s="219">
         <v>10.06</v>
       </c>
-      <c r="K18" s="220">
+      <c r="K18" s="211">
         <v>11.46</v>
       </c>
-      <c r="L18" s="211">
+      <c r="L18" s="215">
         <v>0.31</v>
       </c>
-      <c r="M18" s="221">
+      <c r="M18" s="212">
         <v>-9.75</v>
       </c>
-      <c r="N18" s="212">
+      <c r="N18" s="213">
         <v>-9.6</v>
       </c>
-      <c r="O18" s="217">
+      <c r="O18" s="216">
         <v>-16.41</v>
       </c>
-      <c r="P18" s="213">
+      <c r="P18" s="221">
         <v>-14.24</v>
       </c>
-      <c r="Q18" s="218">
+      <c r="Q18" s="217">
         <v>-15.63</v>
       </c>
-      <c r="R18" s="219">
+      <c r="R18" s="218">
         <v>-16.87</v>
       </c>
-      <c r="S18" s="214">
+      <c r="S18" s="209">
         <v>-19.81</v>
       </c>
-      <c r="T18" s="215">
+      <c r="T18" s="210">
         <v>92.11</v>
       </c>
     </row>
@@ -6616,7 +6616,7 @@
       <c r="C19" t="str">
         <v>603067</v>
       </c>
-      <c r="D19" s="224" t="str">
+      <c r="D19" s="231" t="str">
         <v>净买: 1179.50万</v>
       </c>
       <c r="E19">
@@ -6631,40 +6631,40 @@
       <c r="H19">
         <v>-3.07</v>
       </c>
-      <c r="I19" s="225">
+      <c r="I19" s="232">
         <v>-5.37</v>
       </c>
-      <c r="J19" s="227">
+      <c r="J19" s="222">
         <v>-2.17</v>
       </c>
-      <c r="K19" s="228">
+      <c r="K19" s="229">
         <v>6.55</v>
       </c>
-      <c r="L19" s="229">
+      <c r="L19" s="223">
         <v>4.84</v>
       </c>
-      <c r="M19" s="232">
+      <c r="M19" s="233">
         <v>11.14</v>
       </c>
-      <c r="N19" s="223">
+      <c r="N19" s="230">
         <v>10.82</v>
       </c>
-      <c r="O19" s="230">
+      <c r="O19" s="225">
         <v>9.93</v>
       </c>
-      <c r="P19" s="233">
+      <c r="P19" s="224">
         <v>6.01</v>
       </c>
-      <c r="Q19" s="234">
+      <c r="Q19" s="226">
         <v>3.17</v>
       </c>
-      <c r="R19" s="222">
+      <c r="R19" s="234">
         <v>2.53</v>
       </c>
-      <c r="S19" s="231">
+      <c r="S19" s="227">
         <v>12.78</v>
       </c>
-      <c r="T19" s="226">
+      <c r="T19" s="228">
         <v>27.01</v>
       </c>
     </row>
@@ -6678,7 +6678,7 @@
       <c r="C20" t="str">
         <v>000890</v>
       </c>
-      <c r="D20" s="243" t="str">
+      <c r="D20" s="235" t="str">
         <v>净买: 1030.64万</v>
       </c>
       <c r="E20">
@@ -6693,40 +6693,40 @@
       <c r="H20">
         <v>-9.72</v>
       </c>
-      <c r="I20" s="238">
+      <c r="I20" s="236">
         <v>-0.31</v>
       </c>
-      <c r="J20" s="239">
+      <c r="J20" s="237">
         <v>-10.31</v>
       </c>
-      <c r="K20" s="236">
+      <c r="K20" s="241">
         <v>-10.15</v>
       </c>
-      <c r="L20" s="244">
+      <c r="L20" s="243">
         <v>-16.92</v>
       </c>
-      <c r="M20" s="240">
+      <c r="M20" s="238">
         <v>-14.77</v>
       </c>
-      <c r="N20" s="245">
+      <c r="N20" s="239">
         <v>-16.15</v>
       </c>
-      <c r="O20" s="246">
+      <c r="O20" s="244">
         <v>-17.38</v>
       </c>
-      <c r="P20" s="237">
+      <c r="P20" s="245">
         <v>-20.31</v>
       </c>
-      <c r="Q20" s="241">
+      <c r="Q20" s="240">
         <v>-20.62</v>
       </c>
-      <c r="R20" s="247">
+      <c r="R20" s="242">
         <v>-22</v>
       </c>
-      <c r="S20" s="235">
+      <c r="S20" s="246">
         <v>-21.69</v>
       </c>
-      <c r="T20" s="242">
+      <c r="T20" s="247">
         <v>90.92</v>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       <c r="C21" t="str">
         <v>000890</v>
       </c>
-      <c r="D21" s="250" t="str">
+      <c r="D21" s="254" t="str">
         <v>净卖: -1045.40万</v>
       </c>
       <c r="E21">
@@ -6755,40 +6755,40 @@
       <c r="H21">
         <v>-4.94</v>
       </c>
-      <c r="I21" s="251">
+      <c r="I21" s="249">
         <v>-5.36</v>
       </c>
-      <c r="J21" s="256">
+      <c r="J21" s="250">
         <v>-5.19</v>
       </c>
-      <c r="K21" s="257">
+      <c r="K21" s="259">
         <v>-12.34</v>
       </c>
-      <c r="L21" s="252">
+      <c r="L21" s="253">
         <v>-10.06</v>
       </c>
-      <c r="M21" s="253">
+      <c r="M21" s="255">
         <v>-11.53</v>
       </c>
-      <c r="N21" s="249">
+      <c r="N21" s="251">
         <v>-12.82</v>
       </c>
       <c r="O21" s="260">
         <v>-15.91</v>
       </c>
-      <c r="P21" s="254">
+      <c r="P21" s="248">
         <v>-16.23</v>
       </c>
-      <c r="Q21" s="258">
+      <c r="Q21" s="256">
         <v>-17.69</v>
       </c>
-      <c r="R21" s="255">
+      <c r="R21" s="257">
         <v>-17.37</v>
       </c>
-      <c r="S21" s="259">
+      <c r="S21" s="252">
         <v>-16.23</v>
       </c>
-      <c r="T21" s="248">
+      <c r="T21" s="258">
         <v>101.46</v>
       </c>
     </row>
@@ -6802,7 +6802,7 @@
       <c r="C22" t="str">
         <v>300409</v>
       </c>
-      <c r="D22" s="268" t="str">
+      <c r="D22" s="266" t="str">
         <v>净卖: -3259.20万</v>
       </c>
       <c r="E22">
@@ -6817,40 +6817,40 @@
       <c r="H22">
         <v>4.54</v>
       </c>
-      <c r="I22" s="270">
+      <c r="I22" s="271">
         <v>14.8</v>
       </c>
-      <c r="J22" s="271">
+      <c r="J22" s="272">
         <v>31.48</v>
       </c>
-      <c r="K22" s="266">
+      <c r="K22" s="267">
         <v>32.5</v>
       </c>
-      <c r="L22" s="272">
+      <c r="L22" s="261">
         <v>30.84</v>
       </c>
-      <c r="M22" s="273">
+      <c r="M22" s="264">
         <v>23.86</v>
       </c>
-      <c r="N22" s="269">
+      <c r="N22" s="268">
         <v>48.62</v>
       </c>
-      <c r="O22" s="261">
+      <c r="O22" s="269">
         <v>46.11</v>
       </c>
-      <c r="P22" s="262">
+      <c r="P22" s="273">
         <v>41.64</v>
       </c>
-      <c r="Q22" s="263">
+      <c r="Q22" s="262">
         <v>42.15</v>
       </c>
-      <c r="R22" s="264">
+      <c r="R22" s="265">
         <v>36.03</v>
       </c>
-      <c r="S22" s="265">
+      <c r="S22" s="263">
         <v>31.9</v>
       </c>
-      <c r="T22" s="267">
+      <c r="T22" s="270">
         <v>13.36</v>
       </c>
     </row>
@@ -6864,7 +6864,7 @@
       <c r="C23" t="str">
         <v>300409</v>
       </c>
-      <c r="D23" s="277" t="str">
+      <c r="D23" s="278" t="str">
         <v>净卖: -3736.61万</v>
       </c>
       <c r="E23">
@@ -6879,40 +6879,40 @@
       <c r="H23">
         <v>4.22</v>
       </c>
-      <c r="I23" s="282">
+      <c r="I23" s="279">
         <v>9.88</v>
       </c>
-      <c r="J23" s="274">
+      <c r="J23" s="283">
         <v>10.74</v>
       </c>
-      <c r="K23" s="283">
+      <c r="K23" s="284">
         <v>9.35</v>
       </c>
-      <c r="L23" s="278">
+      <c r="L23" s="275">
         <v>3.52</v>
       </c>
-      <c r="M23" s="275">
+      <c r="M23" s="276">
         <v>24.21</v>
       </c>
-      <c r="N23" s="286">
+      <c r="N23" s="280">
         <v>22.11</v>
       </c>
-      <c r="O23" s="284">
+      <c r="O23" s="281">
         <v>18.38</v>
       </c>
-      <c r="P23" s="285">
+      <c r="P23" s="277">
         <v>18.81</v>
       </c>
-      <c r="Q23" s="279">
+      <c r="Q23" s="285">
         <v>13.69</v>
       </c>
-      <c r="R23" s="280">
+      <c r="R23" s="286">
         <v>10.24</v>
       </c>
-      <c r="S23" s="276">
+      <c r="S23" s="282">
         <v>8</v>
       </c>
-      <c r="T23" s="281">
+      <c r="T23" s="274">
         <v>-5.26</v>
       </c>
     </row>
@@ -6926,7 +6926,7 @@
       <c r="C24" t="str">
         <v>300409</v>
       </c>
-      <c r="D24" s="291" t="str">
+      <c r="D24" s="298" t="str">
         <v>净卖: -2006.10万</v>
       </c>
       <c r="E24">
@@ -6941,40 +6941,40 @@
       <c r="H24">
         <v>1.68</v>
       </c>
-      <c r="I24" s="296">
+      <c r="I24" s="299">
         <v>18</v>
       </c>
-      <c r="J24" s="297">
+      <c r="J24" s="288">
         <v>16.01</v>
       </c>
-      <c r="K24" s="293">
+      <c r="K24" s="296">
         <v>12.46</v>
       </c>
-      <c r="L24" s="298">
+      <c r="L24" s="297">
         <v>12.87</v>
       </c>
-      <c r="M24" s="294">
+      <c r="M24" s="293">
         <v>8</v>
       </c>
-      <c r="N24" s="289">
+      <c r="N24" s="294">
         <v>4.73</v>
       </c>
-      <c r="O24" s="290">
+      <c r="O24" s="289">
         <v>2.6</v>
       </c>
-      <c r="P24" s="299">
+      <c r="P24" s="290">
         <v>1.82</v>
       </c>
-      <c r="Q24" s="287">
+      <c r="Q24" s="291">
         <v>2.36</v>
       </c>
-      <c r="R24" s="295">
+      <c r="R24" s="292">
         <v>8.11</v>
       </c>
-      <c r="S24" s="288">
+      <c r="S24" s="295">
         <v>5.67</v>
       </c>
-      <c r="T24" s="292">
+      <c r="T24" s="287">
         <v>-10</v>
       </c>
     </row>
@@ -7037,40 +7037,40 @@
       <c r="F26" t="str"/>
       <c r="G26" t="str"/>
       <c r="H26" t="str"/>
-      <c r="I26" s="300">
+      <c r="I26" s="304">
         <v>52.17</v>
       </c>
-      <c r="J26" s="304">
+      <c r="J26" s="307">
         <v>52.17</v>
       </c>
-      <c r="K26" s="301">
+      <c r="K26" s="305">
         <v>52.17</v>
       </c>
-      <c r="L26" s="305">
+      <c r="L26" s="308">
         <v>47.83</v>
       </c>
-      <c r="M26" s="306">
+      <c r="M26" s="310">
         <v>43.48</v>
       </c>
-      <c r="N26" s="307">
+      <c r="N26" s="300">
         <v>39.13</v>
       </c>
-      <c r="O26" s="308">
+      <c r="O26" s="301">
         <v>34.78</v>
       </c>
-      <c r="P26" s="309">
+      <c r="P26" s="302">
         <v>39.13</v>
       </c>
-      <c r="Q26" s="302">
+      <c r="Q26" s="311">
         <v>39.13</v>
       </c>
-      <c r="R26" s="303">
+      <c r="R26" s="309">
         <v>39.13</v>
       </c>
-      <c r="S26" s="310">
+      <c r="S26" s="306">
         <v>39.13</v>
       </c>
-      <c r="T26" s="311">
+      <c r="T26" s="303">
         <v>52.17</v>
       </c>
     </row>
@@ -7085,40 +7085,40 @@
       <c r="F27" t="str"/>
       <c r="G27" t="str"/>
       <c r="H27" t="str"/>
-      <c r="I27" s="315">
+      <c r="I27" s="323">
         <v>3.46</v>
       </c>
-      <c r="J27" s="322">
+      <c r="J27" s="315">
         <v>2.89</v>
       </c>
-      <c r="K27" s="323">
+      <c r="K27" s="316">
         <v>0.67</v>
       </c>
-      <c r="L27" s="316">
+      <c r="L27" s="312">
         <v>-0.46</v>
       </c>
       <c r="M27" s="319">
         <v>-1.36</v>
       </c>
-      <c r="N27" s="312">
+      <c r="N27" s="313">
         <v>-0.02</v>
       </c>
       <c r="O27" s="317">
         <v>-1.62</v>
       </c>
-      <c r="P27" s="318">
+      <c r="P27" s="320">
         <v>-2.08</v>
       </c>
-      <c r="Q27" s="320">
+      <c r="Q27" s="318">
         <v>-2.45</v>
       </c>
-      <c r="R27" s="321">
+      <c r="R27" s="314">
         <v>-2.62</v>
       </c>
-      <c r="S27" s="313">
+      <c r="S27" s="321">
         <v>-1.7</v>
       </c>
-      <c r="T27" s="314">
+      <c r="T27" s="322">
         <v>16.19</v>
       </c>
     </row>

--- a/youzi/王海祥/index.xlsx
+++ b/youzi/王海祥/index.xlsx
@@ -39,6 +39,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -87,31 +117,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFDF4A58"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,43 +129,1657 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD1303F"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47B460"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81CB92"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF57BA6E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF62BE77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3A49"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCEEBD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3747"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC949C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF5F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC380"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3B4A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6707C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -171,7 +1791,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4D"/>
+        <fgColor rgb="FF1A7130"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -183,157 +1803,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE3626E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF57BA6E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF62BE77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF47B460"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -345,853 +1839,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3A49"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCEEBD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3747"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C1C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF5F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F41"/>
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0EBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208838"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF72C585"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF48B460"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCFEFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1203,775 +1971,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3B4A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6707C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208838"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0EBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF72C585"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCFEFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF50B768"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC380"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF48B460"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -5562,7 +5562,7 @@
       <c r="C2" t="str">
         <v>002276</v>
       </c>
-      <c r="D2" s="1" t="str">
+      <c r="D2" s="6" t="str">
         <v>净卖: -3245.54万</v>
       </c>
       <c r="E2">
@@ -5577,22 +5577,22 @@
       <c r="H2">
         <v>3.37</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="5">
         <v>6.43</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="10">
         <v>17.1</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="11">
         <v>11.56</v>
       </c>
-      <c r="L2" s="9">
+      <c r="L2" s="12">
         <v>22.72</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="7">
         <v>30.54</v>
       </c>
-      <c r="N2" s="12">
+      <c r="N2" s="8">
         <v>43.57</v>
       </c>
       <c r="O2" s="13">
@@ -5601,17 +5601,17 @@
       <c r="P2" s="3">
         <v>40.15</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="Q2" s="9">
         <v>33.31</v>
       </c>
-      <c r="R2" s="7">
+      <c r="R2" s="4">
         <v>34.45</v>
       </c>
-      <c r="S2" s="4">
+      <c r="S2" s="1">
         <v>40.8</v>
       </c>
-      <c r="T2" s="8">
-        <v>17.92</v>
+      <c r="T2" s="2">
+        <v>19.95</v>
       </c>
     </row>
     <row r="3">
@@ -5639,41 +5639,41 @@
       <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3" s="19">
+      <c r="I3" s="25">
         <v>10.15</v>
       </c>
-      <c r="J3" s="15">
+      <c r="J3" s="26">
         <v>5.97</v>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="14">
         <v>4.48</v>
       </c>
-      <c r="L3" s="25">
+      <c r="L3" s="15">
         <v>3.88</v>
       </c>
-      <c r="M3" s="26">
+      <c r="M3" s="16">
         <v>4.18</v>
       </c>
-      <c r="N3" s="14">
+      <c r="N3" s="17">
         <v>3.88</v>
       </c>
-      <c r="O3" s="22">
+      <c r="O3" s="18">
         <v>5.67</v>
       </c>
-      <c r="P3" s="20">
+      <c r="P3" s="19">
         <v>5.07</v>
       </c>
-      <c r="Q3" s="23">
+      <c r="Q3" s="22">
         <v>4.78</v>
       </c>
-      <c r="R3" s="21">
+      <c r="R3" s="20">
         <v>2.09</v>
       </c>
-      <c r="S3" s="17">
+      <c r="S3" s="21">
         <v>4.18</v>
       </c>
-      <c r="T3" s="18">
-        <v>17.31</v>
+      <c r="T3" s="23">
+        <v>16.72</v>
       </c>
     </row>
     <row r="4">
@@ -5686,7 +5686,7 @@
       <c r="C4" t="str">
         <v>003020</v>
       </c>
-      <c r="D4" s="30" t="str">
+      <c r="D4" s="31" t="str">
         <v>净买: 1240.36万</v>
       </c>
       <c r="E4">
@@ -5701,41 +5701,41 @@
       <c r="H4">
         <v>-3.75</v>
       </c>
-      <c r="I4" s="34">
+      <c r="I4" s="36">
         <v>-6.49</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="37">
         <v>-15.84</v>
       </c>
-      <c r="K4" s="36">
+      <c r="K4" s="32">
         <v>-23.08</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="28">
         <v>-24.06</v>
       </c>
-      <c r="M4" s="37">
+      <c r="M4" s="29">
         <v>-21.79</v>
       </c>
-      <c r="N4" s="38">
+      <c r="N4" s="34">
         <v>-20.71</v>
       </c>
-      <c r="O4" s="32">
+      <c r="O4" s="38">
         <v>-22.89</v>
       </c>
-      <c r="P4" s="39">
+      <c r="P4" s="30">
         <v>-24.61</v>
       </c>
-      <c r="Q4" s="29">
+      <c r="Q4" s="39">
         <v>-23.38</v>
       </c>
-      <c r="R4" s="33">
+      <c r="R4" s="35">
         <v>-24.35</v>
       </c>
-      <c r="S4" s="27">
+      <c r="S4" s="33">
         <v>-22.4</v>
       </c>
-      <c r="T4" s="35">
-        <v>-21.43</v>
+      <c r="T4" s="27">
+        <v>-22.31</v>
       </c>
     </row>
     <row r="5">
@@ -5748,7 +5748,7 @@
       <c r="C5" t="str">
         <v>003020</v>
       </c>
-      <c r="D5" s="42" t="str">
+      <c r="D5" s="46" t="str">
         <v>净买: 1925.03万</v>
       </c>
       <c r="E5">
@@ -5763,41 +5763,41 @@
       <c r="H5">
         <v>-4.9</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="47">
         <v>-3.89</v>
       </c>
-      <c r="J5" s="48">
+      <c r="J5" s="51">
         <v>-5.11</v>
       </c>
-      <c r="K5" s="45">
+      <c r="K5" s="43">
         <v>-2.27</v>
       </c>
-      <c r="L5" s="44">
+      <c r="L5" s="48">
         <v>-0.93</v>
       </c>
-      <c r="M5" s="49">
+      <c r="M5" s="50">
         <v>-3.65</v>
       </c>
-      <c r="N5" s="46">
+      <c r="N5" s="52">
         <v>-5.8</v>
       </c>
-      <c r="O5" s="50">
+      <c r="O5" s="40">
         <v>-4.26</v>
       </c>
-      <c r="P5" s="51">
+      <c r="P5" s="41">
         <v>-5.48</v>
       </c>
-      <c r="Q5" s="47">
+      <c r="Q5" s="49">
         <v>-3.04</v>
       </c>
-      <c r="R5" s="52">
+      <c r="R5" s="42">
         <v>-2.07</v>
       </c>
-      <c r="S5" s="40">
+      <c r="S5" s="44">
         <v>-0.97</v>
       </c>
-      <c r="T5" s="41">
-        <v>-1.83</v>
+      <c r="T5" s="45">
+        <v>-2.92</v>
       </c>
     </row>
     <row r="6">
@@ -5810,7 +5810,7 @@
       <c r="C6" t="str">
         <v>603607</v>
       </c>
-      <c r="D6" s="57" t="str">
+      <c r="D6" s="61" t="str">
         <v>净卖: -1819.82万</v>
       </c>
       <c r="E6">
@@ -5825,41 +5825,41 @@
       <c r="H6">
         <v>9.92</v>
       </c>
-      <c r="I6" s="64">
+      <c r="I6" s="53">
         <v>0.06</v>
       </c>
-      <c r="J6" s="61">
+      <c r="J6" s="57">
         <v>4.62</v>
       </c>
-      <c r="K6" s="53">
+      <c r="K6" s="54">
         <v>4.87</v>
       </c>
-      <c r="L6" s="62">
+      <c r="L6" s="63">
         <v>-5.62</v>
       </c>
-      <c r="M6" s="58">
+      <c r="M6" s="64">
         <v>-15.05</v>
       </c>
-      <c r="N6" s="65">
+      <c r="N6" s="58">
         <v>-13.34</v>
       </c>
-      <c r="O6" s="54">
+      <c r="O6" s="59">
         <v>-18.49</v>
       </c>
-      <c r="P6" s="55">
+      <c r="P6" s="62">
         <v>-19.11</v>
       </c>
-      <c r="Q6" s="59">
+      <c r="Q6" s="65">
         <v>-16.36</v>
       </c>
-      <c r="R6" s="56">
+      <c r="R6" s="60">
         <v>-15.71</v>
       </c>
-      <c r="S6" s="60">
+      <c r="S6" s="55">
         <v>-10.68</v>
       </c>
-      <c r="T6" s="63">
-        <v>-27.48</v>
+      <c r="T6" s="56">
+        <v>-26.58</v>
       </c>
     </row>
     <row r="7">
@@ -5872,7 +5872,7 @@
       <c r="C7" t="str">
         <v>603607</v>
       </c>
-      <c r="D7" s="66" t="str">
+      <c r="D7" s="70" t="str">
         <v>净卖: -2523.15万</v>
       </c>
       <c r="E7">
@@ -5887,41 +5887,41 @@
       <c r="H7">
         <v>1.49</v>
       </c>
-      <c r="I7" s="73">
+      <c r="I7" s="75">
         <v>-1.24</v>
       </c>
-      <c r="J7" s="74">
+      <c r="J7" s="78">
         <v>-11.12</v>
       </c>
-      <c r="K7" s="69">
+      <c r="K7" s="71">
         <v>-20</v>
       </c>
-      <c r="L7" s="78">
+      <c r="L7" s="72">
         <v>-18.38</v>
       </c>
-      <c r="M7" s="67">
+      <c r="M7" s="76">
         <v>-23.24</v>
       </c>
-      <c r="N7" s="75">
+      <c r="N7" s="66">
         <v>-23.82</v>
       </c>
-      <c r="O7" s="70">
+      <c r="O7" s="67">
         <v>-21.24</v>
       </c>
-      <c r="P7" s="76">
+      <c r="P7" s="69">
         <v>-20.62</v>
       </c>
-      <c r="Q7" s="71">
+      <c r="Q7" s="68">
         <v>-15.88</v>
       </c>
-      <c r="R7" s="68">
+      <c r="R7" s="77">
         <v>-18.09</v>
       </c>
-      <c r="S7" s="77">
+      <c r="S7" s="73">
         <v>-25.41</v>
       </c>
-      <c r="T7" s="72">
-        <v>-31.71</v>
+      <c r="T7" s="74">
+        <v>-30.85</v>
       </c>
     </row>
     <row r="8">
@@ -5934,7 +5934,7 @@
       <c r="C8" t="str">
         <v>603823</v>
       </c>
-      <c r="D8" s="79" t="str">
+      <c r="D8" s="82" t="str">
         <v>净卖: -577.99万</v>
       </c>
       <c r="E8">
@@ -5949,41 +5949,41 @@
       <c r="H8">
         <v>-1.03</v>
       </c>
-      <c r="I8" s="80">
+      <c r="I8" s="83">
         <v>11.19</v>
       </c>
-      <c r="J8" s="85">
+      <c r="J8" s="79">
         <v>10.49</v>
       </c>
       <c r="K8" s="84">
         <v>7.03</v>
       </c>
-      <c r="L8" s="81">
+      <c r="L8" s="89">
         <v>2.34</v>
       </c>
-      <c r="M8" s="89">
+      <c r="M8" s="90">
         <v>4.94</v>
       </c>
-      <c r="N8" s="82">
+      <c r="N8" s="85">
         <v>-1.13</v>
       </c>
-      <c r="O8" s="86">
+      <c r="O8" s="88">
         <v>-2.6</v>
       </c>
-      <c r="P8" s="83">
+      <c r="P8" s="86">
         <v>7.11</v>
       </c>
-      <c r="Q8" s="90">
+      <c r="Q8" s="80">
         <v>11.71</v>
       </c>
       <c r="R8" s="87">
         <v>17.52</v>
       </c>
-      <c r="S8" s="88">
+      <c r="S8" s="81">
         <v>17.43</v>
       </c>
       <c r="T8" s="91">
-        <v>40.16</v>
+        <v>40.24</v>
       </c>
     </row>
     <row r="9">
@@ -5996,7 +5996,7 @@
       <c r="C9" t="str">
         <v>601279</v>
       </c>
-      <c r="D9" s="97" t="str">
+      <c r="D9" s="92" t="str">
         <v>净卖: -624.00万</v>
       </c>
       <c r="E9">
@@ -6011,41 +6011,41 @@
       <c r="H9">
         <v>10.09</v>
       </c>
-      <c r="I9" s="93">
+      <c r="I9" s="99">
         <v>0</v>
       </c>
-      <c r="J9" s="103">
+      <c r="J9" s="93">
         <v>-8.75</v>
       </c>
-      <c r="K9" s="101">
+      <c r="K9" s="100">
         <v>-17.92</v>
       </c>
-      <c r="L9" s="98">
+      <c r="L9" s="94">
         <v>-22.08</v>
       </c>
       <c r="M9" s="102">
         <v>-23.12</v>
       </c>
-      <c r="N9" s="94">
+      <c r="N9" s="95">
         <v>-21.88</v>
       </c>
-      <c r="O9" s="99">
+      <c r="O9" s="96">
         <v>-22.29</v>
       </c>
-      <c r="P9" s="95">
+      <c r="P9" s="103">
         <v>-21.25</v>
       </c>
-      <c r="Q9" s="96">
+      <c r="Q9" s="101">
         <v>-20.62</v>
       </c>
-      <c r="R9" s="100">
+      <c r="R9" s="97">
         <v>-21.25</v>
       </c>
-      <c r="S9" s="104">
+      <c r="S9" s="98">
         <v>-19.37</v>
       </c>
-      <c r="T9" s="92">
-        <v>-18.12</v>
+      <c r="T9" s="104">
+        <v>-18.54</v>
       </c>
     </row>
     <row r="10">
@@ -6058,7 +6058,7 @@
       <c r="C10" t="str">
         <v>600980</v>
       </c>
-      <c r="D10" s="107" t="str">
+      <c r="D10" s="108" t="str">
         <v>净卖: -1981.34万</v>
       </c>
       <c r="E10">
@@ -6073,41 +6073,41 @@
       <c r="H10">
         <v>-0.58</v>
       </c>
-      <c r="I10" s="110">
+      <c r="I10" s="109">
         <v>5.96</v>
       </c>
-      <c r="J10" s="112">
+      <c r="J10" s="106">
         <v>-4.64</v>
       </c>
-      <c r="K10" s="116">
+      <c r="K10" s="112">
         <v>-14.14</v>
       </c>
       <c r="L10" s="113">
         <v>-19.62</v>
       </c>
-      <c r="M10" s="117">
+      <c r="M10" s="116">
         <v>-20.09</v>
       </c>
       <c r="N10" s="114">
         <v>-18.71</v>
       </c>
-      <c r="O10" s="111">
+      <c r="O10" s="117">
         <v>-18.89</v>
       </c>
       <c r="P10" s="105">
         <v>-19.15</v>
       </c>
-      <c r="Q10" s="115">
+      <c r="Q10" s="110">
         <v>-20.42</v>
       </c>
-      <c r="R10" s="106">
+      <c r="R10" s="107">
         <v>-17.25</v>
       </c>
-      <c r="S10" s="108">
+      <c r="S10" s="111">
         <v>-11.14</v>
       </c>
-      <c r="T10" s="109">
-        <v>-16.22</v>
+      <c r="T10" s="115">
+        <v>-15.24</v>
       </c>
     </row>
     <row r="11">
@@ -6120,7 +6120,7 @@
       <c r="C11" t="str">
         <v>600330</v>
       </c>
-      <c r="D11" s="119" t="str">
+      <c r="D11" s="130" t="str">
         <v>净卖: -6191.34万</v>
       </c>
       <c r="E11">
@@ -6135,41 +6135,41 @@
       <c r="H11">
         <v>10</v>
       </c>
-      <c r="I11" s="120">
+      <c r="I11" s="118">
         <v>-5.66</v>
       </c>
-      <c r="J11" s="125">
+      <c r="J11" s="126">
         <v>3.77</v>
       </c>
-      <c r="K11" s="126">
+      <c r="K11" s="122">
         <v>-0.51</v>
       </c>
-      <c r="L11" s="121">
+      <c r="L11" s="123">
         <v>-7.72</v>
       </c>
-      <c r="M11" s="118">
+      <c r="M11" s="124">
         <v>-10.89</v>
       </c>
-      <c r="N11" s="127">
+      <c r="N11" s="119">
         <v>-6.43</v>
       </c>
-      <c r="O11" s="128">
+      <c r="O11" s="127">
         <v>-8.23</v>
       </c>
-      <c r="P11" s="122">
+      <c r="P11" s="120">
         <v>-3.77</v>
       </c>
-      <c r="Q11" s="123">
+      <c r="Q11" s="125">
         <v>-2.23</v>
       </c>
-      <c r="R11" s="129">
+      <c r="R11" s="128">
         <v>-1.63</v>
       </c>
-      <c r="S11" s="124">
+      <c r="S11" s="129">
         <v>-0.77</v>
       </c>
-      <c r="T11" s="130">
-        <v>86.36</v>
+      <c r="T11" s="121">
+        <v>104.97</v>
       </c>
     </row>
     <row r="12">
@@ -6182,7 +6182,7 @@
       <c r="C12" t="str">
         <v>600635</v>
       </c>
-      <c r="D12" s="135" t="str">
+      <c r="D12" s="139" t="str">
         <v>净买: 2557.50万</v>
       </c>
       <c r="E12">
@@ -6200,38 +6200,38 @@
       <c r="I12" s="140">
         <v>6.98</v>
       </c>
-      <c r="J12" s="136">
+      <c r="J12" s="141">
         <v>10.75</v>
       </c>
-      <c r="K12" s="141">
+      <c r="K12" s="131">
         <v>21.89</v>
       </c>
-      <c r="L12" s="132">
+      <c r="L12" s="142">
         <v>34.15</v>
       </c>
-      <c r="M12" s="137">
+      <c r="M12" s="132">
         <v>34.15</v>
       </c>
-      <c r="N12" s="142">
+      <c r="N12" s="143">
         <v>30.38</v>
       </c>
-      <c r="O12" s="143">
+      <c r="O12" s="133">
         <v>28.49</v>
       </c>
-      <c r="P12" s="133">
+      <c r="P12" s="135">
         <v>23.58</v>
       </c>
-      <c r="Q12" s="138">
+      <c r="Q12" s="136">
         <v>17.74</v>
       </c>
-      <c r="R12" s="131">
+      <c r="R12" s="137">
         <v>29.43</v>
       </c>
-      <c r="S12" s="139">
+      <c r="S12" s="138">
         <v>33.77</v>
       </c>
       <c r="T12" s="134">
-        <v>1.51</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="13">
@@ -6244,7 +6244,7 @@
       <c r="C13" t="str">
         <v>002488</v>
       </c>
-      <c r="D13" s="146" t="str">
+      <c r="D13" s="152" t="str">
         <v>净卖: -1403.24万</v>
       </c>
       <c r="E13">
@@ -6262,38 +6262,38 @@
       <c r="I13" s="144">
         <v>-9.51</v>
       </c>
-      <c r="J13" s="154">
+      <c r="J13" s="153">
         <v>-0.49</v>
       </c>
-      <c r="K13" s="155">
+      <c r="K13" s="154">
         <v>-8.7</v>
       </c>
-      <c r="L13" s="147">
+      <c r="L13" s="148">
         <v>-14.88</v>
       </c>
-      <c r="M13" s="148">
+      <c r="M13" s="149">
         <v>-14.96</v>
       </c>
-      <c r="N13" s="156">
+      <c r="N13" s="150">
         <v>-18.86</v>
       </c>
       <c r="O13" s="145">
         <v>-19.92</v>
       </c>
-      <c r="P13" s="152">
+      <c r="P13" s="146">
         <v>-18.54</v>
       </c>
-      <c r="Q13" s="153">
+      <c r="Q13" s="151">
         <v>-17.24</v>
       </c>
-      <c r="R13" s="149">
+      <c r="R13" s="155">
         <v>-15.93</v>
       </c>
-      <c r="S13" s="150">
+      <c r="S13" s="156">
         <v>-17.15</v>
       </c>
-      <c r="T13" s="151">
-        <v>2.03</v>
+      <c r="T13" s="147">
+        <v>0.08</v>
       </c>
     </row>
     <row r="14">
@@ -6306,7 +6306,7 @@
       <c r="C14" t="str">
         <v>301246</v>
       </c>
-      <c r="D14" s="166" t="str">
+      <c r="D14" s="165" t="str">
         <v>净卖: -752.38万</v>
       </c>
       <c r="E14">
@@ -6321,41 +6321,41 @@
       <c r="H14">
         <v>-2.99</v>
       </c>
-      <c r="I14" s="164">
+      <c r="I14" s="157">
         <v>23.71</v>
       </c>
-      <c r="J14" s="159">
+      <c r="J14" s="167">
         <v>15.87</v>
       </c>
-      <c r="K14" s="169">
+      <c r="K14" s="158">
         <v>21.68</v>
       </c>
-      <c r="L14" s="160">
+      <c r="L14" s="159">
         <v>20.7</v>
       </c>
-      <c r="M14" s="161">
+      <c r="M14" s="160">
         <v>16.22</v>
       </c>
-      <c r="N14" s="157">
+      <c r="N14" s="168">
         <v>18.95</v>
       </c>
-      <c r="O14" s="162">
+      <c r="O14" s="163">
         <v>19.79</v>
       </c>
-      <c r="P14" s="167">
+      <c r="P14" s="169">
         <v>17.41</v>
       </c>
-      <c r="Q14" s="158">
+      <c r="Q14" s="164">
         <v>19.79</v>
       </c>
-      <c r="R14" s="168">
+      <c r="R14" s="166">
         <v>15.38</v>
       </c>
-      <c r="S14" s="165">
+      <c r="S14" s="161">
         <v>18.25</v>
       </c>
-      <c r="T14" s="163">
-        <v>69.93</v>
+      <c r="T14" s="162">
+        <v>70.42</v>
       </c>
     </row>
     <row r="15">
@@ -6368,7 +6368,7 @@
       <c r="C15" t="str">
         <v>002198</v>
       </c>
-      <c r="D15" s="171" t="str">
+      <c r="D15" s="182" t="str">
         <v>净买: 1396.06万</v>
       </c>
       <c r="E15">
@@ -6383,41 +6383,41 @@
       <c r="H15">
         <v>9.79</v>
       </c>
-      <c r="I15" s="182">
+      <c r="I15" s="170">
         <v>0.24</v>
       </c>
-      <c r="J15" s="177">
+      <c r="J15" s="171">
         <v>-9.75</v>
       </c>
-      <c r="K15" s="179">
+      <c r="K15" s="177">
         <v>-16.17</v>
       </c>
-      <c r="L15" s="172">
+      <c r="L15" s="178">
         <v>-16.77</v>
       </c>
-      <c r="M15" s="173">
+      <c r="M15" s="172">
         <v>-20.33</v>
       </c>
-      <c r="N15" s="174">
+      <c r="N15" s="175">
         <v>-17.72</v>
       </c>
-      <c r="O15" s="180">
+      <c r="O15" s="173">
         <v>-12.72</v>
       </c>
-      <c r="P15" s="175">
+      <c r="P15" s="174">
         <v>-11.18</v>
       </c>
-      <c r="Q15" s="181">
+      <c r="Q15" s="179">
         <v>-10.7</v>
       </c>
-      <c r="R15" s="170">
+      <c r="R15" s="180">
         <v>-10.23</v>
       </c>
       <c r="S15" s="176">
         <v>-11.77</v>
       </c>
-      <c r="T15" s="178">
-        <v>-6.78</v>
+      <c r="T15" s="181">
+        <v>-6.54</v>
       </c>
     </row>
     <row r="16">
@@ -6430,7 +6430,7 @@
       <c r="C16" t="str">
         <v>002114</v>
       </c>
-      <c r="D16" s="191" t="str">
+      <c r="D16" s="193" t="str">
         <v>净卖: -121.61万</v>
       </c>
       <c r="E16">
@@ -6445,41 +6445,41 @@
       <c r="H16">
         <v>9.95</v>
       </c>
-      <c r="I16" s="186">
+      <c r="I16" s="194">
         <v>0</v>
       </c>
-      <c r="J16" s="187">
+      <c r="J16" s="188">
         <v>-9.98</v>
       </c>
-      <c r="K16" s="192">
+      <c r="K16" s="189">
         <v>-15.64</v>
       </c>
-      <c r="L16" s="185">
+      <c r="L16" s="195">
         <v>-7.2</v>
       </c>
-      <c r="M16" s="188">
+      <c r="M16" s="184">
         <v>-9.16</v>
       </c>
-      <c r="N16" s="193">
+      <c r="N16" s="185">
         <v>-5.66</v>
       </c>
-      <c r="O16" s="183">
+      <c r="O16" s="191">
         <v>-7.3</v>
       </c>
-      <c r="P16" s="194">
+      <c r="P16" s="183">
         <v>-3.4</v>
       </c>
-      <c r="Q16" s="195">
+      <c r="Q16" s="186">
         <v>-6.17</v>
       </c>
-      <c r="R16" s="189">
+      <c r="R16" s="190">
         <v>-11.73</v>
       </c>
-      <c r="S16" s="190">
+      <c r="S16" s="187">
         <v>-10.7</v>
       </c>
-      <c r="T16" s="184">
-        <v>-8.33</v>
+      <c r="T16" s="192">
+        <v>-5.56</v>
       </c>
     </row>
     <row r="17">
@@ -6492,7 +6492,7 @@
       <c r="C17" t="str">
         <v>603815</v>
       </c>
-      <c r="D17" s="204" t="str">
+      <c r="D17" s="199" t="str">
         <v>净卖: -1097.64万</v>
       </c>
       <c r="E17">
@@ -6507,41 +6507,41 @@
       <c r="H17">
         <v>0.09</v>
       </c>
-      <c r="I17" s="200">
+      <c r="I17" s="204">
         <v>9.95</v>
       </c>
-      <c r="J17" s="198">
+      <c r="J17" s="196">
         <v>12.93</v>
       </c>
-      <c r="K17" s="199">
+      <c r="K17" s="205">
         <v>12.57</v>
       </c>
-      <c r="L17" s="201">
+      <c r="L17" s="206">
         <v>17.45</v>
       </c>
-      <c r="M17" s="205">
+      <c r="M17" s="200">
         <v>9.76</v>
       </c>
-      <c r="N17" s="206">
+      <c r="N17" s="201">
         <v>9.22</v>
       </c>
-      <c r="O17" s="208">
+      <c r="O17" s="202">
         <v>-1.72</v>
       </c>
-      <c r="P17" s="196">
+      <c r="P17" s="197">
         <v>-11.57</v>
       </c>
-      <c r="Q17" s="202">
+      <c r="Q17" s="203">
         <v>-15.01</v>
       </c>
-      <c r="R17" s="203">
+      <c r="R17" s="207">
         <v>-21.52</v>
       </c>
-      <c r="S17" s="197">
+      <c r="S17" s="208">
         <v>-23.87</v>
       </c>
-      <c r="T17" s="207">
-        <v>-40.6</v>
+      <c r="T17" s="198">
+        <v>-41.86</v>
       </c>
     </row>
     <row r="18">
@@ -6554,7 +6554,7 @@
       <c r="C18" t="str">
         <v>000890</v>
       </c>
-      <c r="D18" s="220" t="str">
+      <c r="D18" s="212" t="str">
         <v>净买: 1092.74万</v>
       </c>
       <c r="E18">
@@ -6569,41 +6569,41 @@
       <c r="H18">
         <v>10.05</v>
       </c>
-      <c r="I18" s="214">
+      <c r="I18" s="219">
         <v>0</v>
       </c>
-      <c r="J18" s="219">
+      <c r="J18" s="220">
         <v>10.06</v>
       </c>
-      <c r="K18" s="211">
+      <c r="K18" s="213">
         <v>11.46</v>
       </c>
-      <c r="L18" s="215">
+      <c r="L18" s="216">
         <v>0.31</v>
       </c>
-      <c r="M18" s="212">
+      <c r="M18" s="221">
         <v>-9.75</v>
       </c>
-      <c r="N18" s="213">
+      <c r="N18" s="209">
         <v>-9.6</v>
       </c>
-      <c r="O18" s="216">
+      <c r="O18" s="214">
         <v>-16.41</v>
       </c>
-      <c r="P18" s="221">
+      <c r="P18" s="215">
         <v>-14.24</v>
       </c>
-      <c r="Q18" s="217">
+      <c r="Q18" s="210">
         <v>-15.63</v>
       </c>
-      <c r="R18" s="218">
+      <c r="R18" s="211">
         <v>-16.87</v>
       </c>
-      <c r="S18" s="209">
+      <c r="S18" s="217">
         <v>-19.81</v>
       </c>
-      <c r="T18" s="210">
-        <v>92.11</v>
+      <c r="T18" s="218">
+        <v>109.75</v>
       </c>
     </row>
     <row r="19">
@@ -6616,7 +6616,7 @@
       <c r="C19" t="str">
         <v>603067</v>
       </c>
-      <c r="D19" s="231" t="str">
+      <c r="D19" s="228" t="str">
         <v>净买: 1179.50万</v>
       </c>
       <c r="E19">
@@ -6631,25 +6631,25 @@
       <c r="H19">
         <v>-3.07</v>
       </c>
-      <c r="I19" s="232">
+      <c r="I19" s="229">
         <v>-5.37</v>
       </c>
-      <c r="J19" s="222">
+      <c r="J19" s="230">
         <v>-2.17</v>
       </c>
-      <c r="K19" s="229">
+      <c r="K19" s="231">
         <v>6.55</v>
       </c>
       <c r="L19" s="223">
         <v>4.84</v>
       </c>
-      <c r="M19" s="233">
+      <c r="M19" s="227">
         <v>11.14</v>
       </c>
-      <c r="N19" s="230">
+      <c r="N19" s="232">
         <v>10.82</v>
       </c>
-      <c r="O19" s="225">
+      <c r="O19" s="233">
         <v>9.93</v>
       </c>
       <c r="P19" s="224">
@@ -6661,11 +6661,11 @@
       <c r="R19" s="234">
         <v>2.53</v>
       </c>
-      <c r="S19" s="227">
+      <c r="S19" s="222">
         <v>12.78</v>
       </c>
-      <c r="T19" s="228">
-        <v>27.01</v>
+      <c r="T19" s="225">
+        <v>26.33</v>
       </c>
     </row>
     <row r="20">
@@ -6678,7 +6678,7 @@
       <c r="C20" t="str">
         <v>000890</v>
       </c>
-      <c r="D20" s="235" t="str">
+      <c r="D20" s="246" t="str">
         <v>净买: 1030.64万</v>
       </c>
       <c r="E20">
@@ -6693,41 +6693,41 @@
       <c r="H20">
         <v>-9.72</v>
       </c>
-      <c r="I20" s="236">
+      <c r="I20" s="239">
         <v>-0.31</v>
       </c>
-      <c r="J20" s="237">
+      <c r="J20" s="240">
         <v>-10.31</v>
       </c>
-      <c r="K20" s="241">
+      <c r="K20" s="235">
         <v>-10.15</v>
       </c>
-      <c r="L20" s="243">
+      <c r="L20" s="236">
         <v>-16.92</v>
       </c>
-      <c r="M20" s="238">
+      <c r="M20" s="241">
         <v>-14.77</v>
       </c>
-      <c r="N20" s="239">
+      <c r="N20" s="244">
         <v>-16.15</v>
       </c>
-      <c r="O20" s="244">
+      <c r="O20" s="237">
         <v>-17.38</v>
       </c>
       <c r="P20" s="245">
         <v>-20.31</v>
       </c>
-      <c r="Q20" s="240">
+      <c r="Q20" s="242">
         <v>-20.62</v>
       </c>
-      <c r="R20" s="242">
+      <c r="R20" s="238">
         <v>-22</v>
       </c>
-      <c r="S20" s="246">
+      <c r="S20" s="243">
         <v>-21.69</v>
       </c>
       <c r="T20" s="247">
-        <v>90.92</v>
+        <v>108.46</v>
       </c>
     </row>
     <row r="21">
@@ -6740,7 +6740,7 @@
       <c r="C21" t="str">
         <v>000890</v>
       </c>
-      <c r="D21" s="254" t="str">
+      <c r="D21" s="259" t="str">
         <v>净卖: -1045.40万</v>
       </c>
       <c r="E21">
@@ -6755,41 +6755,41 @@
       <c r="H21">
         <v>-4.94</v>
       </c>
-      <c r="I21" s="249">
+      <c r="I21" s="251">
         <v>-5.36</v>
       </c>
-      <c r="J21" s="250">
+      <c r="J21" s="249">
         <v>-5.19</v>
       </c>
-      <c r="K21" s="259">
+      <c r="K21" s="255">
         <v>-12.34</v>
       </c>
-      <c r="L21" s="253">
+      <c r="L21" s="252">
         <v>-10.06</v>
       </c>
-      <c r="M21" s="255">
+      <c r="M21" s="253">
         <v>-11.53</v>
       </c>
-      <c r="N21" s="251">
+      <c r="N21" s="254">
         <v>-12.82</v>
       </c>
-      <c r="O21" s="260">
+      <c r="O21" s="256">
         <v>-15.91</v>
       </c>
-      <c r="P21" s="248">
+      <c r="P21" s="257">
         <v>-16.23</v>
       </c>
-      <c r="Q21" s="256">
+      <c r="Q21" s="258">
         <v>-17.69</v>
       </c>
-      <c r="R21" s="257">
+      <c r="R21" s="260">
         <v>-17.37</v>
       </c>
-      <c r="S21" s="252">
+      <c r="S21" s="248">
         <v>-16.23</v>
       </c>
-      <c r="T21" s="258">
-        <v>101.46</v>
+      <c r="T21" s="250">
+        <v>119.97</v>
       </c>
     </row>
     <row r="22">
@@ -6802,7 +6802,7 @@
       <c r="C22" t="str">
         <v>300409</v>
       </c>
-      <c r="D22" s="266" t="str">
+      <c r="D22" s="268" t="str">
         <v>净卖: -3259.20万</v>
       </c>
       <c r="E22">
@@ -6817,41 +6817,41 @@
       <c r="H22">
         <v>4.54</v>
       </c>
-      <c r="I22" s="271">
+      <c r="I22" s="272">
         <v>14.8</v>
       </c>
-      <c r="J22" s="272">
+      <c r="J22" s="262">
         <v>31.48</v>
       </c>
-      <c r="K22" s="267">
+      <c r="K22" s="263">
         <v>32.5</v>
       </c>
-      <c r="L22" s="261">
+      <c r="L22" s="265">
         <v>30.84</v>
       </c>
-      <c r="M22" s="264">
+      <c r="M22" s="273">
         <v>23.86</v>
       </c>
-      <c r="N22" s="268">
+      <c r="N22" s="261">
         <v>48.62</v>
       </c>
-      <c r="O22" s="269">
+      <c r="O22" s="264">
         <v>46.11</v>
       </c>
-      <c r="P22" s="273">
+      <c r="P22" s="269">
         <v>41.64</v>
       </c>
-      <c r="Q22" s="262">
+      <c r="Q22" s="270">
         <v>42.15</v>
       </c>
-      <c r="R22" s="265">
+      <c r="R22" s="266">
         <v>36.03</v>
       </c>
-      <c r="S22" s="263">
+      <c r="S22" s="271">
         <v>31.9</v>
       </c>
-      <c r="T22" s="270">
-        <v>13.36</v>
+      <c r="T22" s="267">
+        <v>13.91</v>
       </c>
     </row>
     <row r="23">
@@ -6864,7 +6864,7 @@
       <c r="C23" t="str">
         <v>300409</v>
       </c>
-      <c r="D23" s="278" t="str">
+      <c r="D23" s="274" t="str">
         <v>净卖: -3736.61万</v>
       </c>
       <c r="E23">
@@ -6879,41 +6879,41 @@
       <c r="H23">
         <v>4.22</v>
       </c>
-      <c r="I23" s="279">
+      <c r="I23" s="280">
         <v>9.88</v>
       </c>
-      <c r="J23" s="283">
+      <c r="J23" s="275">
         <v>10.74</v>
       </c>
-      <c r="K23" s="284">
+      <c r="K23" s="276">
         <v>9.35</v>
       </c>
-      <c r="L23" s="275">
+      <c r="L23" s="281">
         <v>3.52</v>
       </c>
-      <c r="M23" s="276">
+      <c r="M23" s="284">
         <v>24.21</v>
       </c>
-      <c r="N23" s="280">
+      <c r="N23" s="285">
         <v>22.11</v>
       </c>
-      <c r="O23" s="281">
+      <c r="O23" s="282">
         <v>18.38</v>
       </c>
       <c r="P23" s="277">
         <v>18.81</v>
       </c>
-      <c r="Q23" s="285">
+      <c r="Q23" s="278">
         <v>13.69</v>
       </c>
       <c r="R23" s="286">
         <v>10.24</v>
       </c>
-      <c r="S23" s="282">
+      <c r="S23" s="283">
         <v>8</v>
       </c>
-      <c r="T23" s="274">
-        <v>-5.26</v>
+      <c r="T23" s="279">
+        <v>-4.8</v>
       </c>
     </row>
     <row r="24">
@@ -6926,7 +6926,7 @@
       <c r="C24" t="str">
         <v>300409</v>
       </c>
-      <c r="D24" s="298" t="str">
+      <c r="D24" s="294" t="str">
         <v>净卖: -2006.10万</v>
       </c>
       <c r="E24">
@@ -6941,41 +6941,41 @@
       <c r="H24">
         <v>1.68</v>
       </c>
-      <c r="I24" s="299">
+      <c r="I24" s="288">
         <v>18</v>
       </c>
-      <c r="J24" s="288">
+      <c r="J24" s="295">
         <v>16.01</v>
       </c>
-      <c r="K24" s="296">
+      <c r="K24" s="291">
         <v>12.46</v>
       </c>
-      <c r="L24" s="297">
+      <c r="L24" s="296">
         <v>12.87</v>
       </c>
-      <c r="M24" s="293">
+      <c r="M24" s="297">
         <v>8</v>
       </c>
-      <c r="N24" s="294">
+      <c r="N24" s="298">
         <v>4.73</v>
       </c>
-      <c r="O24" s="289">
+      <c r="O24" s="299">
         <v>2.6</v>
       </c>
-      <c r="P24" s="290">
+      <c r="P24" s="287">
         <v>1.82</v>
       </c>
-      <c r="Q24" s="291">
+      <c r="Q24" s="289">
         <v>2.36</v>
       </c>
-      <c r="R24" s="292">
+      <c r="R24" s="290">
         <v>8.11</v>
       </c>
-      <c r="S24" s="295">
+      <c r="S24" s="292">
         <v>5.67</v>
       </c>
-      <c r="T24" s="287">
-        <v>-10</v>
+      <c r="T24" s="293">
+        <v>-9.56</v>
       </c>
     </row>
     <row r="25">
@@ -7037,40 +7037,40 @@
       <c r="F26" t="str"/>
       <c r="G26" t="str"/>
       <c r="H26" t="str"/>
-      <c r="I26" s="304">
+      <c r="I26" s="308">
         <v>52.17</v>
       </c>
-      <c r="J26" s="307">
+      <c r="J26" s="305">
         <v>52.17</v>
       </c>
-      <c r="K26" s="305">
+      <c r="K26" s="306">
         <v>52.17</v>
       </c>
-      <c r="L26" s="308">
+      <c r="L26" s="302">
         <v>47.83</v>
       </c>
       <c r="M26" s="310">
         <v>43.48</v>
       </c>
-      <c r="N26" s="300">
+      <c r="N26" s="303">
         <v>39.13</v>
       </c>
-      <c r="O26" s="301">
+      <c r="O26" s="307">
         <v>34.78</v>
       </c>
-      <c r="P26" s="302">
+      <c r="P26" s="309">
         <v>39.13</v>
       </c>
       <c r="Q26" s="311">
         <v>39.13</v>
       </c>
-      <c r="R26" s="309">
+      <c r="R26" s="304">
         <v>39.13</v>
       </c>
-      <c r="S26" s="306">
+      <c r="S26" s="300">
         <v>39.13</v>
       </c>
-      <c r="T26" s="303">
+      <c r="T26" s="301">
         <v>52.17</v>
       </c>
     </row>
@@ -7085,41 +7085,41 @@
       <c r="F27" t="str"/>
       <c r="G27" t="str"/>
       <c r="H27" t="str"/>
-      <c r="I27" s="323">
+      <c r="I27" s="314">
         <v>3.46</v>
       </c>
-      <c r="J27" s="315">
+      <c r="J27" s="321">
         <v>2.89</v>
       </c>
-      <c r="K27" s="316">
+      <c r="K27" s="315">
         <v>0.67</v>
       </c>
-      <c r="L27" s="312">
+      <c r="L27" s="318">
         <v>-0.46</v>
       </c>
-      <c r="M27" s="319">
+      <c r="M27" s="322">
         <v>-1.36</v>
       </c>
-      <c r="N27" s="313">
+      <c r="N27" s="319">
         <v>-0.02</v>
       </c>
-      <c r="O27" s="317">
+      <c r="O27" s="323">
         <v>-1.62</v>
       </c>
       <c r="P27" s="320">
         <v>-2.08</v>
       </c>
-      <c r="Q27" s="318">
+      <c r="Q27" s="312">
         <v>-2.45</v>
       </c>
-      <c r="R27" s="314">
+      <c r="R27" s="317">
         <v>-2.62</v>
       </c>
-      <c r="S27" s="321">
+      <c r="S27" s="313">
         <v>-1.7</v>
       </c>
-      <c r="T27" s="322">
-        <v>16.19</v>
+      <c r="T27" s="316">
+        <v>19.51</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/王海祥/index.xlsx
+++ b/youzi/王海祥/index.xlsx
@@ -63,12 +63,84 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFCC2E3D"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -81,37 +153,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFE3626E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,49 +189,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD43141"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF57BA6E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47B460"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF62BE77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -183,7 +363,319 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3A49"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3747"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCEEBD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -195,25 +687,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BABF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -225,55 +873,967 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF47B460"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF5F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC380"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3B4A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70C483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6707C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -285,835 +1845,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF81CB92"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF57BA6E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF62BE77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3A49"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCEEBD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3747"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF5F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0EBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0EBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF72C585"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208838"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCFEFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF50B768"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1125,853 +1923,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF48B460"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF6CC380"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3B4A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6707C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0EBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208838"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF72C585"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF48B460"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCFEFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC380"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF50B768"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -5577,41 +5577,41 @@
       <c r="H2">
         <v>3.37</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="12">
         <v>6.43</v>
       </c>
-      <c r="J2" s="10">
+      <c r="J2" s="9">
         <v>17.1</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="4">
         <v>11.56</v>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="13">
         <v>22.72</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="1">
         <v>30.54</v>
       </c>
-      <c r="N2" s="8">
+      <c r="N2" s="7">
         <v>43.57</v>
       </c>
-      <c r="O2" s="13">
+      <c r="O2" s="10">
         <v>42.1</v>
       </c>
-      <c r="P2" s="3">
+      <c r="P2" s="2">
         <v>40.15</v>
       </c>
-      <c r="Q2" s="9">
+      <c r="Q2" s="8">
         <v>33.31</v>
       </c>
-      <c r="R2" s="4">
+      <c r="R2" s="5">
         <v>34.45</v>
       </c>
-      <c r="S2" s="1">
+      <c r="S2" s="11">
         <v>40.8</v>
       </c>
-      <c r="T2" s="2">
-        <v>19.95</v>
+      <c r="T2" s="3">
+        <v>18.08</v>
       </c>
     </row>
     <row r="3">
@@ -5624,7 +5624,7 @@
       <c r="C3" t="str">
         <v>601279</v>
       </c>
-      <c r="D3" s="24" t="str">
+      <c r="D3" s="18" t="str">
         <v>净卖: -85.25万</v>
       </c>
       <c r="E3">
@@ -5639,41 +5639,41 @@
       <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="19">
         <v>10.15</v>
       </c>
-      <c r="J3" s="26">
+      <c r="J3" s="23">
         <v>5.97</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="24">
         <v>4.48</v>
       </c>
-      <c r="L3" s="15">
+      <c r="L3" s="20">
         <v>3.88</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="21">
         <v>4.18</v>
       </c>
-      <c r="N3" s="17">
+      <c r="N3" s="25">
         <v>3.88</v>
       </c>
-      <c r="O3" s="18">
+      <c r="O3" s="26">
         <v>5.67</v>
       </c>
-      <c r="P3" s="19">
+      <c r="P3" s="16">
         <v>5.07</v>
       </c>
-      <c r="Q3" s="22">
+      <c r="Q3" s="14">
         <v>4.78</v>
       </c>
-      <c r="R3" s="20">
+      <c r="R3" s="22">
         <v>2.09</v>
       </c>
-      <c r="S3" s="21">
+      <c r="S3" s="15">
         <v>4.18</v>
       </c>
-      <c r="T3" s="23">
-        <v>16.72</v>
+      <c r="T3" s="17">
+        <v>15.82</v>
       </c>
     </row>
     <row r="4">
@@ -5686,7 +5686,7 @@
       <c r="C4" t="str">
         <v>003020</v>
       </c>
-      <c r="D4" s="31" t="str">
+      <c r="D4" s="27" t="str">
         <v>净买: 1240.36万</v>
       </c>
       <c r="E4">
@@ -5701,41 +5701,41 @@
       <c r="H4">
         <v>-3.75</v>
       </c>
-      <c r="I4" s="36">
+      <c r="I4" s="35">
         <v>-6.49</v>
       </c>
       <c r="J4" s="37">
         <v>-15.84</v>
       </c>
-      <c r="K4" s="32">
+      <c r="K4" s="31">
         <v>-23.08</v>
       </c>
-      <c r="L4" s="28">
+      <c r="L4" s="32">
         <v>-24.06</v>
       </c>
-      <c r="M4" s="29">
+      <c r="M4" s="36">
         <v>-21.79</v>
       </c>
-      <c r="N4" s="34">
+      <c r="N4" s="28">
         <v>-20.71</v>
       </c>
-      <c r="O4" s="38">
+      <c r="O4" s="33">
         <v>-22.89</v>
       </c>
-      <c r="P4" s="30">
+      <c r="P4" s="29">
         <v>-24.61</v>
       </c>
-      <c r="Q4" s="39">
+      <c r="Q4" s="38">
         <v>-23.38</v>
       </c>
-      <c r="R4" s="35">
+      <c r="R4" s="39">
         <v>-24.35</v>
       </c>
-      <c r="S4" s="33">
+      <c r="S4" s="30">
         <v>-22.4</v>
       </c>
-      <c r="T4" s="27">
-        <v>-22.31</v>
+      <c r="T4" s="34">
+        <v>-23.41</v>
       </c>
     </row>
     <row r="5">
@@ -5748,7 +5748,7 @@
       <c r="C5" t="str">
         <v>003020</v>
       </c>
-      <c r="D5" s="46" t="str">
+      <c r="D5" s="48" t="str">
         <v>净买: 1925.03万</v>
       </c>
       <c r="E5">
@@ -5763,41 +5763,41 @@
       <c r="H5">
         <v>-4.9</v>
       </c>
-      <c r="I5" s="47">
+      <c r="I5" s="40">
         <v>-3.89</v>
       </c>
-      <c r="J5" s="51">
+      <c r="J5" s="44">
         <v>-5.11</v>
       </c>
-      <c r="K5" s="43">
+      <c r="K5" s="45">
         <v>-2.27</v>
       </c>
-      <c r="L5" s="48">
+      <c r="L5" s="41">
         <v>-0.93</v>
       </c>
-      <c r="M5" s="50">
+      <c r="M5" s="49">
         <v>-3.65</v>
       </c>
-      <c r="N5" s="52">
+      <c r="N5" s="42">
         <v>-5.8</v>
       </c>
-      <c r="O5" s="40">
+      <c r="O5" s="43">
         <v>-4.26</v>
       </c>
-      <c r="P5" s="41">
+      <c r="P5" s="46">
         <v>-5.48</v>
       </c>
-      <c r="Q5" s="49">
+      <c r="Q5" s="47">
         <v>-3.04</v>
       </c>
-      <c r="R5" s="42">
+      <c r="R5" s="50">
         <v>-2.07</v>
       </c>
-      <c r="S5" s="44">
+      <c r="S5" s="51">
         <v>-0.97</v>
       </c>
-      <c r="T5" s="45">
-        <v>-2.92</v>
+      <c r="T5" s="52">
+        <v>-4.3</v>
       </c>
     </row>
     <row r="6">
@@ -5810,7 +5810,7 @@
       <c r="C6" t="str">
         <v>603607</v>
       </c>
-      <c r="D6" s="61" t="str">
+      <c r="D6" s="54" t="str">
         <v>净卖: -1819.82万</v>
       </c>
       <c r="E6">
@@ -5825,41 +5825,41 @@
       <c r="H6">
         <v>9.92</v>
       </c>
-      <c r="I6" s="53">
+      <c r="I6" s="55">
         <v>0.06</v>
       </c>
-      <c r="J6" s="57">
+      <c r="J6" s="61">
         <v>4.62</v>
       </c>
-      <c r="K6" s="54">
+      <c r="K6" s="56">
         <v>4.87</v>
       </c>
-      <c r="L6" s="63">
+      <c r="L6" s="57">
         <v>-5.62</v>
       </c>
-      <c r="M6" s="64">
+      <c r="M6" s="62">
         <v>-15.05</v>
       </c>
       <c r="N6" s="58">
         <v>-13.34</v>
       </c>
-      <c r="O6" s="59">
+      <c r="O6" s="53">
         <v>-18.49</v>
       </c>
-      <c r="P6" s="62">
+      <c r="P6" s="63">
         <v>-19.11</v>
       </c>
-      <c r="Q6" s="65">
+      <c r="Q6" s="64">
         <v>-16.36</v>
       </c>
-      <c r="R6" s="60">
+      <c r="R6" s="59">
         <v>-15.71</v>
       </c>
-      <c r="S6" s="55">
+      <c r="S6" s="60">
         <v>-10.68</v>
       </c>
-      <c r="T6" s="56">
-        <v>-26.58</v>
+      <c r="T6" s="65">
+        <v>-26.48</v>
       </c>
     </row>
     <row r="7">
@@ -5872,7 +5872,7 @@
       <c r="C7" t="str">
         <v>603607</v>
       </c>
-      <c r="D7" s="70" t="str">
+      <c r="D7" s="73" t="str">
         <v>净卖: -2523.15万</v>
       </c>
       <c r="E7">
@@ -5887,41 +5887,41 @@
       <c r="H7">
         <v>1.49</v>
       </c>
-      <c r="I7" s="75">
+      <c r="I7" s="77">
         <v>-1.24</v>
       </c>
-      <c r="J7" s="78">
+      <c r="J7" s="74">
         <v>-11.12</v>
       </c>
-      <c r="K7" s="71">
+      <c r="K7" s="67">
         <v>-20</v>
       </c>
-      <c r="L7" s="72">
+      <c r="L7" s="75">
         <v>-18.38</v>
       </c>
-      <c r="M7" s="76">
+      <c r="M7" s="68">
         <v>-23.24</v>
       </c>
-      <c r="N7" s="66">
+      <c r="N7" s="69">
         <v>-23.82</v>
       </c>
-      <c r="O7" s="67">
+      <c r="O7" s="70">
         <v>-21.24</v>
       </c>
-      <c r="P7" s="69">
+      <c r="P7" s="72">
         <v>-20.62</v>
       </c>
-      <c r="Q7" s="68">
+      <c r="Q7" s="71">
         <v>-15.88</v>
       </c>
-      <c r="R7" s="77">
+      <c r="R7" s="76">
         <v>-18.09</v>
       </c>
-      <c r="S7" s="73">
+      <c r="S7" s="78">
         <v>-25.41</v>
       </c>
-      <c r="T7" s="74">
-        <v>-30.85</v>
+      <c r="T7" s="66">
+        <v>-30.76</v>
       </c>
     </row>
     <row r="8">
@@ -5934,7 +5934,7 @@
       <c r="C8" t="str">
         <v>603823</v>
       </c>
-      <c r="D8" s="82" t="str">
+      <c r="D8" s="87" t="str">
         <v>净卖: -577.99万</v>
       </c>
       <c r="E8">
@@ -5949,41 +5949,41 @@
       <c r="H8">
         <v>-1.03</v>
       </c>
-      <c r="I8" s="83">
+      <c r="I8" s="82">
         <v>11.19</v>
       </c>
-      <c r="J8" s="79">
+      <c r="J8" s="90">
         <v>10.49</v>
       </c>
-      <c r="K8" s="84">
+      <c r="K8" s="91">
         <v>7.03</v>
       </c>
-      <c r="L8" s="89">
+      <c r="L8" s="85">
         <v>2.34</v>
       </c>
-      <c r="M8" s="90">
+      <c r="M8" s="83">
         <v>4.94</v>
       </c>
-      <c r="N8" s="85">
+      <c r="N8" s="88">
         <v>-1.13</v>
       </c>
-      <c r="O8" s="88">
+      <c r="O8" s="89">
         <v>-2.6</v>
       </c>
-      <c r="P8" s="86">
+      <c r="P8" s="79">
         <v>7.11</v>
       </c>
-      <c r="Q8" s="80">
+      <c r="Q8" s="86">
         <v>11.71</v>
       </c>
-      <c r="R8" s="87">
+      <c r="R8" s="84">
         <v>17.52</v>
       </c>
-      <c r="S8" s="81">
+      <c r="S8" s="80">
         <v>17.43</v>
       </c>
-      <c r="T8" s="91">
-        <v>40.24</v>
+      <c r="T8" s="81">
+        <v>41.63</v>
       </c>
     </row>
     <row r="9">
@@ -5996,7 +5996,7 @@
       <c r="C9" t="str">
         <v>601279</v>
       </c>
-      <c r="D9" s="92" t="str">
+      <c r="D9" s="100" t="str">
         <v>净卖: -624.00万</v>
       </c>
       <c r="E9">
@@ -6011,41 +6011,41 @@
       <c r="H9">
         <v>10.09</v>
       </c>
-      <c r="I9" s="99">
+      <c r="I9" s="101">
         <v>0</v>
       </c>
-      <c r="J9" s="93">
+      <c r="J9" s="95">
         <v>-8.75</v>
       </c>
-      <c r="K9" s="100">
+      <c r="K9" s="102">
         <v>-17.92</v>
       </c>
-      <c r="L9" s="94">
+      <c r="L9" s="96">
         <v>-22.08</v>
       </c>
-      <c r="M9" s="102">
+      <c r="M9" s="98">
         <v>-23.12</v>
       </c>
-      <c r="N9" s="95">
+      <c r="N9" s="97">
         <v>-21.88</v>
       </c>
-      <c r="O9" s="96">
+      <c r="O9" s="103">
         <v>-22.29</v>
       </c>
-      <c r="P9" s="103">
+      <c r="P9" s="104">
         <v>-21.25</v>
       </c>
-      <c r="Q9" s="101">
+      <c r="Q9" s="93">
         <v>-20.62</v>
       </c>
-      <c r="R9" s="97">
+      <c r="R9" s="92">
         <v>-21.25</v>
       </c>
-      <c r="S9" s="98">
+      <c r="S9" s="99">
         <v>-19.37</v>
       </c>
-      <c r="T9" s="104">
-        <v>-18.54</v>
+      <c r="T9" s="94">
+        <v>-19.17</v>
       </c>
     </row>
     <row r="10">
@@ -6058,7 +6058,7 @@
       <c r="C10" t="str">
         <v>600980</v>
       </c>
-      <c r="D10" s="108" t="str">
+      <c r="D10" s="107" t="str">
         <v>净卖: -1981.34万</v>
       </c>
       <c r="E10">
@@ -6073,22 +6073,22 @@
       <c r="H10">
         <v>-0.58</v>
       </c>
-      <c r="I10" s="109">
+      <c r="I10" s="108">
         <v>5.96</v>
       </c>
-      <c r="J10" s="106">
+      <c r="J10" s="109">
         <v>-4.64</v>
       </c>
-      <c r="K10" s="112">
+      <c r="K10" s="113">
         <v>-14.14</v>
       </c>
-      <c r="L10" s="113">
+      <c r="L10" s="114">
         <v>-19.62</v>
       </c>
       <c r="M10" s="116">
         <v>-20.09</v>
       </c>
-      <c r="N10" s="114">
+      <c r="N10" s="110">
         <v>-18.71</v>
       </c>
       <c r="O10" s="117">
@@ -6097,17 +6097,17 @@
       <c r="P10" s="105">
         <v>-19.15</v>
       </c>
-      <c r="Q10" s="110">
+      <c r="Q10" s="111">
         <v>-20.42</v>
       </c>
-      <c r="R10" s="107">
+      <c r="R10" s="115">
         <v>-17.25</v>
       </c>
-      <c r="S10" s="111">
+      <c r="S10" s="106">
         <v>-11.14</v>
       </c>
-      <c r="T10" s="115">
-        <v>-15.24</v>
+      <c r="T10" s="112">
+        <v>-15.67</v>
       </c>
     </row>
     <row r="11">
@@ -6120,7 +6120,7 @@
       <c r="C11" t="str">
         <v>600330</v>
       </c>
-      <c r="D11" s="130" t="str">
+      <c r="D11" s="129" t="str">
         <v>净卖: -6191.34万</v>
       </c>
       <c r="E11">
@@ -6135,41 +6135,41 @@
       <c r="H11">
         <v>10</v>
       </c>
-      <c r="I11" s="118">
+      <c r="I11" s="130">
         <v>-5.66</v>
       </c>
-      <c r="J11" s="126">
+      <c r="J11" s="127">
         <v>3.77</v>
       </c>
-      <c r="K11" s="122">
+      <c r="K11" s="124">
         <v>-0.51</v>
       </c>
-      <c r="L11" s="123">
+      <c r="L11" s="128">
         <v>-7.72</v>
       </c>
-      <c r="M11" s="124">
+      <c r="M11" s="122">
         <v>-10.89</v>
       </c>
-      <c r="N11" s="119">
+      <c r="N11" s="118">
         <v>-6.43</v>
       </c>
-      <c r="O11" s="127">
+      <c r="O11" s="119">
         <v>-8.23</v>
       </c>
       <c r="P11" s="120">
         <v>-3.77</v>
       </c>
-      <c r="Q11" s="125">
+      <c r="Q11" s="123">
         <v>-2.23</v>
       </c>
-      <c r="R11" s="128">
+      <c r="R11" s="125">
         <v>-1.63</v>
       </c>
-      <c r="S11" s="129">
+      <c r="S11" s="121">
         <v>-0.77</v>
       </c>
-      <c r="T11" s="121">
-        <v>104.97</v>
+      <c r="T11" s="126">
+        <v>101.72</v>
       </c>
     </row>
     <row r="12">
@@ -6197,41 +6197,41 @@
       <c r="H12">
         <v>2.91</v>
       </c>
-      <c r="I12" s="140">
+      <c r="I12" s="131">
         <v>6.98</v>
       </c>
-      <c r="J12" s="141">
+      <c r="J12" s="133">
         <v>10.75</v>
       </c>
-      <c r="K12" s="131">
+      <c r="K12" s="134">
         <v>21.89</v>
       </c>
-      <c r="L12" s="142">
+      <c r="L12" s="135">
         <v>34.15</v>
       </c>
       <c r="M12" s="132">
         <v>34.15</v>
       </c>
-      <c r="N12" s="143">
+      <c r="N12" s="140">
         <v>30.38</v>
       </c>
-      <c r="O12" s="133">
+      <c r="O12" s="141">
         <v>28.49</v>
       </c>
-      <c r="P12" s="135">
+      <c r="P12" s="142">
         <v>23.58</v>
       </c>
-      <c r="Q12" s="136">
+      <c r="Q12" s="137">
         <v>17.74</v>
       </c>
-      <c r="R12" s="137">
+      <c r="R12" s="136">
         <v>29.43</v>
       </c>
-      <c r="S12" s="138">
+      <c r="S12" s="143">
         <v>33.77</v>
       </c>
-      <c r="T12" s="134">
-        <v>2.64</v>
+      <c r="T12" s="138">
+        <v>1.7</v>
       </c>
     </row>
     <row r="13">
@@ -6244,7 +6244,7 @@
       <c r="C13" t="str">
         <v>002488</v>
       </c>
-      <c r="D13" s="152" t="str">
+      <c r="D13" s="149" t="str">
         <v>净卖: -1403.24万</v>
       </c>
       <c r="E13">
@@ -6259,41 +6259,41 @@
       <c r="H13">
         <v>-0.57</v>
       </c>
-      <c r="I13" s="144">
+      <c r="I13" s="153">
         <v>-9.51</v>
       </c>
-      <c r="J13" s="153">
+      <c r="J13" s="154">
         <v>-0.49</v>
       </c>
-      <c r="K13" s="154">
+      <c r="K13" s="146">
         <v>-8.7</v>
       </c>
-      <c r="L13" s="148">
+      <c r="L13" s="150">
         <v>-14.88</v>
       </c>
-      <c r="M13" s="149">
+      <c r="M13" s="151">
         <v>-14.96</v>
       </c>
-      <c r="N13" s="150">
+      <c r="N13" s="155">
         <v>-18.86</v>
       </c>
-      <c r="O13" s="145">
+      <c r="O13" s="156">
         <v>-19.92</v>
       </c>
-      <c r="P13" s="146">
+      <c r="P13" s="147">
         <v>-18.54</v>
       </c>
-      <c r="Q13" s="151">
+      <c r="Q13" s="148">
         <v>-17.24</v>
       </c>
-      <c r="R13" s="155">
+      <c r="R13" s="144">
         <v>-15.93</v>
       </c>
-      <c r="S13" s="156">
+      <c r="S13" s="145">
         <v>-17.15</v>
       </c>
-      <c r="T13" s="147">
-        <v>0.08</v>
+      <c r="T13" s="152">
+        <v>-7.07</v>
       </c>
     </row>
     <row r="14">
@@ -6306,7 +6306,7 @@
       <c r="C14" t="str">
         <v>301246</v>
       </c>
-      <c r="D14" s="165" t="str">
+      <c r="D14" s="164" t="str">
         <v>净卖: -752.38万</v>
       </c>
       <c r="E14">
@@ -6321,10 +6321,10 @@
       <c r="H14">
         <v>-2.99</v>
       </c>
-      <c r="I14" s="157">
+      <c r="I14" s="165">
         <v>23.71</v>
       </c>
-      <c r="J14" s="167">
+      <c r="J14" s="168">
         <v>15.87</v>
       </c>
       <c r="K14" s="158">
@@ -6336,26 +6336,26 @@
       <c r="M14" s="160">
         <v>16.22</v>
       </c>
-      <c r="N14" s="168">
+      <c r="N14" s="162">
         <v>18.95</v>
       </c>
-      <c r="O14" s="163">
+      <c r="O14" s="166">
         <v>19.79</v>
       </c>
       <c r="P14" s="169">
         <v>17.41</v>
       </c>
-      <c r="Q14" s="164">
+      <c r="Q14" s="167">
         <v>19.79</v>
       </c>
-      <c r="R14" s="166">
+      <c r="R14" s="157">
         <v>15.38</v>
       </c>
       <c r="S14" s="161">
         <v>18.25</v>
       </c>
-      <c r="T14" s="162">
-        <v>70.42</v>
+      <c r="T14" s="163">
+        <v>68.25</v>
       </c>
     </row>
     <row r="15">
@@ -6368,7 +6368,7 @@
       <c r="C15" t="str">
         <v>002198</v>
       </c>
-      <c r="D15" s="182" t="str">
+      <c r="D15" s="174" t="str">
         <v>净买: 1396.06万</v>
       </c>
       <c r="E15">
@@ -6383,41 +6383,41 @@
       <c r="H15">
         <v>9.79</v>
       </c>
-      <c r="I15" s="170">
+      <c r="I15" s="178">
         <v>0.24</v>
       </c>
-      <c r="J15" s="171">
+      <c r="J15" s="175">
         <v>-9.75</v>
       </c>
-      <c r="K15" s="177">
+      <c r="K15" s="179">
         <v>-16.17</v>
       </c>
-      <c r="L15" s="178">
+      <c r="L15" s="180">
         <v>-16.77</v>
       </c>
-      <c r="M15" s="172">
+      <c r="M15" s="176">
         <v>-20.33</v>
       </c>
-      <c r="N15" s="175">
+      <c r="N15" s="177">
         <v>-17.72</v>
       </c>
-      <c r="O15" s="173">
+      <c r="O15" s="181">
         <v>-12.72</v>
       </c>
-      <c r="P15" s="174">
+      <c r="P15" s="182">
         <v>-11.18</v>
       </c>
-      <c r="Q15" s="179">
+      <c r="Q15" s="170">
         <v>-10.7</v>
       </c>
-      <c r="R15" s="180">
+      <c r="R15" s="171">
         <v>-10.23</v>
       </c>
-      <c r="S15" s="176">
+      <c r="S15" s="172">
         <v>-11.77</v>
       </c>
-      <c r="T15" s="181">
-        <v>-6.54</v>
+      <c r="T15" s="173">
+        <v>-9.39</v>
       </c>
     </row>
     <row r="16">
@@ -6430,7 +6430,7 @@
       <c r="C16" t="str">
         <v>002114</v>
       </c>
-      <c r="D16" s="193" t="str">
+      <c r="D16" s="190" t="str">
         <v>净卖: -121.61万</v>
       </c>
       <c r="E16">
@@ -6445,41 +6445,41 @@
       <c r="H16">
         <v>9.95</v>
       </c>
-      <c r="I16" s="194">
+      <c r="I16" s="186">
         <v>0</v>
       </c>
-      <c r="J16" s="188">
+      <c r="J16" s="194">
         <v>-9.98</v>
       </c>
-      <c r="K16" s="189">
+      <c r="K16" s="187">
         <v>-15.64</v>
       </c>
       <c r="L16" s="195">
         <v>-7.2</v>
       </c>
-      <c r="M16" s="184">
+      <c r="M16" s="183">
         <v>-9.16</v>
       </c>
-      <c r="N16" s="185">
+      <c r="N16" s="189">
         <v>-5.66</v>
       </c>
       <c r="O16" s="191">
         <v>-7.3</v>
       </c>
-      <c r="P16" s="183">
+      <c r="P16" s="188">
         <v>-3.4</v>
       </c>
-      <c r="Q16" s="186">
+      <c r="Q16" s="184">
         <v>-6.17</v>
       </c>
-      <c r="R16" s="190">
+      <c r="R16" s="192">
         <v>-11.73</v>
       </c>
-      <c r="S16" s="187">
+      <c r="S16" s="193">
         <v>-10.7</v>
       </c>
-      <c r="T16" s="192">
-        <v>-5.56</v>
+      <c r="T16" s="185">
+        <v>-7.1</v>
       </c>
     </row>
     <row r="17">
@@ -6492,7 +6492,7 @@
       <c r="C17" t="str">
         <v>603815</v>
       </c>
-      <c r="D17" s="199" t="str">
+      <c r="D17" s="201" t="str">
         <v>净卖: -1097.64万</v>
       </c>
       <c r="E17">
@@ -6507,41 +6507,41 @@
       <c r="H17">
         <v>0.09</v>
       </c>
-      <c r="I17" s="204">
+      <c r="I17" s="202">
         <v>9.95</v>
       </c>
-      <c r="J17" s="196">
+      <c r="J17" s="203">
         <v>12.93</v>
       </c>
-      <c r="K17" s="205">
+      <c r="K17" s="208">
         <v>12.57</v>
       </c>
-      <c r="L17" s="206">
+      <c r="L17" s="204">
         <v>17.45</v>
       </c>
-      <c r="M17" s="200">
+      <c r="M17" s="205">
         <v>9.76</v>
       </c>
-      <c r="N17" s="201">
+      <c r="N17" s="206">
         <v>9.22</v>
       </c>
-      <c r="O17" s="202">
+      <c r="O17" s="207">
         <v>-1.72</v>
       </c>
-      <c r="P17" s="197">
+      <c r="P17" s="196">
         <v>-11.57</v>
       </c>
-      <c r="Q17" s="203">
+      <c r="Q17" s="197">
         <v>-15.01</v>
       </c>
-      <c r="R17" s="207">
+      <c r="R17" s="198">
         <v>-21.52</v>
       </c>
-      <c r="S17" s="208">
+      <c r="S17" s="199">
         <v>-23.87</v>
       </c>
-      <c r="T17" s="198">
-        <v>-41.86</v>
+      <c r="T17" s="200">
+        <v>-36.08</v>
       </c>
     </row>
     <row r="18">
@@ -6554,7 +6554,7 @@
       <c r="C18" t="str">
         <v>000890</v>
       </c>
-      <c r="D18" s="212" t="str">
+      <c r="D18" s="211" t="str">
         <v>净买: 1092.74万</v>
       </c>
       <c r="E18">
@@ -6569,41 +6569,41 @@
       <c r="H18">
         <v>10.05</v>
       </c>
-      <c r="I18" s="219">
+      <c r="I18" s="215">
         <v>0</v>
       </c>
-      <c r="J18" s="220">
+      <c r="J18" s="221">
         <v>10.06</v>
       </c>
-      <c r="K18" s="213">
+      <c r="K18" s="209">
         <v>11.46</v>
       </c>
-      <c r="L18" s="216">
+      <c r="L18" s="218">
         <v>0.31</v>
       </c>
-      <c r="M18" s="221">
+      <c r="M18" s="219">
         <v>-9.75</v>
       </c>
-      <c r="N18" s="209">
+      <c r="N18" s="212">
         <v>-9.6</v>
       </c>
-      <c r="O18" s="214">
+      <c r="O18" s="216">
         <v>-16.41</v>
       </c>
-      <c r="P18" s="215">
+      <c r="P18" s="213">
         <v>-14.24</v>
       </c>
-      <c r="Q18" s="210">
+      <c r="Q18" s="214">
         <v>-15.63</v>
       </c>
-      <c r="R18" s="211">
+      <c r="R18" s="217">
         <v>-16.87</v>
       </c>
-      <c r="S18" s="217">
+      <c r="S18" s="220">
         <v>-19.81</v>
       </c>
-      <c r="T18" s="218">
-        <v>109.75</v>
+      <c r="T18" s="210">
+        <v>125.85</v>
       </c>
     </row>
     <row r="19">
@@ -6616,7 +6616,7 @@
       <c r="C19" t="str">
         <v>603067</v>
       </c>
-      <c r="D19" s="228" t="str">
+      <c r="D19" s="230" t="str">
         <v>净买: 1179.50万</v>
       </c>
       <c r="E19">
@@ -6631,41 +6631,41 @@
       <c r="H19">
         <v>-3.07</v>
       </c>
-      <c r="I19" s="229">
+      <c r="I19" s="224">
         <v>-5.37</v>
       </c>
-      <c r="J19" s="230">
+      <c r="J19" s="231">
         <v>-2.17</v>
       </c>
-      <c r="K19" s="231">
+      <c r="K19" s="228">
         <v>6.55</v>
       </c>
-      <c r="L19" s="223">
+      <c r="L19" s="229">
         <v>4.84</v>
       </c>
-      <c r="M19" s="227">
+      <c r="M19" s="222">
         <v>11.14</v>
       </c>
-      <c r="N19" s="232">
+      <c r="N19" s="223">
         <v>10.82</v>
       </c>
-      <c r="O19" s="233">
+      <c r="O19" s="225">
         <v>9.93</v>
       </c>
-      <c r="P19" s="224">
+      <c r="P19" s="232">
         <v>6.01</v>
       </c>
-      <c r="Q19" s="226">
+      <c r="Q19" s="233">
         <v>3.17</v>
       </c>
-      <c r="R19" s="234">
+      <c r="R19" s="226">
         <v>2.53</v>
       </c>
-      <c r="S19" s="222">
+      <c r="S19" s="227">
         <v>12.78</v>
       </c>
-      <c r="T19" s="225">
-        <v>26.33</v>
+      <c r="T19" s="234">
+        <v>32.74</v>
       </c>
     </row>
     <row r="20">
@@ -6678,7 +6678,7 @@
       <c r="C20" t="str">
         <v>000890</v>
       </c>
-      <c r="D20" s="246" t="str">
+      <c r="D20" s="245" t="str">
         <v>净买: 1030.64万</v>
       </c>
       <c r="E20">
@@ -6693,41 +6693,41 @@
       <c r="H20">
         <v>-9.72</v>
       </c>
-      <c r="I20" s="239">
+      <c r="I20" s="237">
         <v>-0.31</v>
       </c>
-      <c r="J20" s="240">
+      <c r="J20" s="247">
         <v>-10.31</v>
       </c>
-      <c r="K20" s="235">
+      <c r="K20" s="238">
         <v>-10.15</v>
       </c>
-      <c r="L20" s="236">
+      <c r="L20" s="243">
         <v>-16.92</v>
       </c>
-      <c r="M20" s="241">
+      <c r="M20" s="239">
         <v>-14.77</v>
       </c>
-      <c r="N20" s="244">
+      <c r="N20" s="240">
         <v>-16.15</v>
       </c>
-      <c r="O20" s="237">
+      <c r="O20" s="246">
         <v>-17.38</v>
       </c>
-      <c r="P20" s="245">
+      <c r="P20" s="241">
         <v>-20.31</v>
       </c>
-      <c r="Q20" s="242">
+      <c r="Q20" s="235">
         <v>-20.62</v>
       </c>
-      <c r="R20" s="238">
+      <c r="R20" s="242">
         <v>-22</v>
       </c>
-      <c r="S20" s="243">
+      <c r="S20" s="236">
         <v>-21.69</v>
       </c>
-      <c r="T20" s="247">
-        <v>108.46</v>
+      <c r="T20" s="244">
+        <v>124.46</v>
       </c>
     </row>
     <row r="21">
@@ -6740,7 +6740,7 @@
       <c r="C21" t="str">
         <v>000890</v>
       </c>
-      <c r="D21" s="259" t="str">
+      <c r="D21" s="256" t="str">
         <v>净卖: -1045.40万</v>
       </c>
       <c r="E21">
@@ -6755,41 +6755,41 @@
       <c r="H21">
         <v>-4.94</v>
       </c>
-      <c r="I21" s="251">
+      <c r="I21" s="260">
         <v>-5.36</v>
       </c>
-      <c r="J21" s="249">
+      <c r="J21" s="257">
         <v>-5.19</v>
       </c>
-      <c r="K21" s="255">
+      <c r="K21" s="258">
         <v>-12.34</v>
       </c>
-      <c r="L21" s="252">
+      <c r="L21" s="259">
         <v>-10.06</v>
       </c>
-      <c r="M21" s="253">
+      <c r="M21" s="248">
         <v>-11.53</v>
       </c>
-      <c r="N21" s="254">
+      <c r="N21" s="252">
         <v>-12.82</v>
       </c>
-      <c r="O21" s="256">
+      <c r="O21" s="253">
         <v>-15.91</v>
       </c>
-      <c r="P21" s="257">
+      <c r="P21" s="254">
         <v>-16.23</v>
       </c>
-      <c r="Q21" s="258">
+      <c r="Q21" s="249">
         <v>-17.69</v>
       </c>
-      <c r="R21" s="260">
+      <c r="R21" s="255">
         <v>-17.37</v>
       </c>
-      <c r="S21" s="248">
+      <c r="S21" s="250">
         <v>-16.23</v>
       </c>
-      <c r="T21" s="250">
-        <v>119.97</v>
+      <c r="T21" s="251">
+        <v>136.85</v>
       </c>
     </row>
     <row r="22">
@@ -6817,41 +6817,41 @@
       <c r="H22">
         <v>4.54</v>
       </c>
-      <c r="I22" s="272">
+      <c r="I22" s="264">
         <v>14.8</v>
       </c>
-      <c r="J22" s="262">
+      <c r="J22" s="269">
         <v>31.48</v>
       </c>
-      <c r="K22" s="263">
+      <c r="K22" s="273">
         <v>32.5</v>
       </c>
-      <c r="L22" s="265">
+      <c r="L22" s="262">
         <v>30.84</v>
       </c>
-      <c r="M22" s="273">
+      <c r="M22" s="270">
         <v>23.86</v>
       </c>
-      <c r="N22" s="261">
+      <c r="N22" s="271">
         <v>48.62</v>
       </c>
-      <c r="O22" s="264">
+      <c r="O22" s="263">
         <v>46.11</v>
       </c>
-      <c r="P22" s="269">
+      <c r="P22" s="272">
         <v>41.64</v>
       </c>
-      <c r="Q22" s="270">
+      <c r="Q22" s="265">
         <v>42.15</v>
       </c>
       <c r="R22" s="266">
         <v>36.03</v>
       </c>
-      <c r="S22" s="271">
+      <c r="S22" s="261">
         <v>31.9</v>
       </c>
       <c r="T22" s="267">
-        <v>13.91</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="23">
@@ -6864,7 +6864,7 @@
       <c r="C23" t="str">
         <v>300409</v>
       </c>
-      <c r="D23" s="274" t="str">
+      <c r="D23" s="280" t="str">
         <v>净卖: -3736.61万</v>
       </c>
       <c r="E23">
@@ -6879,41 +6879,41 @@
       <c r="H23">
         <v>4.22</v>
       </c>
-      <c r="I23" s="280">
+      <c r="I23" s="285">
         <v>9.88</v>
       </c>
-      <c r="J23" s="275">
+      <c r="J23" s="281">
         <v>10.74</v>
       </c>
-      <c r="K23" s="276">
+      <c r="K23" s="278">
         <v>9.35</v>
       </c>
-      <c r="L23" s="281">
+      <c r="L23" s="286">
         <v>3.52</v>
       </c>
-      <c r="M23" s="284">
+      <c r="M23" s="282">
         <v>24.21</v>
       </c>
-      <c r="N23" s="285">
+      <c r="N23" s="283">
         <v>22.11</v>
       </c>
-      <c r="O23" s="282">
+      <c r="O23" s="279">
         <v>18.38</v>
       </c>
-      <c r="P23" s="277">
+      <c r="P23" s="275">
         <v>18.81</v>
       </c>
-      <c r="Q23" s="278">
+      <c r="Q23" s="276">
         <v>13.69</v>
       </c>
-      <c r="R23" s="286">
+      <c r="R23" s="277">
         <v>10.24</v>
       </c>
-      <c r="S23" s="283">
+      <c r="S23" s="274">
         <v>8</v>
       </c>
-      <c r="T23" s="279">
-        <v>-4.8</v>
+      <c r="T23" s="284">
+        <v>-3.31</v>
       </c>
     </row>
     <row r="24">
@@ -6926,7 +6926,7 @@
       <c r="C24" t="str">
         <v>300409</v>
       </c>
-      <c r="D24" s="294" t="str">
+      <c r="D24" s="296" t="str">
         <v>净卖: -2006.10万</v>
       </c>
       <c r="E24">
@@ -6941,41 +6941,41 @@
       <c r="H24">
         <v>1.68</v>
       </c>
-      <c r="I24" s="288">
+      <c r="I24" s="290">
         <v>18</v>
       </c>
-      <c r="J24" s="295">
+      <c r="J24" s="297">
         <v>16.01</v>
       </c>
-      <c r="K24" s="291">
+      <c r="K24" s="298">
         <v>12.46</v>
       </c>
-      <c r="L24" s="296">
+      <c r="L24" s="293">
         <v>12.87</v>
       </c>
-      <c r="M24" s="297">
+      <c r="M24" s="299">
         <v>8</v>
       </c>
-      <c r="N24" s="298">
+      <c r="N24" s="288">
         <v>4.73</v>
       </c>
-      <c r="O24" s="299">
+      <c r="O24" s="294">
         <v>2.6</v>
       </c>
-      <c r="P24" s="287">
+      <c r="P24" s="291">
         <v>1.82</v>
       </c>
-      <c r="Q24" s="289">
+      <c r="Q24" s="287">
         <v>2.36</v>
       </c>
-      <c r="R24" s="290">
+      <c r="R24" s="292">
         <v>8.11</v>
       </c>
-      <c r="S24" s="292">
+      <c r="S24" s="295">
         <v>5.67</v>
       </c>
-      <c r="T24" s="293">
-        <v>-9.56</v>
+      <c r="T24" s="289">
+        <v>-8.14</v>
       </c>
     </row>
     <row r="25">
@@ -7037,41 +7037,41 @@
       <c r="F26" t="str"/>
       <c r="G26" t="str"/>
       <c r="H26" t="str"/>
-      <c r="I26" s="308">
+      <c r="I26" s="311">
         <v>52.17</v>
       </c>
-      <c r="J26" s="305">
+      <c r="J26" s="300">
         <v>52.17</v>
       </c>
-      <c r="K26" s="306">
+      <c r="K26" s="302">
         <v>52.17</v>
       </c>
-      <c r="L26" s="302">
+      <c r="L26" s="303">
         <v>47.83</v>
       </c>
-      <c r="M26" s="310">
+      <c r="M26" s="306">
         <v>43.48</v>
       </c>
-      <c r="N26" s="303">
+      <c r="N26" s="304">
         <v>39.13</v>
       </c>
       <c r="O26" s="307">
         <v>34.78</v>
       </c>
-      <c r="P26" s="309">
+      <c r="P26" s="301">
         <v>39.13</v>
       </c>
-      <c r="Q26" s="311">
+      <c r="Q26" s="308">
         <v>39.13</v>
       </c>
-      <c r="R26" s="304">
+      <c r="R26" s="309">
         <v>39.13</v>
       </c>
-      <c r="S26" s="300">
+      <c r="S26" s="310">
         <v>39.13</v>
       </c>
-      <c r="T26" s="301">
-        <v>52.17</v>
+      <c r="T26" s="305">
+        <v>47.83</v>
       </c>
     </row>
     <row r="27">
@@ -7085,41 +7085,41 @@
       <c r="F27" t="str"/>
       <c r="G27" t="str"/>
       <c r="H27" t="str"/>
-      <c r="I27" s="314">
+      <c r="I27" s="319">
         <v>3.46</v>
       </c>
-      <c r="J27" s="321">
+      <c r="J27" s="316">
         <v>2.89</v>
       </c>
-      <c r="K27" s="315">
+      <c r="K27" s="317">
         <v>0.67</v>
       </c>
-      <c r="L27" s="318">
+      <c r="L27" s="322">
         <v>-0.46</v>
       </c>
-      <c r="M27" s="322">
+      <c r="M27" s="323">
         <v>-1.36</v>
       </c>
-      <c r="N27" s="319">
+      <c r="N27" s="312">
         <v>-0.02</v>
       </c>
-      <c r="O27" s="323">
+      <c r="O27" s="313">
         <v>-1.62</v>
       </c>
-      <c r="P27" s="320">
+      <c r="P27" s="318">
         <v>-2.08</v>
       </c>
-      <c r="Q27" s="312">
+      <c r="Q27" s="320">
         <v>-2.45</v>
       </c>
-      <c r="R27" s="317">
+      <c r="R27" s="314">
         <v>-2.62</v>
       </c>
-      <c r="S27" s="313">
+      <c r="S27" s="321">
         <v>-1.7</v>
       </c>
-      <c r="T27" s="316">
-        <v>19.51</v>
+      <c r="T27" s="315">
+        <v>21.39</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/王海祥/index.xlsx
+++ b/youzi/王海祥/index.xlsx
@@ -75,36 +75,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCC2E3D"/>
         <bgColor/>
       </patternFill>
@@ -117,25 +87,325 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDD3D4D"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE15663"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF57BA6E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF62BE77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47B460"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3A49"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -147,25 +417,301 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3747"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCEEBD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -177,13 +723,1093 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626E"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF5F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC380"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3B4A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6707C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -195,115 +1821,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF57BA6E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF47B460"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0EBD6"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -315,823 +1851,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF62BE77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3A49"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3747"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCEEBD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BABF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF5F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0EBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF72C585"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208838"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1143,19 +1923,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1167,739 +1953,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF269F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3B4A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70C483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6707C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0EBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0EBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF72C585"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208838"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
+        <fgColor rgb="FF50B768"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1911,67 +1965,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF50B768"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF23943D"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF48B460"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC380"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -5577,41 +5577,41 @@
       <c r="H2">
         <v>3.37</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="7">
         <v>6.43</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="8">
         <v>17.1</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="9">
         <v>11.56</v>
       </c>
-      <c r="L2" s="13">
+      <c r="L2" s="1">
         <v>22.72</v>
       </c>
-      <c r="M2" s="1">
+      <c r="M2" s="2">
         <v>30.54</v>
       </c>
-      <c r="N2" s="7">
+      <c r="N2" s="3">
         <v>43.57</v>
       </c>
       <c r="O2" s="10">
         <v>42.1</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="4">
         <v>40.15</v>
       </c>
-      <c r="Q2" s="8">
+      <c r="Q2" s="5">
         <v>33.31</v>
       </c>
-      <c r="R2" s="5">
+      <c r="R2" s="12">
         <v>34.45</v>
       </c>
       <c r="S2" s="11">
         <v>40.8</v>
       </c>
-      <c r="T2" s="3">
-        <v>18.08</v>
+      <c r="T2" s="13">
+        <v>12.3</v>
       </c>
     </row>
     <row r="3">
@@ -5624,7 +5624,7 @@
       <c r="C3" t="str">
         <v>601279</v>
       </c>
-      <c r="D3" s="18" t="str">
+      <c r="D3" s="19" t="str">
         <v>净卖: -85.25万</v>
       </c>
       <c r="E3">
@@ -5639,41 +5639,41 @@
       <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3" s="19">
+      <c r="I3" s="25">
         <v>10.15</v>
       </c>
-      <c r="J3" s="23">
+      <c r="J3" s="26">
         <v>5.97</v>
       </c>
-      <c r="K3" s="24">
+      <c r="K3" s="23">
         <v>4.48</v>
       </c>
-      <c r="L3" s="20">
+      <c r="L3" s="15">
         <v>3.88</v>
       </c>
-      <c r="M3" s="21">
+      <c r="M3" s="14">
         <v>4.18</v>
       </c>
-      <c r="N3" s="25">
+      <c r="N3" s="16">
         <v>3.88</v>
       </c>
-      <c r="O3" s="26">
+      <c r="O3" s="17">
         <v>5.67</v>
       </c>
-      <c r="P3" s="16">
+      <c r="P3" s="20">
         <v>5.07</v>
       </c>
-      <c r="Q3" s="14">
+      <c r="Q3" s="18">
         <v>4.78</v>
       </c>
-      <c r="R3" s="22">
+      <c r="R3" s="24">
         <v>2.09</v>
       </c>
-      <c r="S3" s="15">
+      <c r="S3" s="21">
         <v>4.18</v>
       </c>
-      <c r="T3" s="17">
-        <v>15.82</v>
+      <c r="T3" s="22">
+        <v>15.52</v>
       </c>
     </row>
     <row r="4">
@@ -5686,7 +5686,7 @@
       <c r="C4" t="str">
         <v>003020</v>
       </c>
-      <c r="D4" s="27" t="str">
+      <c r="D4" s="32" t="str">
         <v>净买: 1240.36万</v>
       </c>
       <c r="E4">
@@ -5701,41 +5701,41 @@
       <c r="H4">
         <v>-3.75</v>
       </c>
-      <c r="I4" s="35">
+      <c r="I4" s="33">
         <v>-6.49</v>
       </c>
-      <c r="J4" s="37">
+      <c r="J4" s="29">
         <v>-15.84</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="30">
         <v>-23.08</v>
       </c>
-      <c r="L4" s="32">
+      <c r="L4" s="34">
         <v>-24.06</v>
       </c>
-      <c r="M4" s="36">
+      <c r="M4" s="38">
         <v>-21.79</v>
       </c>
-      <c r="N4" s="28">
+      <c r="N4" s="35">
         <v>-20.71</v>
       </c>
-      <c r="O4" s="33">
+      <c r="O4" s="39">
         <v>-22.89</v>
       </c>
-      <c r="P4" s="29">
+      <c r="P4" s="27">
         <v>-24.61</v>
       </c>
-      <c r="Q4" s="38">
+      <c r="Q4" s="36">
         <v>-23.38</v>
       </c>
-      <c r="R4" s="39">
+      <c r="R4" s="28">
         <v>-24.35</v>
       </c>
-      <c r="S4" s="30">
+      <c r="S4" s="37">
         <v>-22.4</v>
       </c>
-      <c r="T4" s="34">
-        <v>-23.41</v>
+      <c r="T4" s="31">
+        <v>-23.64</v>
       </c>
     </row>
     <row r="5">
@@ -5748,7 +5748,7 @@
       <c r="C5" t="str">
         <v>003020</v>
       </c>
-      <c r="D5" s="48" t="str">
+      <c r="D5" s="40" t="str">
         <v>净买: 1925.03万</v>
       </c>
       <c r="E5">
@@ -5763,31 +5763,31 @@
       <c r="H5">
         <v>-4.9</v>
       </c>
-      <c r="I5" s="40">
+      <c r="I5" s="41">
         <v>-3.89</v>
       </c>
-      <c r="J5" s="44">
+      <c r="J5" s="49">
         <v>-5.11</v>
       </c>
-      <c r="K5" s="45">
+      <c r="K5" s="42">
         <v>-2.27</v>
       </c>
-      <c r="L5" s="41">
+      <c r="L5" s="43">
         <v>-0.93</v>
       </c>
-      <c r="M5" s="49">
+      <c r="M5" s="45">
         <v>-3.65</v>
       </c>
-      <c r="N5" s="42">
+      <c r="N5" s="46">
         <v>-5.8</v>
       </c>
-      <c r="O5" s="43">
+      <c r="O5" s="47">
         <v>-4.26</v>
       </c>
-      <c r="P5" s="46">
+      <c r="P5" s="48">
         <v>-5.48</v>
       </c>
-      <c r="Q5" s="47">
+      <c r="Q5" s="44">
         <v>-3.04</v>
       </c>
       <c r="R5" s="50">
@@ -5797,7 +5797,7 @@
         <v>-0.97</v>
       </c>
       <c r="T5" s="52">
-        <v>-4.3</v>
+        <v>-4.58</v>
       </c>
     </row>
     <row r="6">
@@ -5810,7 +5810,7 @@
       <c r="C6" t="str">
         <v>603607</v>
       </c>
-      <c r="D6" s="54" t="str">
+      <c r="D6" s="63" t="str">
         <v>净卖: -1819.82万</v>
       </c>
       <c r="E6">
@@ -5825,41 +5825,41 @@
       <c r="H6">
         <v>9.92</v>
       </c>
-      <c r="I6" s="55">
+      <c r="I6" s="56">
         <v>0.06</v>
       </c>
-      <c r="J6" s="61">
+      <c r="J6" s="64">
         <v>4.62</v>
       </c>
-      <c r="K6" s="56">
+      <c r="K6" s="57">
         <v>4.87</v>
       </c>
-      <c r="L6" s="57">
+      <c r="L6" s="60">
         <v>-5.62</v>
       </c>
-      <c r="M6" s="62">
+      <c r="M6" s="61">
         <v>-15.05</v>
       </c>
-      <c r="N6" s="58">
+      <c r="N6" s="65">
         <v>-13.34</v>
       </c>
-      <c r="O6" s="53">
+      <c r="O6" s="62">
         <v>-18.49</v>
       </c>
-      <c r="P6" s="63">
+      <c r="P6" s="58">
         <v>-19.11</v>
       </c>
-      <c r="Q6" s="64">
+      <c r="Q6" s="53">
         <v>-16.36</v>
       </c>
-      <c r="R6" s="59">
+      <c r="R6" s="54">
         <v>-15.71</v>
       </c>
-      <c r="S6" s="60">
+      <c r="S6" s="59">
         <v>-10.68</v>
       </c>
-      <c r="T6" s="65">
-        <v>-26.48</v>
+      <c r="T6" s="55">
+        <v>-27.39</v>
       </c>
     </row>
     <row r="7">
@@ -5872,7 +5872,7 @@
       <c r="C7" t="str">
         <v>603607</v>
       </c>
-      <c r="D7" s="73" t="str">
+      <c r="D7" s="70" t="str">
         <v>净卖: -2523.15万</v>
       </c>
       <c r="E7">
@@ -5887,41 +5887,41 @@
       <c r="H7">
         <v>1.49</v>
       </c>
-      <c r="I7" s="77">
+      <c r="I7" s="74">
         <v>-1.24</v>
       </c>
-      <c r="J7" s="74">
+      <c r="J7" s="76">
         <v>-11.12</v>
       </c>
-      <c r="K7" s="67">
+      <c r="K7" s="71">
         <v>-20</v>
       </c>
       <c r="L7" s="75">
         <v>-18.38</v>
       </c>
-      <c r="M7" s="68">
+      <c r="M7" s="77">
         <v>-23.24</v>
       </c>
-      <c r="N7" s="69">
+      <c r="N7" s="78">
         <v>-23.82</v>
       </c>
-      <c r="O7" s="70">
+      <c r="O7" s="72">
         <v>-21.24</v>
       </c>
-      <c r="P7" s="72">
+      <c r="P7" s="66">
         <v>-20.62</v>
       </c>
-      <c r="Q7" s="71">
+      <c r="Q7" s="73">
         <v>-15.88</v>
       </c>
-      <c r="R7" s="76">
+      <c r="R7" s="68">
         <v>-18.09</v>
       </c>
-      <c r="S7" s="78">
+      <c r="S7" s="69">
         <v>-25.41</v>
       </c>
-      <c r="T7" s="66">
-        <v>-30.76</v>
+      <c r="T7" s="67">
+        <v>-31.62</v>
       </c>
     </row>
     <row r="8">
@@ -5934,7 +5934,7 @@
       <c r="C8" t="str">
         <v>603823</v>
       </c>
-      <c r="D8" s="87" t="str">
+      <c r="D8" s="90" t="str">
         <v>净卖: -577.99万</v>
       </c>
       <c r="E8">
@@ -5949,41 +5949,41 @@
       <c r="H8">
         <v>-1.03</v>
       </c>
-      <c r="I8" s="82">
+      <c r="I8" s="91">
         <v>11.19</v>
       </c>
-      <c r="J8" s="90">
+      <c r="J8" s="79">
         <v>10.49</v>
       </c>
-      <c r="K8" s="91">
+      <c r="K8" s="80">
         <v>7.03</v>
       </c>
-      <c r="L8" s="85">
+      <c r="L8" s="81">
         <v>2.34</v>
       </c>
-      <c r="M8" s="83">
+      <c r="M8" s="86">
         <v>4.94</v>
       </c>
-      <c r="N8" s="88">
+      <c r="N8" s="87">
         <v>-1.13</v>
       </c>
-      <c r="O8" s="89">
+      <c r="O8" s="88">
         <v>-2.6</v>
       </c>
-      <c r="P8" s="79">
+      <c r="P8" s="82">
         <v>7.11</v>
       </c>
-      <c r="Q8" s="86">
+      <c r="Q8" s="83">
         <v>11.71</v>
       </c>
       <c r="R8" s="84">
         <v>17.52</v>
       </c>
-      <c r="S8" s="80">
+      <c r="S8" s="89">
         <v>17.43</v>
       </c>
-      <c r="T8" s="81">
-        <v>41.63</v>
+      <c r="T8" s="85">
+        <v>42.15</v>
       </c>
     </row>
     <row r="9">
@@ -5996,7 +5996,7 @@
       <c r="C9" t="str">
         <v>601279</v>
       </c>
-      <c r="D9" s="100" t="str">
+      <c r="D9" s="101" t="str">
         <v>净卖: -624.00万</v>
       </c>
       <c r="E9">
@@ -6011,41 +6011,41 @@
       <c r="H9">
         <v>10.09</v>
       </c>
-      <c r="I9" s="101">
+      <c r="I9" s="92">
         <v>0</v>
       </c>
-      <c r="J9" s="95">
+      <c r="J9" s="98">
         <v>-8.75</v>
       </c>
-      <c r="K9" s="102">
+      <c r="K9" s="93">
         <v>-17.92</v>
       </c>
-      <c r="L9" s="96">
+      <c r="L9" s="102">
         <v>-22.08</v>
       </c>
-      <c r="M9" s="98">
+      <c r="M9" s="103">
         <v>-23.12</v>
       </c>
-      <c r="N9" s="97">
+      <c r="N9" s="99">
         <v>-21.88</v>
       </c>
-      <c r="O9" s="103">
+      <c r="O9" s="100">
         <v>-22.29</v>
       </c>
-      <c r="P9" s="104">
+      <c r="P9" s="94">
         <v>-21.25</v>
       </c>
-      <c r="Q9" s="93">
+      <c r="Q9" s="95">
         <v>-20.62</v>
       </c>
-      <c r="R9" s="92">
+      <c r="R9" s="96">
         <v>-21.25</v>
       </c>
-      <c r="S9" s="99">
+      <c r="S9" s="104">
         <v>-19.37</v>
       </c>
-      <c r="T9" s="94">
-        <v>-19.17</v>
+      <c r="T9" s="97">
+        <v>-19.37</v>
       </c>
     </row>
     <row r="10">
@@ -6058,7 +6058,7 @@
       <c r="C10" t="str">
         <v>600980</v>
       </c>
-      <c r="D10" s="107" t="str">
+      <c r="D10" s="111" t="str">
         <v>净卖: -1981.34万</v>
       </c>
       <c r="E10">
@@ -6073,41 +6073,41 @@
       <c r="H10">
         <v>-0.58</v>
       </c>
-      <c r="I10" s="108">
+      <c r="I10" s="114">
         <v>5.96</v>
       </c>
-      <c r="J10" s="109">
+      <c r="J10" s="105">
         <v>-4.64</v>
       </c>
-      <c r="K10" s="113">
+      <c r="K10" s="115">
         <v>-14.14</v>
       </c>
-      <c r="L10" s="114">
+      <c r="L10" s="116">
         <v>-19.62</v>
       </c>
-      <c r="M10" s="116">
+      <c r="M10" s="112">
         <v>-20.09</v>
       </c>
-      <c r="N10" s="110">
+      <c r="N10" s="108">
         <v>-18.71</v>
       </c>
-      <c r="O10" s="117">
+      <c r="O10" s="106">
         <v>-18.89</v>
       </c>
-      <c r="P10" s="105">
+      <c r="P10" s="107">
         <v>-19.15</v>
       </c>
-      <c r="Q10" s="111">
+      <c r="Q10" s="113">
         <v>-20.42</v>
       </c>
-      <c r="R10" s="115">
+      <c r="R10" s="109">
         <v>-17.25</v>
       </c>
-      <c r="S10" s="106">
+      <c r="S10" s="117">
         <v>-11.14</v>
       </c>
-      <c r="T10" s="112">
-        <v>-15.67</v>
+      <c r="T10" s="110">
+        <v>-17.43</v>
       </c>
     </row>
     <row r="11">
@@ -6120,7 +6120,7 @@
       <c r="C11" t="str">
         <v>600330</v>
       </c>
-      <c r="D11" s="129" t="str">
+      <c r="D11" s="126" t="str">
         <v>净卖: -6191.34万</v>
       </c>
       <c r="E11">
@@ -6135,41 +6135,41 @@
       <c r="H11">
         <v>10</v>
       </c>
-      <c r="I11" s="130">
+      <c r="I11" s="119">
         <v>-5.66</v>
       </c>
-      <c r="J11" s="127">
+      <c r="J11" s="120">
         <v>3.77</v>
       </c>
-      <c r="K11" s="124">
+      <c r="K11" s="122">
         <v>-0.51</v>
       </c>
-      <c r="L11" s="128">
+      <c r="L11" s="123">
         <v>-7.72</v>
       </c>
-      <c r="M11" s="122">
+      <c r="M11" s="129">
         <v>-10.89</v>
       </c>
-      <c r="N11" s="118">
+      <c r="N11" s="124">
         <v>-6.43</v>
       </c>
-      <c r="O11" s="119">
+      <c r="O11" s="121">
         <v>-8.23</v>
       </c>
-      <c r="P11" s="120">
+      <c r="P11" s="125">
         <v>-3.77</v>
       </c>
-      <c r="Q11" s="123">
+      <c r="Q11" s="130">
         <v>-2.23</v>
       </c>
-      <c r="R11" s="125">
+      <c r="R11" s="127">
         <v>-1.63</v>
       </c>
-      <c r="S11" s="121">
+      <c r="S11" s="128">
         <v>-0.77</v>
       </c>
-      <c r="T11" s="126">
-        <v>101.72</v>
+      <c r="T11" s="118">
+        <v>122.04</v>
       </c>
     </row>
     <row r="12">
@@ -6182,7 +6182,7 @@
       <c r="C12" t="str">
         <v>600635</v>
       </c>
-      <c r="D12" s="139" t="str">
+      <c r="D12" s="142" t="str">
         <v>净买: 2557.50万</v>
       </c>
       <c r="E12">
@@ -6197,41 +6197,41 @@
       <c r="H12">
         <v>2.91</v>
       </c>
-      <c r="I12" s="131">
+      <c r="I12" s="134">
         <v>6.98</v>
       </c>
-      <c r="J12" s="133">
+      <c r="J12" s="141">
         <v>10.75</v>
       </c>
-      <c r="K12" s="134">
+      <c r="K12" s="137">
         <v>21.89</v>
       </c>
-      <c r="L12" s="135">
+      <c r="L12" s="138">
         <v>34.15</v>
       </c>
-      <c r="M12" s="132">
+      <c r="M12" s="143">
         <v>34.15</v>
       </c>
-      <c r="N12" s="140">
+      <c r="N12" s="131">
         <v>30.38</v>
       </c>
-      <c r="O12" s="141">
+      <c r="O12" s="132">
         <v>28.49</v>
       </c>
-      <c r="P12" s="142">
+      <c r="P12" s="135">
         <v>23.58</v>
       </c>
-      <c r="Q12" s="137">
+      <c r="Q12" s="139">
         <v>17.74</v>
       </c>
       <c r="R12" s="136">
         <v>29.43</v>
       </c>
-      <c r="S12" s="143">
+      <c r="S12" s="133">
         <v>33.77</v>
       </c>
-      <c r="T12" s="138">
-        <v>1.7</v>
+      <c r="T12" s="140">
+        <v>0.57</v>
       </c>
     </row>
     <row r="13">
@@ -6244,7 +6244,7 @@
       <c r="C13" t="str">
         <v>002488</v>
       </c>
-      <c r="D13" s="149" t="str">
+      <c r="D13" s="150" t="str">
         <v>净卖: -1403.24万</v>
       </c>
       <c r="E13">
@@ -6259,40 +6259,40 @@
       <c r="H13">
         <v>-0.57</v>
       </c>
-      <c r="I13" s="153">
+      <c r="I13" s="156">
         <v>-9.51</v>
       </c>
-      <c r="J13" s="154">
+      <c r="J13" s="147">
         <v>-0.49</v>
       </c>
-      <c r="K13" s="146">
+      <c r="K13" s="144">
         <v>-8.7</v>
       </c>
-      <c r="L13" s="150">
+      <c r="L13" s="145">
         <v>-14.88</v>
       </c>
       <c r="M13" s="151">
         <v>-14.96</v>
       </c>
-      <c r="N13" s="155">
+      <c r="N13" s="146">
         <v>-18.86</v>
       </c>
-      <c r="O13" s="156">
+      <c r="O13" s="152">
         <v>-19.92</v>
       </c>
-      <c r="P13" s="147">
+      <c r="P13" s="153">
         <v>-18.54</v>
       </c>
-      <c r="Q13" s="148">
+      <c r="Q13" s="155">
         <v>-17.24</v>
       </c>
-      <c r="R13" s="144">
+      <c r="R13" s="148">
         <v>-15.93</v>
       </c>
-      <c r="S13" s="145">
+      <c r="S13" s="154">
         <v>-17.15</v>
       </c>
-      <c r="T13" s="152">
+      <c r="T13" s="149">
         <v>-7.07</v>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       <c r="C14" t="str">
         <v>301246</v>
       </c>
-      <c r="D14" s="164" t="str">
+      <c r="D14" s="163" t="str">
         <v>净卖: -752.38万</v>
       </c>
       <c r="E14">
@@ -6324,38 +6324,38 @@
       <c r="I14" s="165">
         <v>23.71</v>
       </c>
-      <c r="J14" s="168">
+      <c r="J14" s="166">
         <v>15.87</v>
       </c>
-      <c r="K14" s="158">
+      <c r="K14" s="160">
         <v>21.68</v>
       </c>
-      <c r="L14" s="159">
+      <c r="L14" s="167">
         <v>20.7</v>
       </c>
-      <c r="M14" s="160">
+      <c r="M14" s="164">
         <v>16.22</v>
       </c>
-      <c r="N14" s="162">
+      <c r="N14" s="169">
         <v>18.95</v>
       </c>
-      <c r="O14" s="166">
+      <c r="O14" s="157">
         <v>19.79</v>
       </c>
-      <c r="P14" s="169">
+      <c r="P14" s="161">
         <v>17.41</v>
       </c>
-      <c r="Q14" s="167">
+      <c r="Q14" s="158">
         <v>19.79</v>
       </c>
-      <c r="R14" s="157">
+      <c r="R14" s="159">
         <v>15.38</v>
       </c>
-      <c r="S14" s="161">
+      <c r="S14" s="162">
         <v>18.25</v>
       </c>
-      <c r="T14" s="163">
-        <v>68.25</v>
+      <c r="T14" s="168">
+        <v>71.05</v>
       </c>
     </row>
     <row r="15">
@@ -6368,7 +6368,7 @@
       <c r="C15" t="str">
         <v>002198</v>
       </c>
-      <c r="D15" s="174" t="str">
+      <c r="D15" s="181" t="str">
         <v>净买: 1396.06万</v>
       </c>
       <c r="E15">
@@ -6383,41 +6383,41 @@
       <c r="H15">
         <v>9.79</v>
       </c>
-      <c r="I15" s="178">
+      <c r="I15" s="171">
         <v>0.24</v>
       </c>
       <c r="J15" s="175">
         <v>-9.75</v>
       </c>
-      <c r="K15" s="179">
+      <c r="K15" s="176">
         <v>-16.17</v>
       </c>
-      <c r="L15" s="180">
+      <c r="L15" s="177">
         <v>-16.77</v>
       </c>
-      <c r="M15" s="176">
+      <c r="M15" s="182">
         <v>-20.33</v>
       </c>
-      <c r="N15" s="177">
+      <c r="N15" s="172">
         <v>-17.72</v>
       </c>
-      <c r="O15" s="181">
+      <c r="O15" s="173">
         <v>-12.72</v>
       </c>
-      <c r="P15" s="182">
+      <c r="P15" s="170">
         <v>-11.18</v>
       </c>
-      <c r="Q15" s="170">
+      <c r="Q15" s="178">
         <v>-10.7</v>
       </c>
-      <c r="R15" s="171">
+      <c r="R15" s="179">
         <v>-10.23</v>
       </c>
-      <c r="S15" s="172">
+      <c r="S15" s="180">
         <v>-11.77</v>
       </c>
-      <c r="T15" s="173">
-        <v>-9.39</v>
+      <c r="T15" s="174">
+        <v>-14.98</v>
       </c>
     </row>
     <row r="16">
@@ -6430,7 +6430,7 @@
       <c r="C16" t="str">
         <v>002114</v>
       </c>
-      <c r="D16" s="190" t="str">
+      <c r="D16" s="191" t="str">
         <v>净卖: -121.61万</v>
       </c>
       <c r="E16">
@@ -6445,41 +6445,41 @@
       <c r="H16">
         <v>9.95</v>
       </c>
-      <c r="I16" s="186">
+      <c r="I16" s="185">
         <v>0</v>
       </c>
-      <c r="J16" s="194">
+      <c r="J16" s="186">
         <v>-9.98</v>
       </c>
-      <c r="K16" s="187">
+      <c r="K16" s="183">
         <v>-15.64</v>
       </c>
-      <c r="L16" s="195">
+      <c r="L16" s="188">
         <v>-7.2</v>
       </c>
-      <c r="M16" s="183">
+      <c r="M16" s="189">
         <v>-9.16</v>
       </c>
-      <c r="N16" s="189">
+      <c r="N16" s="192">
         <v>-5.66</v>
       </c>
-      <c r="O16" s="191">
+      <c r="O16" s="190">
         <v>-7.3</v>
       </c>
-      <c r="P16" s="188">
+      <c r="P16" s="187">
         <v>-3.4</v>
       </c>
       <c r="Q16" s="184">
         <v>-6.17</v>
       </c>
-      <c r="R16" s="192">
+      <c r="R16" s="193">
         <v>-11.73</v>
       </c>
-      <c r="S16" s="193">
+      <c r="S16" s="194">
         <v>-10.7</v>
       </c>
-      <c r="T16" s="185">
-        <v>-7.1</v>
+      <c r="T16" s="195">
+        <v>-7</v>
       </c>
     </row>
     <row r="17">
@@ -6492,7 +6492,7 @@
       <c r="C17" t="str">
         <v>603815</v>
       </c>
-      <c r="D17" s="201" t="str">
+      <c r="D17" s="199" t="str">
         <v>净卖: -1097.64万</v>
       </c>
       <c r="E17">
@@ -6507,41 +6507,41 @@
       <c r="H17">
         <v>0.09</v>
       </c>
-      <c r="I17" s="202">
+      <c r="I17" s="200">
         <v>9.95</v>
       </c>
-      <c r="J17" s="203">
+      <c r="J17" s="206">
         <v>12.93</v>
       </c>
-      <c r="K17" s="208">
+      <c r="K17" s="201">
         <v>12.57</v>
       </c>
-      <c r="L17" s="204">
+      <c r="L17" s="207">
         <v>17.45</v>
       </c>
-      <c r="M17" s="205">
+      <c r="M17" s="208">
         <v>9.76</v>
       </c>
-      <c r="N17" s="206">
+      <c r="N17" s="196">
         <v>9.22</v>
       </c>
-      <c r="O17" s="207">
+      <c r="O17" s="202">
         <v>-1.72</v>
       </c>
-      <c r="P17" s="196">
+      <c r="P17" s="203">
         <v>-11.57</v>
       </c>
-      <c r="Q17" s="197">
+      <c r="Q17" s="204">
         <v>-15.01</v>
       </c>
-      <c r="R17" s="198">
+      <c r="R17" s="205">
         <v>-21.52</v>
       </c>
-      <c r="S17" s="199">
+      <c r="S17" s="197">
         <v>-23.87</v>
       </c>
-      <c r="T17" s="200">
-        <v>-36.08</v>
+      <c r="T17" s="198">
+        <v>-35.44</v>
       </c>
     </row>
     <row r="18">
@@ -6554,7 +6554,7 @@
       <c r="C18" t="str">
         <v>000890</v>
       </c>
-      <c r="D18" s="211" t="str">
+      <c r="D18" s="217" t="str">
         <v>净买: 1092.74万</v>
       </c>
       <c r="E18">
@@ -6569,41 +6569,41 @@
       <c r="H18">
         <v>10.05</v>
       </c>
-      <c r="I18" s="215">
+      <c r="I18" s="218">
         <v>0</v>
       </c>
-      <c r="J18" s="221">
+      <c r="J18" s="219">
         <v>10.06</v>
       </c>
-      <c r="K18" s="209">
+      <c r="K18" s="213">
         <v>11.46</v>
       </c>
-      <c r="L18" s="218">
+      <c r="L18" s="221">
         <v>0.31</v>
       </c>
-      <c r="M18" s="219">
+      <c r="M18" s="209">
         <v>-9.75</v>
       </c>
-      <c r="N18" s="212">
+      <c r="N18" s="210">
         <v>-9.6</v>
       </c>
-      <c r="O18" s="216">
+      <c r="O18" s="214">
         <v>-16.41</v>
       </c>
-      <c r="P18" s="213">
+      <c r="P18" s="215">
         <v>-14.24</v>
       </c>
-      <c r="Q18" s="214">
+      <c r="Q18" s="216">
         <v>-15.63</v>
       </c>
-      <c r="R18" s="217">
+      <c r="R18" s="220">
         <v>-16.87</v>
       </c>
-      <c r="S18" s="220">
+      <c r="S18" s="211">
         <v>-19.81</v>
       </c>
-      <c r="T18" s="210">
-        <v>125.85</v>
+      <c r="T18" s="212">
+        <v>151.39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,7 +6616,7 @@
       <c r="C19" t="str">
         <v>603067</v>
       </c>
-      <c r="D19" s="230" t="str">
+      <c r="D19" s="222" t="str">
         <v>净买: 1179.50万</v>
       </c>
       <c r="E19">
@@ -6631,10 +6631,10 @@
       <c r="H19">
         <v>-3.07</v>
       </c>
-      <c r="I19" s="224">
+      <c r="I19" s="225">
         <v>-5.37</v>
       </c>
-      <c r="J19" s="231">
+      <c r="J19" s="226">
         <v>-2.17</v>
       </c>
       <c r="K19" s="228">
@@ -6643,29 +6643,29 @@
       <c r="L19" s="229">
         <v>4.84</v>
       </c>
-      <c r="M19" s="222">
+      <c r="M19" s="227">
         <v>11.14</v>
       </c>
-      <c r="N19" s="223">
+      <c r="N19" s="234">
         <v>10.82</v>
       </c>
-      <c r="O19" s="225">
+      <c r="O19" s="230">
         <v>9.93</v>
       </c>
-      <c r="P19" s="232">
+      <c r="P19" s="223">
         <v>6.01</v>
       </c>
-      <c r="Q19" s="233">
+      <c r="Q19" s="224">
         <v>3.17</v>
       </c>
-      <c r="R19" s="226">
+      <c r="R19" s="231">
         <v>2.53</v>
       </c>
-      <c r="S19" s="227">
+      <c r="S19" s="232">
         <v>12.78</v>
       </c>
-      <c r="T19" s="234">
-        <v>32.74</v>
+      <c r="T19" s="233">
+        <v>33.42</v>
       </c>
     </row>
     <row r="20">
@@ -6678,7 +6678,7 @@
       <c r="C20" t="str">
         <v>000890</v>
       </c>
-      <c r="D20" s="245" t="str">
+      <c r="D20" s="246" t="str">
         <v>净买: 1030.64万</v>
       </c>
       <c r="E20">
@@ -6693,41 +6693,41 @@
       <c r="H20">
         <v>-9.72</v>
       </c>
-      <c r="I20" s="237">
+      <c r="I20" s="236">
         <v>-0.31</v>
       </c>
-      <c r="J20" s="247">
+      <c r="J20" s="237">
         <v>-10.31</v>
       </c>
-      <c r="K20" s="238">
+      <c r="K20" s="247">
         <v>-10.15</v>
       </c>
       <c r="L20" s="243">
         <v>-16.92</v>
       </c>
-      <c r="M20" s="239">
+      <c r="M20" s="240">
         <v>-14.77</v>
       </c>
-      <c r="N20" s="240">
+      <c r="N20" s="238">
         <v>-16.15</v>
       </c>
-      <c r="O20" s="246">
+      <c r="O20" s="244">
         <v>-17.38</v>
       </c>
-      <c r="P20" s="241">
+      <c r="P20" s="235">
         <v>-20.31</v>
       </c>
-      <c r="Q20" s="235">
+      <c r="Q20" s="245">
         <v>-20.62</v>
       </c>
-      <c r="R20" s="242">
+      <c r="R20" s="241">
         <v>-22</v>
       </c>
-      <c r="S20" s="236">
+      <c r="S20" s="239">
         <v>-21.69</v>
       </c>
-      <c r="T20" s="244">
-        <v>124.46</v>
+      <c r="T20" s="242">
+        <v>149.85</v>
       </c>
     </row>
     <row r="21">
@@ -6740,7 +6740,7 @@
       <c r="C21" t="str">
         <v>000890</v>
       </c>
-      <c r="D21" s="256" t="str">
+      <c r="D21" s="255" t="str">
         <v>净卖: -1045.40万</v>
       </c>
       <c r="E21">
@@ -6755,41 +6755,41 @@
       <c r="H21">
         <v>-4.94</v>
       </c>
-      <c r="I21" s="260">
+      <c r="I21" s="250">
         <v>-5.36</v>
       </c>
-      <c r="J21" s="257">
+      <c r="J21" s="251">
         <v>-5.19</v>
       </c>
-      <c r="K21" s="258">
+      <c r="K21" s="256">
         <v>-12.34</v>
       </c>
-      <c r="L21" s="259">
+      <c r="L21" s="257">
         <v>-10.06</v>
       </c>
-      <c r="M21" s="248">
+      <c r="M21" s="258">
         <v>-11.53</v>
       </c>
       <c r="N21" s="252">
         <v>-12.82</v>
       </c>
-      <c r="O21" s="253">
+      <c r="O21" s="259">
         <v>-15.91</v>
       </c>
-      <c r="P21" s="254">
+      <c r="P21" s="260">
         <v>-16.23</v>
       </c>
-      <c r="Q21" s="249">
+      <c r="Q21" s="248">
         <v>-17.69</v>
       </c>
-      <c r="R21" s="255">
+      <c r="R21" s="253">
         <v>-17.37</v>
       </c>
-      <c r="S21" s="250">
+      <c r="S21" s="254">
         <v>-16.23</v>
       </c>
-      <c r="T21" s="251">
-        <v>136.85</v>
+      <c r="T21" s="249">
+        <v>163.64</v>
       </c>
     </row>
     <row r="22">
@@ -6802,7 +6802,7 @@
       <c r="C22" t="str">
         <v>300409</v>
       </c>
-      <c r="D22" s="268" t="str">
+      <c r="D22" s="264" t="str">
         <v>净卖: -3259.20万</v>
       </c>
       <c r="E22">
@@ -6817,41 +6817,41 @@
       <c r="H22">
         <v>4.54</v>
       </c>
-      <c r="I22" s="264">
+      <c r="I22" s="265">
         <v>14.8</v>
       </c>
-      <c r="J22" s="269">
+      <c r="J22" s="261">
         <v>31.48</v>
       </c>
-      <c r="K22" s="273">
+      <c r="K22" s="267">
         <v>32.5</v>
       </c>
-      <c r="L22" s="262">
+      <c r="L22" s="271">
         <v>30.84</v>
       </c>
-      <c r="M22" s="270">
+      <c r="M22" s="268">
         <v>23.86</v>
       </c>
-      <c r="N22" s="271">
+      <c r="N22" s="272">
         <v>48.62</v>
       </c>
-      <c r="O22" s="263">
+      <c r="O22" s="262">
         <v>46.11</v>
       </c>
-      <c r="P22" s="272">
+      <c r="P22" s="266">
         <v>41.64</v>
       </c>
-      <c r="Q22" s="265">
+      <c r="Q22" s="273">
         <v>42.15</v>
       </c>
-      <c r="R22" s="266">
+      <c r="R22" s="269">
         <v>36.03</v>
       </c>
-      <c r="S22" s="261">
+      <c r="S22" s="263">
         <v>31.9</v>
       </c>
-      <c r="T22" s="267">
-        <v>15.7</v>
+      <c r="T22" s="270">
+        <v>13.61</v>
       </c>
     </row>
     <row r="23">
@@ -6864,7 +6864,7 @@
       <c r="C23" t="str">
         <v>300409</v>
       </c>
-      <c r="D23" s="280" t="str">
+      <c r="D23" s="277" t="str">
         <v>净卖: -3736.61万</v>
       </c>
       <c r="E23">
@@ -6879,41 +6879,41 @@
       <c r="H23">
         <v>4.22</v>
       </c>
-      <c r="I23" s="285">
+      <c r="I23" s="283">
         <v>9.88</v>
       </c>
-      <c r="J23" s="281">
+      <c r="J23" s="284">
         <v>10.74</v>
       </c>
       <c r="K23" s="278">
         <v>9.35</v>
       </c>
-      <c r="L23" s="286">
+      <c r="L23" s="279">
         <v>3.52</v>
       </c>
-      <c r="M23" s="282">
+      <c r="M23" s="274">
         <v>24.21</v>
       </c>
-      <c r="N23" s="283">
+      <c r="N23" s="280">
         <v>22.11</v>
       </c>
-      <c r="O23" s="279">
+      <c r="O23" s="281">
         <v>18.38</v>
       </c>
-      <c r="P23" s="275">
+      <c r="P23" s="285">
         <v>18.81</v>
       </c>
       <c r="Q23" s="276">
         <v>13.69</v>
       </c>
-      <c r="R23" s="277">
+      <c r="R23" s="275">
         <v>10.24</v>
       </c>
-      <c r="S23" s="274">
+      <c r="S23" s="282">
         <v>8</v>
       </c>
-      <c r="T23" s="284">
-        <v>-3.31</v>
+      <c r="T23" s="286">
+        <v>-5.05</v>
       </c>
     </row>
     <row r="24">
@@ -6926,7 +6926,7 @@
       <c r="C24" t="str">
         <v>300409</v>
       </c>
-      <c r="D24" s="296" t="str">
+      <c r="D24" s="298" t="str">
         <v>净卖: -2006.10万</v>
       </c>
       <c r="E24">
@@ -6941,41 +6941,41 @@
       <c r="H24">
         <v>1.68</v>
       </c>
-      <c r="I24" s="290">
+      <c r="I24" s="288">
         <v>18</v>
       </c>
-      <c r="J24" s="297">
+      <c r="J24" s="289">
         <v>16.01</v>
       </c>
-      <c r="K24" s="298">
+      <c r="K24" s="295">
         <v>12.46</v>
       </c>
-      <c r="L24" s="293">
+      <c r="L24" s="290">
         <v>12.87</v>
       </c>
-      <c r="M24" s="299">
+      <c r="M24" s="296">
         <v>8</v>
       </c>
-      <c r="N24" s="288">
+      <c r="N24" s="291">
         <v>4.73</v>
       </c>
-      <c r="O24" s="294">
+      <c r="O24" s="299">
         <v>2.6</v>
       </c>
-      <c r="P24" s="291">
+      <c r="P24" s="292">
         <v>1.82</v>
       </c>
-      <c r="Q24" s="287">
+      <c r="Q24" s="293">
         <v>2.36</v>
       </c>
-      <c r="R24" s="292">
+      <c r="R24" s="287">
         <v>8.11</v>
       </c>
-      <c r="S24" s="295">
+      <c r="S24" s="297">
         <v>5.67</v>
       </c>
-      <c r="T24" s="289">
-        <v>-8.14</v>
+      <c r="T24" s="294">
+        <v>-9.79</v>
       </c>
     </row>
     <row r="25">
@@ -7037,40 +7037,40 @@
       <c r="F26" t="str"/>
       <c r="G26" t="str"/>
       <c r="H26" t="str"/>
-      <c r="I26" s="311">
+      <c r="I26" s="310">
         <v>52.17</v>
       </c>
-      <c r="J26" s="300">
+      <c r="J26" s="311">
         <v>52.17</v>
       </c>
-      <c r="K26" s="302">
+      <c r="K26" s="300">
         <v>52.17</v>
       </c>
-      <c r="L26" s="303">
+      <c r="L26" s="305">
         <v>47.83</v>
       </c>
       <c r="M26" s="306">
         <v>43.48</v>
       </c>
-      <c r="N26" s="304">
+      <c r="N26" s="303">
         <v>39.13</v>
       </c>
       <c r="O26" s="307">
         <v>34.78</v>
       </c>
-      <c r="P26" s="301">
+      <c r="P26" s="308">
         <v>39.13</v>
       </c>
-      <c r="Q26" s="308">
+      <c r="Q26" s="302">
         <v>39.13</v>
       </c>
-      <c r="R26" s="309">
+      <c r="R26" s="304">
         <v>39.13</v>
       </c>
-      <c r="S26" s="310">
+      <c r="S26" s="309">
         <v>39.13</v>
       </c>
-      <c r="T26" s="305">
+      <c r="T26" s="301">
         <v>47.83</v>
       </c>
     </row>
@@ -7085,41 +7085,41 @@
       <c r="F27" t="str"/>
       <c r="G27" t="str"/>
       <c r="H27" t="str"/>
-      <c r="I27" s="319">
+      <c r="I27" s="315">
         <v>3.46</v>
       </c>
-      <c r="J27" s="316">
+      <c r="J27" s="318">
         <v>2.89</v>
       </c>
-      <c r="K27" s="317">
+      <c r="K27" s="316">
         <v>0.67</v>
       </c>
-      <c r="L27" s="322">
+      <c r="L27" s="312">
         <v>-0.46</v>
       </c>
-      <c r="M27" s="323">
+      <c r="M27" s="319">
         <v>-1.36</v>
       </c>
-      <c r="N27" s="312">
+      <c r="N27" s="321">
         <v>-0.02</v>
       </c>
-      <c r="O27" s="313">
+      <c r="O27" s="320">
         <v>-1.62</v>
       </c>
-      <c r="P27" s="318">
+      <c r="P27" s="313">
         <v>-2.08</v>
       </c>
-      <c r="Q27" s="320">
+      <c r="Q27" s="314">
         <v>-2.45</v>
       </c>
-      <c r="R27" s="314">
+      <c r="R27" s="322">
         <v>-2.62</v>
       </c>
-      <c r="S27" s="321">
+      <c r="S27" s="323">
         <v>-1.7</v>
       </c>
-      <c r="T27" s="315">
-        <v>21.39</v>
+      <c r="T27" s="317">
+        <v>24.88</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/王海祥/index.xlsx
+++ b/youzi/王海祥/index.xlsx
@@ -45,36 +45,60 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFCC2E3D"/>
         <bgColor/>
       </patternFill>
@@ -93,25 +117,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFE3626E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,13 +147,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE3626E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626E"/>
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -141,7 +177,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4D"/>
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47B460"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF57BA6E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF62BE77"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -153,37 +357,313 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3A49"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCEEBD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3747"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -225,43 +705,349 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF61BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -279,43 +1065,769 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF57BA6E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF62BE77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF47B460"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF5F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC380"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3B4A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6707C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -327,811 +1839,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3A49"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3747"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCEEBD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF5F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0EBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208838"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0EBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF72C585"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF50B768"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF48B460"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1143,13 +1941,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCFEFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1161,817 +1971,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF218D3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3B4A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6707C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0EBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0EBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF72C585"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208838"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC380"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF50B768"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCFEFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF48B460"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -5562,7 +5562,7 @@
       <c r="C2" t="str">
         <v>002276</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="2" t="str">
         <v>净卖: -3245.54万</v>
       </c>
       <c r="E2">
@@ -5577,41 +5577,41 @@
       <c r="H2">
         <v>3.37</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="11">
         <v>6.43</v>
       </c>
-      <c r="J2" s="8">
+      <c r="J2" s="7">
         <v>17.1</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="12">
         <v>11.56</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2" s="8">
         <v>22.72</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="3">
         <v>30.54</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="13">
         <v>43.57</v>
       </c>
-      <c r="O2" s="10">
+      <c r="O2" s="4">
         <v>42.1</v>
       </c>
-      <c r="P2" s="4">
+      <c r="P2" s="9">
         <v>40.15</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="1">
         <v>33.31</v>
       </c>
-      <c r="R2" s="12">
+      <c r="R2" s="5">
         <v>34.45</v>
       </c>
-      <c r="S2" s="11">
+      <c r="S2" s="10">
         <v>40.8</v>
       </c>
-      <c r="T2" s="13">
-        <v>12.3</v>
+      <c r="T2" s="6">
+        <v>10.83</v>
       </c>
     </row>
     <row r="3">
@@ -5624,7 +5624,7 @@
       <c r="C3" t="str">
         <v>601279</v>
       </c>
-      <c r="D3" s="19" t="str">
+      <c r="D3" s="15" t="str">
         <v>净卖: -85.25万</v>
       </c>
       <c r="E3">
@@ -5639,41 +5639,41 @@
       <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="22">
         <v>10.15</v>
       </c>
-      <c r="J3" s="26">
+      <c r="J3" s="19">
         <v>5.97</v>
       </c>
-      <c r="K3" s="23">
+      <c r="K3" s="20">
         <v>4.48</v>
       </c>
-      <c r="L3" s="15">
+      <c r="L3" s="16">
         <v>3.88</v>
       </c>
-      <c r="M3" s="14">
+      <c r="M3" s="21">
         <v>4.18</v>
       </c>
-      <c r="N3" s="16">
+      <c r="N3" s="14">
         <v>3.88</v>
       </c>
-      <c r="O3" s="17">
+      <c r="O3" s="23">
         <v>5.67</v>
       </c>
-      <c r="P3" s="20">
+      <c r="P3" s="24">
         <v>5.07</v>
       </c>
-      <c r="Q3" s="18">
+      <c r="Q3" s="17">
         <v>4.78</v>
       </c>
-      <c r="R3" s="24">
+      <c r="R3" s="25">
         <v>2.09</v>
       </c>
-      <c r="S3" s="21">
+      <c r="S3" s="18">
         <v>4.18</v>
       </c>
-      <c r="T3" s="22">
-        <v>15.52</v>
+      <c r="T3" s="26">
+        <v>17.01</v>
       </c>
     </row>
     <row r="4">
@@ -5686,7 +5686,7 @@
       <c r="C4" t="str">
         <v>003020</v>
       </c>
-      <c r="D4" s="32" t="str">
+      <c r="D4" s="36" t="str">
         <v>净买: 1240.36万</v>
       </c>
       <c r="E4">
@@ -5701,41 +5701,41 @@
       <c r="H4">
         <v>-3.75</v>
       </c>
-      <c r="I4" s="33">
+      <c r="I4" s="37">
         <v>-6.49</v>
       </c>
-      <c r="J4" s="29">
+      <c r="J4" s="34">
         <v>-15.84</v>
       </c>
-      <c r="K4" s="30">
+      <c r="K4" s="27">
         <v>-23.08</v>
       </c>
-      <c r="L4" s="34">
+      <c r="L4" s="31">
         <v>-24.06</v>
       </c>
       <c r="M4" s="38">
         <v>-21.79</v>
       </c>
-      <c r="N4" s="35">
+      <c r="N4" s="28">
         <v>-20.71</v>
       </c>
-      <c r="O4" s="39">
+      <c r="O4" s="29">
         <v>-22.89</v>
       </c>
-      <c r="P4" s="27">
+      <c r="P4" s="32">
         <v>-24.61</v>
       </c>
-      <c r="Q4" s="36">
+      <c r="Q4" s="33">
         <v>-23.38</v>
       </c>
-      <c r="R4" s="28">
+      <c r="R4" s="30">
         <v>-24.35</v>
       </c>
-      <c r="S4" s="37">
+      <c r="S4" s="35">
         <v>-22.4</v>
       </c>
-      <c r="T4" s="31">
-        <v>-23.64</v>
+      <c r="T4" s="39">
+        <v>-24.38</v>
       </c>
     </row>
     <row r="5">
@@ -5748,7 +5748,7 @@
       <c r="C5" t="str">
         <v>003020</v>
       </c>
-      <c r="D5" s="40" t="str">
+      <c r="D5" s="45" t="str">
         <v>净买: 1925.03万</v>
       </c>
       <c r="E5">
@@ -5763,41 +5763,41 @@
       <c r="H5">
         <v>-4.9</v>
       </c>
-      <c r="I5" s="41">
+      <c r="I5" s="46">
         <v>-3.89</v>
       </c>
-      <c r="J5" s="49">
+      <c r="J5" s="50">
         <v>-5.11</v>
       </c>
-      <c r="K5" s="42">
+      <c r="K5" s="48">
         <v>-2.27</v>
       </c>
-      <c r="L5" s="43">
+      <c r="L5" s="51">
         <v>-0.93</v>
       </c>
-      <c r="M5" s="45">
+      <c r="M5" s="52">
         <v>-3.65</v>
       </c>
-      <c r="N5" s="46">
+      <c r="N5" s="49">
         <v>-5.8</v>
       </c>
-      <c r="O5" s="47">
+      <c r="O5" s="42">
         <v>-4.26</v>
       </c>
-      <c r="P5" s="48">
+      <c r="P5" s="47">
         <v>-5.48</v>
       </c>
-      <c r="Q5" s="44">
+      <c r="Q5" s="40">
         <v>-3.04</v>
       </c>
-      <c r="R5" s="50">
+      <c r="R5" s="43">
         <v>-2.07</v>
       </c>
-      <c r="S5" s="51">
+      <c r="S5" s="41">
         <v>-0.97</v>
       </c>
-      <c r="T5" s="52">
-        <v>-4.58</v>
+      <c r="T5" s="44">
+        <v>-5.52</v>
       </c>
     </row>
     <row r="6">
@@ -5810,7 +5810,7 @@
       <c r="C6" t="str">
         <v>603607</v>
       </c>
-      <c r="D6" s="63" t="str">
+      <c r="D6" s="53" t="str">
         <v>净卖: -1819.82万</v>
       </c>
       <c r="E6">
@@ -5825,41 +5825,41 @@
       <c r="H6">
         <v>9.92</v>
       </c>
-      <c r="I6" s="56">
+      <c r="I6" s="60">
         <v>0.06</v>
       </c>
-      <c r="J6" s="64">
+      <c r="J6" s="57">
         <v>4.62</v>
       </c>
-      <c r="K6" s="57">
+      <c r="K6" s="58">
         <v>4.87</v>
       </c>
-      <c r="L6" s="60">
+      <c r="L6" s="54">
         <v>-5.62</v>
       </c>
-      <c r="M6" s="61">
+      <c r="M6" s="55">
         <v>-15.05</v>
       </c>
-      <c r="N6" s="65">
+      <c r="N6" s="64">
         <v>-13.34</v>
       </c>
-      <c r="O6" s="62">
+      <c r="O6" s="65">
         <v>-18.49</v>
       </c>
-      <c r="P6" s="58">
+      <c r="P6" s="59">
         <v>-19.11</v>
       </c>
-      <c r="Q6" s="53">
+      <c r="Q6" s="61">
         <v>-16.36</v>
       </c>
-      <c r="R6" s="54">
+      <c r="R6" s="62">
         <v>-15.71</v>
       </c>
-      <c r="S6" s="59">
+      <c r="S6" s="56">
         <v>-10.68</v>
       </c>
-      <c r="T6" s="55">
-        <v>-27.39</v>
+      <c r="T6" s="63">
+        <v>-26.3</v>
       </c>
     </row>
     <row r="7">
@@ -5872,7 +5872,7 @@
       <c r="C7" t="str">
         <v>603607</v>
       </c>
-      <c r="D7" s="70" t="str">
+      <c r="D7" s="73" t="str">
         <v>净卖: -2523.15万</v>
       </c>
       <c r="E7">
@@ -5887,41 +5887,41 @@
       <c r="H7">
         <v>1.49</v>
       </c>
-      <c r="I7" s="74">
+      <c r="I7" s="75">
         <v>-1.24</v>
       </c>
       <c r="J7" s="76">
         <v>-11.12</v>
       </c>
-      <c r="K7" s="71">
+      <c r="K7" s="67">
         <v>-20</v>
       </c>
-      <c r="L7" s="75">
+      <c r="L7" s="68">
         <v>-18.38</v>
       </c>
       <c r="M7" s="77">
         <v>-23.24</v>
       </c>
-      <c r="N7" s="78">
+      <c r="N7" s="69">
         <v>-23.82</v>
       </c>
-      <c r="O7" s="72">
+      <c r="O7" s="70">
         <v>-21.24</v>
       </c>
-      <c r="P7" s="66">
+      <c r="P7" s="78">
         <v>-20.62</v>
       </c>
-      <c r="Q7" s="73">
+      <c r="Q7" s="71">
         <v>-15.88</v>
       </c>
-      <c r="R7" s="68">
+      <c r="R7" s="66">
         <v>-18.09</v>
       </c>
-      <c r="S7" s="69">
+      <c r="S7" s="72">
         <v>-25.41</v>
       </c>
-      <c r="T7" s="67">
-        <v>-31.62</v>
+      <c r="T7" s="74">
+        <v>-30.59</v>
       </c>
     </row>
     <row r="8">
@@ -5934,7 +5934,7 @@
       <c r="C8" t="str">
         <v>603823</v>
       </c>
-      <c r="D8" s="90" t="str">
+      <c r="D8" s="88" t="str">
         <v>净卖: -577.99万</v>
       </c>
       <c r="E8">
@@ -5949,41 +5949,41 @@
       <c r="H8">
         <v>-1.03</v>
       </c>
-      <c r="I8" s="91">
+      <c r="I8" s="84">
         <v>11.19</v>
       </c>
-      <c r="J8" s="79">
+      <c r="J8" s="80">
         <v>10.49</v>
       </c>
-      <c r="K8" s="80">
+      <c r="K8" s="87">
         <v>7.03</v>
       </c>
-      <c r="L8" s="81">
+      <c r="L8" s="89">
         <v>2.34</v>
       </c>
-      <c r="M8" s="86">
+      <c r="M8" s="90">
         <v>4.94</v>
       </c>
-      <c r="N8" s="87">
+      <c r="N8" s="85">
         <v>-1.13</v>
       </c>
-      <c r="O8" s="88">
+      <c r="O8" s="86">
         <v>-2.6</v>
       </c>
-      <c r="P8" s="82">
+      <c r="P8" s="91">
         <v>7.11</v>
       </c>
-      <c r="Q8" s="83">
+      <c r="Q8" s="79">
         <v>11.71</v>
       </c>
-      <c r="R8" s="84">
+      <c r="R8" s="81">
         <v>17.52</v>
       </c>
-      <c r="S8" s="89">
+      <c r="S8" s="82">
         <v>17.43</v>
       </c>
-      <c r="T8" s="85">
-        <v>42.15</v>
+      <c r="T8" s="83">
+        <v>41.37</v>
       </c>
     </row>
     <row r="9">
@@ -5996,7 +5996,7 @@
       <c r="C9" t="str">
         <v>601279</v>
       </c>
-      <c r="D9" s="101" t="str">
+      <c r="D9" s="99" t="str">
         <v>净卖: -624.00万</v>
       </c>
       <c r="E9">
@@ -6011,41 +6011,41 @@
       <c r="H9">
         <v>10.09</v>
       </c>
-      <c r="I9" s="92">
+      <c r="I9" s="100">
         <v>0</v>
       </c>
-      <c r="J9" s="98">
+      <c r="J9" s="103">
         <v>-8.75</v>
       </c>
-      <c r="K9" s="93">
+      <c r="K9" s="104">
         <v>-17.92</v>
       </c>
-      <c r="L9" s="102">
+      <c r="L9" s="94">
         <v>-22.08</v>
       </c>
-      <c r="M9" s="103">
+      <c r="M9" s="95">
         <v>-23.12</v>
       </c>
-      <c r="N9" s="99">
+      <c r="N9" s="92">
         <v>-21.88</v>
       </c>
-      <c r="O9" s="100">
+      <c r="O9" s="96">
         <v>-22.29</v>
       </c>
-      <c r="P9" s="94">
+      <c r="P9" s="101">
         <v>-21.25</v>
       </c>
-      <c r="Q9" s="95">
+      <c r="Q9" s="93">
         <v>-20.62</v>
       </c>
-      <c r="R9" s="96">
+      <c r="R9" s="102">
         <v>-21.25</v>
       </c>
-      <c r="S9" s="104">
+      <c r="S9" s="97">
         <v>-19.37</v>
       </c>
-      <c r="T9" s="97">
-        <v>-19.37</v>
+      <c r="T9" s="98">
+        <v>-18.33</v>
       </c>
     </row>
     <row r="10">
@@ -6058,7 +6058,7 @@
       <c r="C10" t="str">
         <v>600980</v>
       </c>
-      <c r="D10" s="111" t="str">
+      <c r="D10" s="117" t="str">
         <v>净卖: -1981.34万</v>
       </c>
       <c r="E10">
@@ -6073,41 +6073,41 @@
       <c r="H10">
         <v>-0.58</v>
       </c>
-      <c r="I10" s="114">
+      <c r="I10" s="106">
         <v>5.96</v>
       </c>
-      <c r="J10" s="105">
+      <c r="J10" s="113">
         <v>-4.64</v>
       </c>
-      <c r="K10" s="115">
+      <c r="K10" s="107">
         <v>-14.14</v>
       </c>
-      <c r="L10" s="116">
+      <c r="L10" s="114">
         <v>-19.62</v>
       </c>
-      <c r="M10" s="112">
+      <c r="M10" s="115">
         <v>-20.09</v>
       </c>
       <c r="N10" s="108">
         <v>-18.71</v>
       </c>
-      <c r="O10" s="106">
+      <c r="O10" s="116">
         <v>-18.89</v>
       </c>
-      <c r="P10" s="107">
+      <c r="P10" s="109">
         <v>-19.15</v>
       </c>
-      <c r="Q10" s="113">
+      <c r="Q10" s="105">
         <v>-20.42</v>
       </c>
-      <c r="R10" s="109">
+      <c r="R10" s="110">
         <v>-17.25</v>
       </c>
-      <c r="S10" s="117">
+      <c r="S10" s="111">
         <v>-11.14</v>
       </c>
-      <c r="T10" s="110">
-        <v>-17.43</v>
+      <c r="T10" s="112">
+        <v>-19.47</v>
       </c>
     </row>
     <row r="11">
@@ -6120,7 +6120,7 @@
       <c r="C11" t="str">
         <v>600330</v>
       </c>
-      <c r="D11" s="126" t="str">
+      <c r="D11" s="119" t="str">
         <v>净卖: -6191.34万</v>
       </c>
       <c r="E11">
@@ -6135,41 +6135,41 @@
       <c r="H11">
         <v>10</v>
       </c>
-      <c r="I11" s="119">
+      <c r="I11" s="120">
         <v>-5.66</v>
       </c>
-      <c r="J11" s="120">
+      <c r="J11" s="129">
         <v>3.77</v>
       </c>
-      <c r="K11" s="122">
+      <c r="K11" s="125">
         <v>-0.51</v>
       </c>
-      <c r="L11" s="123">
+      <c r="L11" s="130">
         <v>-7.72</v>
       </c>
-      <c r="M11" s="129">
+      <c r="M11" s="121">
         <v>-10.89</v>
       </c>
-      <c r="N11" s="124">
+      <c r="N11" s="126">
         <v>-6.43</v>
       </c>
-      <c r="O11" s="121">
+      <c r="O11" s="118">
         <v>-8.23</v>
       </c>
-      <c r="P11" s="125">
+      <c r="P11" s="122">
         <v>-3.77</v>
       </c>
-      <c r="Q11" s="130">
+      <c r="Q11" s="127">
         <v>-2.23</v>
       </c>
-      <c r="R11" s="127">
+      <c r="R11" s="128">
         <v>-1.63</v>
       </c>
-      <c r="S11" s="128">
+      <c r="S11" s="123">
         <v>-0.77</v>
       </c>
-      <c r="T11" s="118">
-        <v>122.04</v>
+      <c r="T11" s="124">
+        <v>135.16</v>
       </c>
     </row>
     <row r="12">
@@ -6182,7 +6182,7 @@
       <c r="C12" t="str">
         <v>600635</v>
       </c>
-      <c r="D12" s="142" t="str">
+      <c r="D12" s="134" t="str">
         <v>净买: 2557.50万</v>
       </c>
       <c r="E12">
@@ -6197,41 +6197,41 @@
       <c r="H12">
         <v>2.91</v>
       </c>
-      <c r="I12" s="134">
+      <c r="I12" s="142">
         <v>6.98</v>
       </c>
-      <c r="J12" s="141">
+      <c r="J12" s="135">
         <v>10.75</v>
       </c>
-      <c r="K12" s="137">
+      <c r="K12" s="138">
         <v>21.89</v>
       </c>
-      <c r="L12" s="138">
+      <c r="L12" s="143">
         <v>34.15</v>
       </c>
-      <c r="M12" s="143">
+      <c r="M12" s="139">
         <v>34.15</v>
       </c>
       <c r="N12" s="131">
         <v>30.38</v>
       </c>
-      <c r="O12" s="132">
+      <c r="O12" s="140">
         <v>28.49</v>
       </c>
-      <c r="P12" s="135">
+      <c r="P12" s="136">
         <v>23.58</v>
       </c>
-      <c r="Q12" s="139">
+      <c r="Q12" s="137">
         <v>17.74</v>
       </c>
-      <c r="R12" s="136">
+      <c r="R12" s="132">
         <v>29.43</v>
       </c>
       <c r="S12" s="133">
         <v>33.77</v>
       </c>
-      <c r="T12" s="140">
-        <v>0.57</v>
+      <c r="T12" s="141">
+        <v>1.13</v>
       </c>
     </row>
     <row r="13">
@@ -6244,7 +6244,7 @@
       <c r="C13" t="str">
         <v>002488</v>
       </c>
-      <c r="D13" s="150" t="str">
+      <c r="D13" s="152" t="str">
         <v>净卖: -1403.24万</v>
       </c>
       <c r="E13">
@@ -6259,41 +6259,41 @@
       <c r="H13">
         <v>-0.57</v>
       </c>
-      <c r="I13" s="156">
+      <c r="I13" s="146">
         <v>-9.51</v>
       </c>
-      <c r="J13" s="147">
+      <c r="J13" s="155">
         <v>-0.49</v>
       </c>
-      <c r="K13" s="144">
+      <c r="K13" s="153">
         <v>-8.7</v>
       </c>
-      <c r="L13" s="145">
+      <c r="L13" s="154">
         <v>-14.88</v>
       </c>
-      <c r="M13" s="151">
+      <c r="M13" s="147">
         <v>-14.96</v>
       </c>
-      <c r="N13" s="146">
+      <c r="N13" s="150">
         <v>-18.86</v>
       </c>
-      <c r="O13" s="152">
+      <c r="O13" s="156">
         <v>-19.92</v>
       </c>
-      <c r="P13" s="153">
+      <c r="P13" s="148">
         <v>-18.54</v>
       </c>
-      <c r="Q13" s="155">
+      <c r="Q13" s="144">
         <v>-17.24</v>
       </c>
-      <c r="R13" s="148">
+      <c r="R13" s="145">
         <v>-15.93</v>
       </c>
-      <c r="S13" s="154">
+      <c r="S13" s="151">
         <v>-17.15</v>
       </c>
       <c r="T13" s="149">
-        <v>-7.07</v>
+        <v>-3.66</v>
       </c>
     </row>
     <row r="14">
@@ -6306,7 +6306,7 @@
       <c r="C14" t="str">
         <v>301246</v>
       </c>
-      <c r="D14" s="163" t="str">
+      <c r="D14" s="159" t="str">
         <v>净卖: -752.38万</v>
       </c>
       <c r="E14">
@@ -6321,41 +6321,41 @@
       <c r="H14">
         <v>-2.99</v>
       </c>
-      <c r="I14" s="165">
+      <c r="I14" s="164">
         <v>23.71</v>
       </c>
-      <c r="J14" s="166">
+      <c r="J14" s="165">
         <v>15.87</v>
       </c>
-      <c r="K14" s="160">
+      <c r="K14" s="166">
         <v>21.68</v>
       </c>
-      <c r="L14" s="167">
+      <c r="L14" s="160">
         <v>20.7</v>
       </c>
-      <c r="M14" s="164">
+      <c r="M14" s="157">
         <v>16.22</v>
       </c>
-      <c r="N14" s="169">
+      <c r="N14" s="167">
         <v>18.95</v>
       </c>
-      <c r="O14" s="157">
+      <c r="O14" s="161">
         <v>19.79</v>
       </c>
-      <c r="P14" s="161">
+      <c r="P14" s="158">
         <v>17.41</v>
       </c>
-      <c r="Q14" s="158">
+      <c r="Q14" s="162">
         <v>19.79</v>
       </c>
-      <c r="R14" s="159">
+      <c r="R14" s="168">
         <v>15.38</v>
       </c>
-      <c r="S14" s="162">
+      <c r="S14" s="169">
         <v>18.25</v>
       </c>
-      <c r="T14" s="168">
-        <v>71.05</v>
+      <c r="T14" s="163">
+        <v>78.53</v>
       </c>
     </row>
     <row r="15">
@@ -6368,7 +6368,7 @@
       <c r="C15" t="str">
         <v>002198</v>
       </c>
-      <c r="D15" s="181" t="str">
+      <c r="D15" s="171" t="str">
         <v>净买: 1396.06万</v>
       </c>
       <c r="E15">
@@ -6383,19 +6383,19 @@
       <c r="H15">
         <v>9.79</v>
       </c>
-      <c r="I15" s="171">
+      <c r="I15" s="177">
         <v>0.24</v>
       </c>
-      <c r="J15" s="175">
+      <c r="J15" s="178">
         <v>-9.75</v>
       </c>
-      <c r="K15" s="176">
+      <c r="K15" s="179">
         <v>-16.17</v>
       </c>
-      <c r="L15" s="177">
+      <c r="L15" s="180">
         <v>-16.77</v>
       </c>
-      <c r="M15" s="182">
+      <c r="M15" s="181">
         <v>-20.33</v>
       </c>
       <c r="N15" s="172">
@@ -6404,20 +6404,20 @@
       <c r="O15" s="173">
         <v>-12.72</v>
       </c>
-      <c r="P15" s="170">
+      <c r="P15" s="175">
         <v>-11.18</v>
       </c>
-      <c r="Q15" s="178">
+      <c r="Q15" s="182">
         <v>-10.7</v>
       </c>
-      <c r="R15" s="179">
+      <c r="R15" s="174">
         <v>-10.23</v>
       </c>
-      <c r="S15" s="180">
+      <c r="S15" s="176">
         <v>-11.77</v>
       </c>
-      <c r="T15" s="174">
-        <v>-14.98</v>
+      <c r="T15" s="170">
+        <v>-21.64</v>
       </c>
     </row>
     <row r="16">
@@ -6430,7 +6430,7 @@
       <c r="C16" t="str">
         <v>002114</v>
       </c>
-      <c r="D16" s="191" t="str">
+      <c r="D16" s="188" t="str">
         <v>净卖: -121.61万</v>
       </c>
       <c r="E16">
@@ -6445,41 +6445,41 @@
       <c r="H16">
         <v>9.95</v>
       </c>
-      <c r="I16" s="185">
+      <c r="I16" s="194">
         <v>0</v>
       </c>
-      <c r="J16" s="186">
+      <c r="J16" s="187">
         <v>-9.98</v>
       </c>
-      <c r="K16" s="183">
+      <c r="K16" s="189">
         <v>-15.64</v>
       </c>
-      <c r="L16" s="188">
+      <c r="L16" s="190">
         <v>-7.2</v>
       </c>
-      <c r="M16" s="189">
+      <c r="M16" s="191">
         <v>-9.16</v>
       </c>
-      <c r="N16" s="192">
+      <c r="N16" s="184">
         <v>-5.66</v>
       </c>
-      <c r="O16" s="190">
+      <c r="O16" s="185">
         <v>-7.3</v>
       </c>
-      <c r="P16" s="187">
+      <c r="P16" s="195">
         <v>-3.4</v>
       </c>
-      <c r="Q16" s="184">
+      <c r="Q16" s="183">
         <v>-6.17</v>
       </c>
-      <c r="R16" s="193">
+      <c r="R16" s="192">
         <v>-11.73</v>
       </c>
-      <c r="S16" s="194">
+      <c r="S16" s="193">
         <v>-10.7</v>
       </c>
-      <c r="T16" s="195">
-        <v>-7</v>
+      <c r="T16" s="186">
+        <v>-6.58</v>
       </c>
     </row>
     <row r="17">
@@ -6492,7 +6492,7 @@
       <c r="C17" t="str">
         <v>603815</v>
       </c>
-      <c r="D17" s="199" t="str">
+      <c r="D17" s="207" t="str">
         <v>净卖: -1097.64万</v>
       </c>
       <c r="E17">
@@ -6507,41 +6507,41 @@
       <c r="H17">
         <v>0.09</v>
       </c>
-      <c r="I17" s="200">
+      <c r="I17" s="204">
         <v>9.95</v>
       </c>
-      <c r="J17" s="206">
+      <c r="J17" s="199">
         <v>12.93</v>
       </c>
-      <c r="K17" s="201">
+      <c r="K17" s="208">
         <v>12.57</v>
       </c>
-      <c r="L17" s="207">
+      <c r="L17" s="205">
         <v>17.45</v>
       </c>
-      <c r="M17" s="208">
+      <c r="M17" s="200">
         <v>9.76</v>
       </c>
-      <c r="N17" s="196">
+      <c r="N17" s="201">
         <v>9.22</v>
       </c>
-      <c r="O17" s="202">
+      <c r="O17" s="196">
         <v>-1.72</v>
       </c>
-      <c r="P17" s="203">
+      <c r="P17" s="197">
         <v>-11.57</v>
       </c>
-      <c r="Q17" s="204">
+      <c r="Q17" s="202">
         <v>-15.01</v>
       </c>
-      <c r="R17" s="205">
+      <c r="R17" s="203">
         <v>-21.52</v>
       </c>
-      <c r="S17" s="197">
+      <c r="S17" s="198">
         <v>-23.87</v>
       </c>
-      <c r="T17" s="198">
-        <v>-35.44</v>
+      <c r="T17" s="206">
+        <v>-37.52</v>
       </c>
     </row>
     <row r="18">
@@ -6554,7 +6554,7 @@
       <c r="C18" t="str">
         <v>000890</v>
       </c>
-      <c r="D18" s="217" t="str">
+      <c r="D18" s="218" t="str">
         <v>净买: 1092.74万</v>
       </c>
       <c r="E18">
@@ -6569,41 +6569,41 @@
       <c r="H18">
         <v>10.05</v>
       </c>
-      <c r="I18" s="218">
+      <c r="I18" s="216">
         <v>0</v>
       </c>
-      <c r="J18" s="219">
+      <c r="J18" s="217">
         <v>10.06</v>
       </c>
-      <c r="K18" s="213">
+      <c r="K18" s="210">
         <v>11.46</v>
       </c>
-      <c r="L18" s="221">
+      <c r="L18" s="211">
         <v>0.31</v>
       </c>
-      <c r="M18" s="209">
+      <c r="M18" s="219">
         <v>-9.75</v>
       </c>
-      <c r="N18" s="210">
+      <c r="N18" s="214">
         <v>-9.6</v>
       </c>
-      <c r="O18" s="214">
+      <c r="O18" s="220">
         <v>-16.41</v>
       </c>
-      <c r="P18" s="215">
+      <c r="P18" s="221">
         <v>-14.24</v>
       </c>
-      <c r="Q18" s="216">
+      <c r="Q18" s="212">
         <v>-15.63</v>
       </c>
-      <c r="R18" s="220">
+      <c r="R18" s="213">
         <v>-16.87</v>
       </c>
-      <c r="S18" s="211">
+      <c r="S18" s="209">
         <v>-19.81</v>
       </c>
-      <c r="T18" s="212">
-        <v>151.39</v>
+      <c r="T18" s="215">
+        <v>155.57</v>
       </c>
     </row>
     <row r="19">
@@ -6616,7 +6616,7 @@
       <c r="C19" t="str">
         <v>603067</v>
       </c>
-      <c r="D19" s="222" t="str">
+      <c r="D19" s="234" t="str">
         <v>净买: 1179.50万</v>
       </c>
       <c r="E19">
@@ -6631,41 +6631,41 @@
       <c r="H19">
         <v>-3.07</v>
       </c>
-      <c r="I19" s="225">
+      <c r="I19" s="224">
         <v>-5.37</v>
       </c>
-      <c r="J19" s="226">
+      <c r="J19" s="225">
         <v>-2.17</v>
       </c>
-      <c r="K19" s="228">
+      <c r="K19" s="231">
         <v>6.55</v>
       </c>
-      <c r="L19" s="229">
+      <c r="L19" s="226">
         <v>4.84</v>
       </c>
-      <c r="M19" s="227">
+      <c r="M19" s="222">
         <v>11.14</v>
       </c>
-      <c r="N19" s="234">
+      <c r="N19" s="232">
         <v>10.82</v>
       </c>
-      <c r="O19" s="230">
+      <c r="O19" s="228">
         <v>9.93</v>
       </c>
-      <c r="P19" s="223">
+      <c r="P19" s="229">
         <v>6.01</v>
       </c>
-      <c r="Q19" s="224">
+      <c r="Q19" s="230">
         <v>3.17</v>
       </c>
-      <c r="R19" s="231">
+      <c r="R19" s="233">
         <v>2.53</v>
       </c>
-      <c r="S19" s="232">
+      <c r="S19" s="227">
         <v>12.78</v>
       </c>
-      <c r="T19" s="233">
-        <v>33.42</v>
+      <c r="T19" s="223">
+        <v>28.86</v>
       </c>
     </row>
     <row r="20">
@@ -6678,7 +6678,7 @@
       <c r="C20" t="str">
         <v>000890</v>
       </c>
-      <c r="D20" s="246" t="str">
+      <c r="D20" s="235" t="str">
         <v>净买: 1030.64万</v>
       </c>
       <c r="E20">
@@ -6693,41 +6693,41 @@
       <c r="H20">
         <v>-9.72</v>
       </c>
-      <c r="I20" s="236">
+      <c r="I20" s="243">
         <v>-0.31</v>
       </c>
-      <c r="J20" s="237">
+      <c r="J20" s="236">
         <v>-10.31</v>
       </c>
-      <c r="K20" s="247">
+      <c r="K20" s="237">
         <v>-10.15</v>
       </c>
-      <c r="L20" s="243">
+      <c r="L20" s="244">
         <v>-16.92</v>
       </c>
-      <c r="M20" s="240">
+      <c r="M20" s="245">
         <v>-14.77</v>
       </c>
       <c r="N20" s="238">
         <v>-16.15</v>
       </c>
-      <c r="O20" s="244">
+      <c r="O20" s="239">
         <v>-17.38</v>
       </c>
-      <c r="P20" s="235">
+      <c r="P20" s="240">
         <v>-20.31</v>
       </c>
-      <c r="Q20" s="245">
+      <c r="Q20" s="246">
         <v>-20.62</v>
       </c>
       <c r="R20" s="241">
         <v>-22</v>
       </c>
-      <c r="S20" s="239">
+      <c r="S20" s="247">
         <v>-21.69</v>
       </c>
       <c r="T20" s="242">
-        <v>149.85</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21">
@@ -6740,7 +6740,7 @@
       <c r="C21" t="str">
         <v>000890</v>
       </c>
-      <c r="D21" s="255" t="str">
+      <c r="D21" s="251" t="str">
         <v>净卖: -1045.40万</v>
       </c>
       <c r="E21">
@@ -6755,41 +6755,41 @@
       <c r="H21">
         <v>-4.94</v>
       </c>
-      <c r="I21" s="250">
+      <c r="I21" s="248">
         <v>-5.36</v>
       </c>
-      <c r="J21" s="251">
+      <c r="J21" s="249">
         <v>-5.19</v>
       </c>
-      <c r="K21" s="256">
+      <c r="K21" s="254">
         <v>-12.34</v>
       </c>
-      <c r="L21" s="257">
+      <c r="L21" s="258">
         <v>-10.06</v>
       </c>
-      <c r="M21" s="258">
+      <c r="M21" s="252">
         <v>-11.53</v>
       </c>
-      <c r="N21" s="252">
+      <c r="N21" s="250">
         <v>-12.82</v>
       </c>
       <c r="O21" s="259">
         <v>-15.91</v>
       </c>
-      <c r="P21" s="260">
+      <c r="P21" s="255">
         <v>-16.23</v>
       </c>
-      <c r="Q21" s="248">
+      <c r="Q21" s="256">
         <v>-17.69</v>
       </c>
       <c r="R21" s="253">
         <v>-17.37</v>
       </c>
-      <c r="S21" s="254">
+      <c r="S21" s="260">
         <v>-16.23</v>
       </c>
-      <c r="T21" s="249">
-        <v>163.64</v>
+      <c r="T21" s="257">
+        <v>168.02</v>
       </c>
     </row>
     <row r="22">
@@ -6802,7 +6802,7 @@
       <c r="C22" t="str">
         <v>300409</v>
       </c>
-      <c r="D22" s="264" t="str">
+      <c r="D22" s="268" t="str">
         <v>净卖: -3259.20万</v>
       </c>
       <c r="E22">
@@ -6817,41 +6817,41 @@
       <c r="H22">
         <v>4.54</v>
       </c>
-      <c r="I22" s="265">
+      <c r="I22" s="269">
         <v>14.8</v>
       </c>
-      <c r="J22" s="261">
+      <c r="J22" s="270">
         <v>31.48</v>
       </c>
-      <c r="K22" s="267">
+      <c r="K22" s="263">
         <v>32.5</v>
       </c>
-      <c r="L22" s="271">
+      <c r="L22" s="272">
         <v>30.84</v>
       </c>
-      <c r="M22" s="268">
+      <c r="M22" s="264">
         <v>23.86</v>
       </c>
-      <c r="N22" s="272">
+      <c r="N22" s="271">
         <v>48.62</v>
       </c>
-      <c r="O22" s="262">
+      <c r="O22" s="273">
         <v>46.11</v>
       </c>
-      <c r="P22" s="266">
+      <c r="P22" s="261">
         <v>41.64</v>
       </c>
-      <c r="Q22" s="273">
+      <c r="Q22" s="265">
         <v>42.15</v>
       </c>
-      <c r="R22" s="269">
+      <c r="R22" s="262">
         <v>36.03</v>
       </c>
-      <c r="S22" s="263">
+      <c r="S22" s="266">
         <v>31.9</v>
       </c>
-      <c r="T22" s="270">
-        <v>13.61</v>
+      <c r="T22" s="267">
+        <v>15.48</v>
       </c>
     </row>
     <row r="23">
@@ -6864,7 +6864,7 @@
       <c r="C23" t="str">
         <v>300409</v>
       </c>
-      <c r="D23" s="277" t="str">
+      <c r="D23" s="275" t="str">
         <v>净卖: -3736.61万</v>
       </c>
       <c r="E23">
@@ -6879,41 +6879,41 @@
       <c r="H23">
         <v>4.22</v>
       </c>
-      <c r="I23" s="283">
+      <c r="I23" s="281">
         <v>9.88</v>
       </c>
-      <c r="J23" s="284">
+      <c r="J23" s="276">
         <v>10.74</v>
       </c>
-      <c r="K23" s="278">
+      <c r="K23" s="283">
         <v>9.35</v>
       </c>
-      <c r="L23" s="279">
+      <c r="L23" s="284">
         <v>3.52</v>
       </c>
-      <c r="M23" s="274">
+      <c r="M23" s="285">
         <v>24.21</v>
       </c>
-      <c r="N23" s="280">
+      <c r="N23" s="286">
         <v>22.11</v>
       </c>
-      <c r="O23" s="281">
+      <c r="O23" s="282">
         <v>18.38</v>
       </c>
-      <c r="P23" s="285">
+      <c r="P23" s="279">
         <v>18.81</v>
       </c>
-      <c r="Q23" s="276">
+      <c r="Q23" s="277">
         <v>13.69</v>
       </c>
-      <c r="R23" s="275">
+      <c r="R23" s="280">
         <v>10.24</v>
       </c>
-      <c r="S23" s="282">
+      <c r="S23" s="278">
         <v>8</v>
       </c>
-      <c r="T23" s="286">
-        <v>-5.05</v>
+      <c r="T23" s="274">
+        <v>-3.48</v>
       </c>
     </row>
     <row r="24">
@@ -6926,7 +6926,7 @@
       <c r="C24" t="str">
         <v>300409</v>
       </c>
-      <c r="D24" s="298" t="str">
+      <c r="D24" s="288" t="str">
         <v>净卖: -2006.10万</v>
       </c>
       <c r="E24">
@@ -6941,41 +6941,41 @@
       <c r="H24">
         <v>1.68</v>
       </c>
-      <c r="I24" s="288">
+      <c r="I24" s="297">
         <v>18</v>
       </c>
       <c r="J24" s="289">
         <v>16.01</v>
       </c>
-      <c r="K24" s="295">
+      <c r="K24" s="290">
         <v>12.46</v>
       </c>
-      <c r="L24" s="290">
+      <c r="L24" s="295">
         <v>12.87</v>
       </c>
-      <c r="M24" s="296">
+      <c r="M24" s="298">
         <v>8</v>
       </c>
       <c r="N24" s="291">
         <v>4.73</v>
       </c>
-      <c r="O24" s="299">
+      <c r="O24" s="292">
         <v>2.6</v>
       </c>
-      <c r="P24" s="292">
+      <c r="P24" s="293">
         <v>1.82</v>
       </c>
-      <c r="Q24" s="293">
+      <c r="Q24" s="296">
         <v>2.36</v>
       </c>
-      <c r="R24" s="287">
+      <c r="R24" s="299">
         <v>8.11</v>
       </c>
-      <c r="S24" s="297">
+      <c r="S24" s="287">
         <v>5.67</v>
       </c>
       <c r="T24" s="294">
-        <v>-9.79</v>
+        <v>-8.31</v>
       </c>
     </row>
     <row r="25">
@@ -7037,40 +7037,40 @@
       <c r="F26" t="str"/>
       <c r="G26" t="str"/>
       <c r="H26" t="str"/>
-      <c r="I26" s="310">
+      <c r="I26" s="306">
         <v>52.17</v>
       </c>
-      <c r="J26" s="311">
+      <c r="J26" s="308">
         <v>52.17</v>
       </c>
-      <c r="K26" s="300">
+      <c r="K26" s="307">
         <v>52.17</v>
       </c>
-      <c r="L26" s="305">
+      <c r="L26" s="302">
         <v>47.83</v>
       </c>
-      <c r="M26" s="306">
+      <c r="M26" s="310">
         <v>43.48</v>
       </c>
-      <c r="N26" s="303">
+      <c r="N26" s="311">
         <v>39.13</v>
       </c>
-      <c r="O26" s="307">
+      <c r="O26" s="303">
         <v>34.78</v>
       </c>
-      <c r="P26" s="308">
+      <c r="P26" s="300">
         <v>39.13</v>
       </c>
-      <c r="Q26" s="302">
+      <c r="Q26" s="301">
         <v>39.13</v>
       </c>
       <c r="R26" s="304">
         <v>39.13</v>
       </c>
-      <c r="S26" s="309">
+      <c r="S26" s="305">
         <v>39.13</v>
       </c>
-      <c r="T26" s="301">
+      <c r="T26" s="309">
         <v>47.83</v>
       </c>
     </row>
@@ -7085,41 +7085,41 @@
       <c r="F27" t="str"/>
       <c r="G27" t="str"/>
       <c r="H27" t="str"/>
-      <c r="I27" s="315">
+      <c r="I27" s="318">
         <v>3.46</v>
       </c>
-      <c r="J27" s="318">
+      <c r="J27" s="320">
         <v>2.89</v>
       </c>
-      <c r="K27" s="316">
+      <c r="K27" s="321">
         <v>0.67</v>
       </c>
-      <c r="L27" s="312">
+      <c r="L27" s="315">
         <v>-0.46</v>
       </c>
-      <c r="M27" s="319">
+      <c r="M27" s="322">
         <v>-1.36</v>
       </c>
-      <c r="N27" s="321">
+      <c r="N27" s="319">
         <v>-0.02</v>
       </c>
-      <c r="O27" s="320">
+      <c r="O27" s="312">
         <v>-1.62</v>
       </c>
-      <c r="P27" s="313">
+      <c r="P27" s="316">
         <v>-2.08</v>
       </c>
-      <c r="Q27" s="314">
+      <c r="Q27" s="317">
         <v>-2.45</v>
       </c>
-      <c r="R27" s="322">
+      <c r="R27" s="323">
         <v>-2.62</v>
       </c>
-      <c r="S27" s="323">
+      <c r="S27" s="313">
         <v>-1.7</v>
       </c>
-      <c r="T27" s="317">
-        <v>24.88</v>
+      <c r="T27" s="314">
+        <v>26.09</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/王海祥/index.xlsx
+++ b/youzi/王海祥/index.xlsx
@@ -39,66 +39,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCC2E3D"/>
         <bgColor/>
       </patternFill>
@@ -117,31 +63,637 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE3626E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE3626E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE3626E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF62BE77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47B460"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF57BA6E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3A49"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3747"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCEEBD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -153,19 +705,1099 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF68C17C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF5F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC380"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3B4A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6707C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -177,139 +1809,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF47B460"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF57BA6E"/>
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF72C585"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -321,811 +1851,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF62BE77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3A49"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCEEBD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3747"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF61BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF5F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF208838"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0EBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0EBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC380"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCFEFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1137,391 +1935,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF269F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC380"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3B4A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF50B768"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1533,384 +1953,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6707C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0EBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208838"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0EBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF72C585"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF50B768"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF48B460"/>
         <bgColor/>
       </patternFill>
@@ -1923,55 +1965,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCFEFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC380"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -5562,7 +5562,7 @@
       <c r="C2" t="str">
         <v>002276</v>
       </c>
-      <c r="D2" s="2" t="str">
+      <c r="D2" s="1" t="str">
         <v>净卖: -3245.54万</v>
       </c>
       <c r="E2">
@@ -5577,41 +5577,41 @@
       <c r="H2">
         <v>3.37</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="2">
         <v>6.43</v>
       </c>
       <c r="J2" s="7">
         <v>17.1</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="8">
         <v>11.56</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2" s="9">
         <v>22.72</v>
       </c>
-      <c r="M2" s="3">
+      <c r="M2" s="10">
         <v>30.54</v>
       </c>
-      <c r="N2" s="13">
+      <c r="N2" s="11">
         <v>43.57</v>
       </c>
-      <c r="O2" s="4">
+      <c r="O2" s="3">
         <v>42.1</v>
       </c>
-      <c r="P2" s="9">
+      <c r="P2" s="4">
         <v>40.15</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="12">
         <v>33.31</v>
       </c>
-      <c r="R2" s="5">
+      <c r="R2" s="13">
         <v>34.45</v>
       </c>
-      <c r="S2" s="10">
+      <c r="S2" s="5">
         <v>40.8</v>
       </c>
       <c r="T2" s="6">
-        <v>10.83</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="3">
@@ -5624,7 +5624,7 @@
       <c r="C3" t="str">
         <v>601279</v>
       </c>
-      <c r="D3" s="15" t="str">
+      <c r="D3" s="25" t="str">
         <v>净卖: -85.25万</v>
       </c>
       <c r="E3">
@@ -5639,41 +5639,41 @@
       <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="26">
         <v>10.15</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="23">
         <v>5.97</v>
       </c>
-      <c r="K3" s="20">
+      <c r="K3" s="14">
         <v>4.48</v>
       </c>
       <c r="L3" s="16">
         <v>3.88</v>
       </c>
-      <c r="M3" s="21">
+      <c r="M3" s="17">
         <v>4.18</v>
       </c>
-      <c r="N3" s="14">
+      <c r="N3" s="15">
         <v>3.88</v>
       </c>
-      <c r="O3" s="23">
+      <c r="O3" s="18">
         <v>5.67</v>
       </c>
-      <c r="P3" s="24">
+      <c r="P3" s="19">
         <v>5.07</v>
       </c>
-      <c r="Q3" s="17">
+      <c r="Q3" s="20">
         <v>4.78</v>
       </c>
-      <c r="R3" s="25">
+      <c r="R3" s="21">
         <v>2.09</v>
       </c>
-      <c r="S3" s="18">
+      <c r="S3" s="24">
         <v>4.18</v>
       </c>
-      <c r="T3" s="26">
-        <v>17.01</v>
+      <c r="T3" s="22">
+        <v>15.22</v>
       </c>
     </row>
     <row r="4">
@@ -5686,7 +5686,7 @@
       <c r="C4" t="str">
         <v>003020</v>
       </c>
-      <c r="D4" s="36" t="str">
+      <c r="D4" s="28" t="str">
         <v>净买: 1240.36万</v>
       </c>
       <c r="E4">
@@ -5701,41 +5701,41 @@
       <c r="H4">
         <v>-3.75</v>
       </c>
-      <c r="I4" s="37">
+      <c r="I4" s="35">
         <v>-6.49</v>
       </c>
-      <c r="J4" s="34">
+      <c r="J4" s="29">
         <v>-15.84</v>
       </c>
-      <c r="K4" s="27">
+      <c r="K4" s="37">
         <v>-23.08</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="32">
         <v>-24.06</v>
       </c>
-      <c r="M4" s="38">
+      <c r="M4" s="30">
         <v>-21.79</v>
       </c>
-      <c r="N4" s="28">
+      <c r="N4" s="33">
         <v>-20.71</v>
       </c>
-      <c r="O4" s="29">
+      <c r="O4" s="36">
         <v>-22.89</v>
       </c>
-      <c r="P4" s="32">
+      <c r="P4" s="34">
         <v>-24.61</v>
       </c>
-      <c r="Q4" s="33">
+      <c r="Q4" s="31">
         <v>-23.38</v>
       </c>
-      <c r="R4" s="30">
+      <c r="R4" s="38">
         <v>-24.35</v>
       </c>
-      <c r="S4" s="35">
+      <c r="S4" s="39">
         <v>-22.4</v>
       </c>
-      <c r="T4" s="39">
-        <v>-24.38</v>
+      <c r="T4" s="27">
+        <v>-26.62</v>
       </c>
     </row>
     <row r="5">
@@ -5748,7 +5748,7 @@
       <c r="C5" t="str">
         <v>003020</v>
       </c>
-      <c r="D5" s="45" t="str">
+      <c r="D5" s="51" t="str">
         <v>净买: 1925.03万</v>
       </c>
       <c r="E5">
@@ -5763,41 +5763,41 @@
       <c r="H5">
         <v>-4.9</v>
       </c>
-      <c r="I5" s="46">
+      <c r="I5" s="52">
         <v>-3.89</v>
       </c>
-      <c r="J5" s="50">
+      <c r="J5" s="43">
         <v>-5.11</v>
       </c>
-      <c r="K5" s="48">
+      <c r="K5" s="44">
         <v>-2.27</v>
       </c>
-      <c r="L5" s="51">
+      <c r="L5" s="40">
         <v>-0.93</v>
       </c>
-      <c r="M5" s="52">
+      <c r="M5" s="41">
         <v>-3.65</v>
       </c>
-      <c r="N5" s="49">
+      <c r="N5" s="47">
         <v>-5.8</v>
       </c>
-      <c r="O5" s="42">
+      <c r="O5" s="48">
         <v>-4.26</v>
       </c>
-      <c r="P5" s="47">
+      <c r="P5" s="45">
         <v>-5.48</v>
       </c>
-      <c r="Q5" s="40">
+      <c r="Q5" s="46">
         <v>-3.04</v>
       </c>
-      <c r="R5" s="43">
+      <c r="R5" s="42">
         <v>-2.07</v>
       </c>
-      <c r="S5" s="41">
+      <c r="S5" s="49">
         <v>-0.97</v>
       </c>
-      <c r="T5" s="44">
-        <v>-5.52</v>
+      <c r="T5" s="50">
+        <v>-8.32</v>
       </c>
     </row>
     <row r="6">
@@ -5810,7 +5810,7 @@
       <c r="C6" t="str">
         <v>603607</v>
       </c>
-      <c r="D6" s="53" t="str">
+      <c r="D6" s="58" t="str">
         <v>净卖: -1819.82万</v>
       </c>
       <c r="E6">
@@ -5825,31 +5825,31 @@
       <c r="H6">
         <v>9.92</v>
       </c>
-      <c r="I6" s="60">
+      <c r="I6" s="57">
         <v>0.06</v>
       </c>
-      <c r="J6" s="57">
+      <c r="J6" s="59">
         <v>4.62</v>
       </c>
-      <c r="K6" s="58">
+      <c r="K6" s="60">
         <v>4.87</v>
       </c>
-      <c r="L6" s="54">
+      <c r="L6" s="53">
         <v>-5.62</v>
       </c>
-      <c r="M6" s="55">
+      <c r="M6" s="63">
         <v>-15.05</v>
       </c>
-      <c r="N6" s="64">
+      <c r="N6" s="61">
         <v>-13.34</v>
       </c>
-      <c r="O6" s="65">
+      <c r="O6" s="64">
         <v>-18.49</v>
       </c>
-      <c r="P6" s="59">
+      <c r="P6" s="54">
         <v>-19.11</v>
       </c>
-      <c r="Q6" s="61">
+      <c r="Q6" s="55">
         <v>-16.36</v>
       </c>
       <c r="R6" s="62">
@@ -5858,8 +5858,8 @@
       <c r="S6" s="56">
         <v>-10.68</v>
       </c>
-      <c r="T6" s="63">
-        <v>-26.3</v>
+      <c r="T6" s="65">
+        <v>-26.64</v>
       </c>
     </row>
     <row r="7">
@@ -5872,7 +5872,7 @@
       <c r="C7" t="str">
         <v>603607</v>
       </c>
-      <c r="D7" s="73" t="str">
+      <c r="D7" s="66" t="str">
         <v>净卖: -2523.15万</v>
       </c>
       <c r="E7">
@@ -5887,41 +5887,41 @@
       <c r="H7">
         <v>1.49</v>
       </c>
-      <c r="I7" s="75">
+      <c r="I7" s="71">
         <v>-1.24</v>
       </c>
-      <c r="J7" s="76">
+      <c r="J7" s="67">
         <v>-11.12</v>
       </c>
-      <c r="K7" s="67">
+      <c r="K7" s="73">
         <v>-20</v>
       </c>
       <c r="L7" s="68">
         <v>-18.38</v>
       </c>
-      <c r="M7" s="77">
+      <c r="M7" s="74">
         <v>-23.24</v>
       </c>
       <c r="N7" s="69">
         <v>-23.82</v>
       </c>
-      <c r="O7" s="70">
+      <c r="O7" s="75">
         <v>-21.24</v>
       </c>
-      <c r="P7" s="78">
+      <c r="P7" s="76">
         <v>-20.62</v>
       </c>
-      <c r="Q7" s="71">
+      <c r="Q7" s="77">
         <v>-15.88</v>
       </c>
-      <c r="R7" s="66">
+      <c r="R7" s="70">
         <v>-18.09</v>
       </c>
       <c r="S7" s="72">
         <v>-25.41</v>
       </c>
-      <c r="T7" s="74">
-        <v>-30.59</v>
+      <c r="T7" s="78">
+        <v>-30.91</v>
       </c>
     </row>
     <row r="8">
@@ -5934,7 +5934,7 @@
       <c r="C8" t="str">
         <v>603823</v>
       </c>
-      <c r="D8" s="88" t="str">
+      <c r="D8" s="82" t="str">
         <v>净卖: -577.99万</v>
       </c>
       <c r="E8">
@@ -5949,41 +5949,41 @@
       <c r="H8">
         <v>-1.03</v>
       </c>
-      <c r="I8" s="84">
+      <c r="I8" s="87">
         <v>11.19</v>
       </c>
-      <c r="J8" s="80">
+      <c r="J8" s="83">
         <v>10.49</v>
       </c>
-      <c r="K8" s="87">
+      <c r="K8" s="91">
         <v>7.03</v>
       </c>
-      <c r="L8" s="89">
+      <c r="L8" s="84">
         <v>2.34</v>
       </c>
-      <c r="M8" s="90">
+      <c r="M8" s="79">
         <v>4.94</v>
       </c>
-      <c r="N8" s="85">
+      <c r="N8" s="80">
         <v>-1.13</v>
       </c>
-      <c r="O8" s="86">
+      <c r="O8" s="85">
         <v>-2.6</v>
       </c>
-      <c r="P8" s="91">
+      <c r="P8" s="81">
         <v>7.11</v>
       </c>
-      <c r="Q8" s="79">
+      <c r="Q8" s="90">
         <v>11.71</v>
       </c>
-      <c r="R8" s="81">
+      <c r="R8" s="88">
         <v>17.52</v>
       </c>
-      <c r="S8" s="82">
+      <c r="S8" s="86">
         <v>17.43</v>
       </c>
-      <c r="T8" s="83">
-        <v>41.37</v>
+      <c r="T8" s="89">
+        <v>41.28</v>
       </c>
     </row>
     <row r="9">
@@ -5996,7 +5996,7 @@
       <c r="C9" t="str">
         <v>601279</v>
       </c>
-      <c r="D9" s="99" t="str">
+      <c r="D9" s="101" t="str">
         <v>净卖: -624.00万</v>
       </c>
       <c r="E9">
@@ -6011,41 +6011,41 @@
       <c r="H9">
         <v>10.09</v>
       </c>
-      <c r="I9" s="100">
+      <c r="I9" s="93">
         <v>0</v>
       </c>
-      <c r="J9" s="103">
+      <c r="J9" s="99">
         <v>-8.75</v>
       </c>
-      <c r="K9" s="104">
+      <c r="K9" s="102">
         <v>-17.92</v>
       </c>
-      <c r="L9" s="94">
+      <c r="L9" s="98">
         <v>-22.08</v>
       </c>
-      <c r="M9" s="95">
+      <c r="M9" s="94">
         <v>-23.12</v>
       </c>
-      <c r="N9" s="92">
+      <c r="N9" s="95">
         <v>-21.88</v>
       </c>
-      <c r="O9" s="96">
+      <c r="O9" s="103">
         <v>-22.29</v>
       </c>
-      <c r="P9" s="101">
+      <c r="P9" s="96">
         <v>-21.25</v>
       </c>
-      <c r="Q9" s="93">
+      <c r="Q9" s="100">
         <v>-20.62</v>
       </c>
-      <c r="R9" s="102">
+      <c r="R9" s="104">
         <v>-21.25</v>
       </c>
       <c r="S9" s="97">
         <v>-19.37</v>
       </c>
-      <c r="T9" s="98">
-        <v>-18.33</v>
+      <c r="T9" s="92">
+        <v>-19.58</v>
       </c>
     </row>
     <row r="10">
@@ -6058,7 +6058,7 @@
       <c r="C10" t="str">
         <v>600980</v>
       </c>
-      <c r="D10" s="117" t="str">
+      <c r="D10" s="107" t="str">
         <v>净卖: -1981.34万</v>
       </c>
       <c r="E10">
@@ -6073,13 +6073,13 @@
       <c r="H10">
         <v>-0.58</v>
       </c>
-      <c r="I10" s="106">
+      <c r="I10" s="111">
         <v>5.96</v>
       </c>
-      <c r="J10" s="113">
+      <c r="J10" s="108">
         <v>-4.64</v>
       </c>
-      <c r="K10" s="107">
+      <c r="K10" s="109">
         <v>-14.14</v>
       </c>
       <c r="L10" s="114">
@@ -6088,26 +6088,26 @@
       <c r="M10" s="115">
         <v>-20.09</v>
       </c>
-      <c r="N10" s="108">
+      <c r="N10" s="110">
         <v>-18.71</v>
       </c>
-      <c r="O10" s="116">
+      <c r="O10" s="117">
         <v>-18.89</v>
       </c>
-      <c r="P10" s="109">
+      <c r="P10" s="116">
         <v>-19.15</v>
       </c>
-      <c r="Q10" s="105">
+      <c r="Q10" s="112">
         <v>-20.42</v>
       </c>
-      <c r="R10" s="110">
+      <c r="R10" s="113">
         <v>-17.25</v>
       </c>
-      <c r="S10" s="111">
+      <c r="S10" s="105">
         <v>-11.14</v>
       </c>
-      <c r="T10" s="112">
-        <v>-19.47</v>
+      <c r="T10" s="106">
+        <v>-20.09</v>
       </c>
     </row>
     <row r="11">
@@ -6120,7 +6120,7 @@
       <c r="C11" t="str">
         <v>600330</v>
       </c>
-      <c r="D11" s="119" t="str">
+      <c r="D11" s="122" t="str">
         <v>净卖: -6191.34万</v>
       </c>
       <c r="E11">
@@ -6135,41 +6135,41 @@
       <c r="H11">
         <v>10</v>
       </c>
-      <c r="I11" s="120">
+      <c r="I11" s="128">
         <v>-5.66</v>
       </c>
-      <c r="J11" s="129">
+      <c r="J11" s="125">
         <v>3.77</v>
       </c>
-      <c r="K11" s="125">
+      <c r="K11" s="123">
         <v>-0.51</v>
       </c>
-      <c r="L11" s="130">
+      <c r="L11" s="129">
         <v>-7.72</v>
       </c>
-      <c r="M11" s="121">
+      <c r="M11" s="130">
         <v>-10.89</v>
       </c>
-      <c r="N11" s="126">
+      <c r="N11" s="124">
         <v>-6.43</v>
       </c>
-      <c r="O11" s="118">
+      <c r="O11" s="126">
         <v>-8.23</v>
       </c>
-      <c r="P11" s="122">
+      <c r="P11" s="127">
         <v>-3.77</v>
       </c>
-      <c r="Q11" s="127">
+      <c r="Q11" s="120">
         <v>-2.23</v>
       </c>
-      <c r="R11" s="128">
+      <c r="R11" s="121">
         <v>-1.63</v>
       </c>
-      <c r="S11" s="123">
+      <c r="S11" s="118">
         <v>-0.77</v>
       </c>
-      <c r="T11" s="124">
-        <v>135.16</v>
+      <c r="T11" s="119">
+        <v>126.59</v>
       </c>
     </row>
     <row r="12">
@@ -6182,7 +6182,7 @@
       <c r="C12" t="str">
         <v>600635</v>
       </c>
-      <c r="D12" s="134" t="str">
+      <c r="D12" s="143" t="str">
         <v>净买: 2557.50万</v>
       </c>
       <c r="E12">
@@ -6197,41 +6197,41 @@
       <c r="H12">
         <v>2.91</v>
       </c>
-      <c r="I12" s="142">
+      <c r="I12" s="131">
         <v>6.98</v>
       </c>
-      <c r="J12" s="135">
+      <c r="J12" s="132">
         <v>10.75</v>
       </c>
-      <c r="K12" s="138">
+      <c r="K12" s="135">
         <v>21.89</v>
       </c>
-      <c r="L12" s="143">
+      <c r="L12" s="140">
         <v>34.15</v>
       </c>
-      <c r="M12" s="139">
+      <c r="M12" s="141">
         <v>34.15</v>
       </c>
-      <c r="N12" s="131">
+      <c r="N12" s="136">
         <v>30.38</v>
       </c>
-      <c r="O12" s="140">
+      <c r="O12" s="142">
         <v>28.49</v>
       </c>
-      <c r="P12" s="136">
+      <c r="P12" s="137">
         <v>23.58</v>
       </c>
-      <c r="Q12" s="137">
+      <c r="Q12" s="138">
         <v>17.74</v>
       </c>
-      <c r="R12" s="132">
+      <c r="R12" s="133">
         <v>29.43</v>
       </c>
-      <c r="S12" s="133">
+      <c r="S12" s="134">
         <v>33.77</v>
       </c>
-      <c r="T12" s="141">
-        <v>1.13</v>
+      <c r="T12" s="139">
+        <v>1.89</v>
       </c>
     </row>
     <row r="13">
@@ -6244,7 +6244,7 @@
       <c r="C13" t="str">
         <v>002488</v>
       </c>
-      <c r="D13" s="152" t="str">
+      <c r="D13" s="156" t="str">
         <v>净卖: -1403.24万</v>
       </c>
       <c r="E13">
@@ -6259,13 +6259,13 @@
       <c r="H13">
         <v>-0.57</v>
       </c>
-      <c r="I13" s="146">
+      <c r="I13" s="150">
         <v>-9.51</v>
       </c>
-      <c r="J13" s="155">
+      <c r="J13" s="153">
         <v>-0.49</v>
       </c>
-      <c r="K13" s="153">
+      <c r="K13" s="146">
         <v>-8.7</v>
       </c>
       <c r="L13" s="154">
@@ -6274,26 +6274,26 @@
       <c r="M13" s="147">
         <v>-14.96</v>
       </c>
-      <c r="N13" s="150">
+      <c r="N13" s="155">
         <v>-18.86</v>
       </c>
-      <c r="O13" s="156">
+      <c r="O13" s="151">
         <v>-19.92</v>
       </c>
-      <c r="P13" s="148">
+      <c r="P13" s="152">
         <v>-18.54</v>
       </c>
-      <c r="Q13" s="144">
+      <c r="Q13" s="148">
         <v>-17.24</v>
       </c>
-      <c r="R13" s="145">
+      <c r="R13" s="144">
         <v>-15.93</v>
       </c>
-      <c r="S13" s="151">
+      <c r="S13" s="149">
         <v>-17.15</v>
       </c>
-      <c r="T13" s="149">
-        <v>-3.66</v>
+      <c r="T13" s="145">
+        <v>-3.5</v>
       </c>
     </row>
     <row r="14">
@@ -6306,7 +6306,7 @@
       <c r="C14" t="str">
         <v>301246</v>
       </c>
-      <c r="D14" s="159" t="str">
+      <c r="D14" s="164" t="str">
         <v>净卖: -752.38万</v>
       </c>
       <c r="E14">
@@ -6321,41 +6321,41 @@
       <c r="H14">
         <v>-2.99</v>
       </c>
-      <c r="I14" s="164">
+      <c r="I14" s="159">
         <v>23.71</v>
       </c>
-      <c r="J14" s="165">
+      <c r="J14" s="160">
         <v>15.87</v>
       </c>
-      <c r="K14" s="166">
+      <c r="K14" s="161">
         <v>21.68</v>
       </c>
-      <c r="L14" s="160">
+      <c r="L14" s="162">
         <v>20.7</v>
       </c>
-      <c r="M14" s="157">
+      <c r="M14" s="165">
         <v>16.22</v>
       </c>
-      <c r="N14" s="167">
+      <c r="N14" s="169">
         <v>18.95</v>
       </c>
-      <c r="O14" s="161">
+      <c r="O14" s="166">
         <v>19.79</v>
       </c>
-      <c r="P14" s="158">
+      <c r="P14" s="163">
         <v>17.41</v>
       </c>
-      <c r="Q14" s="162">
+      <c r="Q14" s="157">
         <v>19.79</v>
       </c>
-      <c r="R14" s="168">
+      <c r="R14" s="167">
         <v>15.38</v>
       </c>
-      <c r="S14" s="169">
+      <c r="S14" s="168">
         <v>18.25</v>
       </c>
-      <c r="T14" s="163">
-        <v>78.53</v>
+      <c r="T14" s="158">
+        <v>76.22</v>
       </c>
     </row>
     <row r="15">
@@ -6368,7 +6368,7 @@
       <c r="C15" t="str">
         <v>002198</v>
       </c>
-      <c r="D15" s="171" t="str">
+      <c r="D15" s="172" t="str">
         <v>净买: 1396.06万</v>
       </c>
       <c r="E15">
@@ -6383,41 +6383,41 @@
       <c r="H15">
         <v>9.79</v>
       </c>
-      <c r="I15" s="177">
+      <c r="I15" s="181">
         <v>0.24</v>
       </c>
-      <c r="J15" s="178">
+      <c r="J15" s="182">
         <v>-9.75</v>
       </c>
-      <c r="K15" s="179">
+      <c r="K15" s="170">
         <v>-16.17</v>
       </c>
-      <c r="L15" s="180">
+      <c r="L15" s="173">
         <v>-16.77</v>
       </c>
-      <c r="M15" s="181">
+      <c r="M15" s="174">
         <v>-20.33</v>
       </c>
-      <c r="N15" s="172">
+      <c r="N15" s="175">
         <v>-17.72</v>
       </c>
-      <c r="O15" s="173">
+      <c r="O15" s="176">
         <v>-12.72</v>
       </c>
-      <c r="P15" s="175">
+      <c r="P15" s="171">
         <v>-11.18</v>
       </c>
-      <c r="Q15" s="182">
+      <c r="Q15" s="177">
         <v>-10.7</v>
       </c>
-      <c r="R15" s="174">
+      <c r="R15" s="178">
         <v>-10.23</v>
       </c>
-      <c r="S15" s="176">
+      <c r="S15" s="179">
         <v>-11.77</v>
       </c>
-      <c r="T15" s="170">
-        <v>-21.64</v>
+      <c r="T15" s="180">
+        <v>-23.19</v>
       </c>
     </row>
     <row r="16">
@@ -6430,7 +6430,7 @@
       <c r="C16" t="str">
         <v>002114</v>
       </c>
-      <c r="D16" s="188" t="str">
+      <c r="D16" s="187" t="str">
         <v>净卖: -121.61万</v>
       </c>
       <c r="E16">
@@ -6445,41 +6445,41 @@
       <c r="H16">
         <v>9.95</v>
       </c>
-      <c r="I16" s="194">
+      <c r="I16" s="190">
         <v>0</v>
       </c>
-      <c r="J16" s="187">
+      <c r="J16" s="194">
         <v>-9.98</v>
       </c>
-      <c r="K16" s="189">
+      <c r="K16" s="184">
         <v>-15.64</v>
       </c>
-      <c r="L16" s="190">
+      <c r="L16" s="191">
         <v>-7.2</v>
       </c>
-      <c r="M16" s="191">
+      <c r="M16" s="192">
         <v>-9.16</v>
       </c>
-      <c r="N16" s="184">
+      <c r="N16" s="195">
         <v>-5.66</v>
       </c>
-      <c r="O16" s="185">
+      <c r="O16" s="193">
         <v>-7.3</v>
       </c>
-      <c r="P16" s="195">
+      <c r="P16" s="185">
         <v>-3.4</v>
       </c>
       <c r="Q16" s="183">
         <v>-6.17</v>
       </c>
-      <c r="R16" s="192">
+      <c r="R16" s="186">
         <v>-11.73</v>
       </c>
-      <c r="S16" s="193">
+      <c r="S16" s="188">
         <v>-10.7</v>
       </c>
-      <c r="T16" s="186">
-        <v>-6.58</v>
+      <c r="T16" s="189">
+        <v>-8.85</v>
       </c>
     </row>
     <row r="17">
@@ -6492,7 +6492,7 @@
       <c r="C17" t="str">
         <v>603815</v>
       </c>
-      <c r="D17" s="207" t="str">
+      <c r="D17" s="208" t="str">
         <v>净卖: -1097.64万</v>
       </c>
       <c r="E17">
@@ -6507,41 +6507,41 @@
       <c r="H17">
         <v>0.09</v>
       </c>
-      <c r="I17" s="204">
+      <c r="I17" s="206">
         <v>9.95</v>
       </c>
       <c r="J17" s="199">
         <v>12.93</v>
       </c>
-      <c r="K17" s="208">
+      <c r="K17" s="196">
         <v>12.57</v>
       </c>
-      <c r="L17" s="205">
+      <c r="L17" s="200">
         <v>17.45</v>
       </c>
-      <c r="M17" s="200">
+      <c r="M17" s="197">
         <v>9.76</v>
       </c>
-      <c r="N17" s="201">
+      <c r="N17" s="204">
         <v>9.22</v>
       </c>
-      <c r="O17" s="196">
+      <c r="O17" s="198">
         <v>-1.72</v>
       </c>
-      <c r="P17" s="197">
+      <c r="P17" s="201">
         <v>-11.57</v>
       </c>
-      <c r="Q17" s="202">
+      <c r="Q17" s="207">
         <v>-15.01</v>
       </c>
-      <c r="R17" s="203">
+      <c r="R17" s="202">
         <v>-21.52</v>
       </c>
-      <c r="S17" s="198">
+      <c r="S17" s="205">
         <v>-23.87</v>
       </c>
-      <c r="T17" s="206">
-        <v>-37.52</v>
+      <c r="T17" s="203">
+        <v>-37.07</v>
       </c>
     </row>
     <row r="18">
@@ -6569,41 +6569,41 @@
       <c r="H18">
         <v>10.05</v>
       </c>
-      <c r="I18" s="216">
+      <c r="I18" s="221">
         <v>0</v>
       </c>
-      <c r="J18" s="217">
+      <c r="J18" s="209">
         <v>10.06</v>
       </c>
-      <c r="K18" s="210">
+      <c r="K18" s="217">
         <v>11.46</v>
       </c>
-      <c r="L18" s="211">
+      <c r="L18" s="219">
         <v>0.31</v>
       </c>
-      <c r="M18" s="219">
+      <c r="M18" s="212">
         <v>-9.75</v>
       </c>
-      <c r="N18" s="214">
+      <c r="N18" s="210">
         <v>-9.6</v>
       </c>
-      <c r="O18" s="220">
+      <c r="O18" s="211">
         <v>-16.41</v>
       </c>
-      <c r="P18" s="221">
+      <c r="P18" s="213">
         <v>-14.24</v>
       </c>
-      <c r="Q18" s="212">
+      <c r="Q18" s="214">
         <v>-15.63</v>
       </c>
-      <c r="R18" s="213">
+      <c r="R18" s="220">
         <v>-16.87</v>
       </c>
-      <c r="S18" s="209">
+      <c r="S18" s="215">
         <v>-19.81</v>
       </c>
-      <c r="T18" s="215">
-        <v>155.57</v>
+      <c r="T18" s="216">
+        <v>146.13</v>
       </c>
     </row>
     <row r="19">
@@ -6616,7 +6616,7 @@
       <c r="C19" t="str">
         <v>603067</v>
       </c>
-      <c r="D19" s="234" t="str">
+      <c r="D19" s="222" t="str">
         <v>净买: 1179.50万</v>
       </c>
       <c r="E19">
@@ -6631,41 +6631,41 @@
       <c r="H19">
         <v>-3.07</v>
       </c>
-      <c r="I19" s="224">
+      <c r="I19" s="227">
         <v>-5.37</v>
       </c>
-      <c r="J19" s="225">
+      <c r="J19" s="228">
         <v>-2.17</v>
       </c>
-      <c r="K19" s="231">
+      <c r="K19" s="225">
         <v>6.55</v>
       </c>
-      <c r="L19" s="226">
+      <c r="L19" s="229">
         <v>4.84</v>
       </c>
-      <c r="M19" s="222">
+      <c r="M19" s="230">
         <v>11.14</v>
       </c>
-      <c r="N19" s="232">
+      <c r="N19" s="223">
         <v>10.82</v>
       </c>
-      <c r="O19" s="228">
+      <c r="O19" s="226">
         <v>9.93</v>
       </c>
-      <c r="P19" s="229">
+      <c r="P19" s="231">
         <v>6.01</v>
       </c>
-      <c r="Q19" s="230">
+      <c r="Q19" s="232">
         <v>3.17</v>
       </c>
       <c r="R19" s="233">
         <v>2.53</v>
       </c>
-      <c r="S19" s="227">
+      <c r="S19" s="224">
         <v>12.78</v>
       </c>
-      <c r="T19" s="223">
-        <v>28.86</v>
+      <c r="T19" s="234">
+        <v>26.62</v>
       </c>
     </row>
     <row r="20">
@@ -6678,7 +6678,7 @@
       <c r="C20" t="str">
         <v>000890</v>
       </c>
-      <c r="D20" s="235" t="str">
+      <c r="D20" s="238" t="str">
         <v>净买: 1030.64万</v>
       </c>
       <c r="E20">
@@ -6693,41 +6693,41 @@
       <c r="H20">
         <v>-9.72</v>
       </c>
-      <c r="I20" s="243">
+      <c r="I20" s="245">
         <v>-0.31</v>
       </c>
-      <c r="J20" s="236">
+      <c r="J20" s="247">
         <v>-10.31</v>
       </c>
-      <c r="K20" s="237">
+      <c r="K20" s="239">
         <v>-10.15</v>
       </c>
-      <c r="L20" s="244">
+      <c r="L20" s="240">
         <v>-16.92</v>
       </c>
-      <c r="M20" s="245">
+      <c r="M20" s="241">
         <v>-14.77</v>
       </c>
-      <c r="N20" s="238">
+      <c r="N20" s="246">
         <v>-16.15</v>
       </c>
-      <c r="O20" s="239">
+      <c r="O20" s="243">
         <v>-17.38</v>
       </c>
-      <c r="P20" s="240">
+      <c r="P20" s="235">
         <v>-20.31</v>
       </c>
-      <c r="Q20" s="246">
+      <c r="Q20" s="242">
         <v>-20.62</v>
       </c>
-      <c r="R20" s="241">
+      <c r="R20" s="244">
         <v>-22</v>
       </c>
-      <c r="S20" s="247">
+      <c r="S20" s="236">
         <v>-21.69</v>
       </c>
-      <c r="T20" s="242">
-        <v>154</v>
+      <c r="T20" s="237">
+        <v>144.62</v>
       </c>
     </row>
     <row r="21">
@@ -6740,7 +6740,7 @@
       <c r="C21" t="str">
         <v>000890</v>
       </c>
-      <c r="D21" s="251" t="str">
+      <c r="D21" s="248" t="str">
         <v>净卖: -1045.40万</v>
       </c>
       <c r="E21">
@@ -6755,7 +6755,7 @@
       <c r="H21">
         <v>-4.94</v>
       </c>
-      <c r="I21" s="248">
+      <c r="I21" s="259">
         <v>-5.36</v>
       </c>
       <c r="J21" s="249">
@@ -6764,32 +6764,32 @@
       <c r="K21" s="254">
         <v>-12.34</v>
       </c>
-      <c r="L21" s="258">
+      <c r="L21" s="255">
         <v>-10.06</v>
       </c>
-      <c r="M21" s="252">
+      <c r="M21" s="250">
         <v>-11.53</v>
       </c>
-      <c r="N21" s="250">
+      <c r="N21" s="252">
         <v>-12.82</v>
       </c>
-      <c r="O21" s="259">
+      <c r="O21" s="260">
         <v>-15.91</v>
       </c>
-      <c r="P21" s="255">
+      <c r="P21" s="251">
         <v>-16.23</v>
       </c>
       <c r="Q21" s="256">
         <v>-17.69</v>
       </c>
-      <c r="R21" s="253">
+      <c r="R21" s="257">
         <v>-17.37</v>
       </c>
-      <c r="S21" s="260">
+      <c r="S21" s="258">
         <v>-16.23</v>
       </c>
-      <c r="T21" s="257">
-        <v>168.02</v>
+      <c r="T21" s="253">
+        <v>158.12</v>
       </c>
     </row>
     <row r="22">
@@ -6802,7 +6802,7 @@
       <c r="C22" t="str">
         <v>300409</v>
       </c>
-      <c r="D22" s="268" t="str">
+      <c r="D22" s="264" t="str">
         <v>净卖: -3259.20万</v>
       </c>
       <c r="E22">
@@ -6820,38 +6820,38 @@
       <c r="I22" s="269">
         <v>14.8</v>
       </c>
-      <c r="J22" s="270">
+      <c r="J22" s="273">
         <v>31.48</v>
       </c>
-      <c r="K22" s="263">
+      <c r="K22" s="265">
         <v>32.5</v>
       </c>
-      <c r="L22" s="272">
+      <c r="L22" s="262">
         <v>30.84</v>
       </c>
-      <c r="M22" s="264">
+      <c r="M22" s="266">
         <v>23.86</v>
       </c>
-      <c r="N22" s="271">
+      <c r="N22" s="270">
         <v>48.62</v>
       </c>
-      <c r="O22" s="273">
+      <c r="O22" s="267">
         <v>46.11</v>
       </c>
-      <c r="P22" s="261">
+      <c r="P22" s="271">
         <v>41.64</v>
       </c>
-      <c r="Q22" s="265">
+      <c r="Q22" s="261">
         <v>42.15</v>
       </c>
-      <c r="R22" s="262">
+      <c r="R22" s="268">
         <v>36.03</v>
       </c>
-      <c r="S22" s="266">
+      <c r="S22" s="272">
         <v>31.9</v>
       </c>
-      <c r="T22" s="267">
-        <v>15.48</v>
+      <c r="T22" s="263">
+        <v>12.25</v>
       </c>
     </row>
     <row r="23">
@@ -6864,7 +6864,7 @@
       <c r="C23" t="str">
         <v>300409</v>
       </c>
-      <c r="D23" s="275" t="str">
+      <c r="D23" s="280" t="str">
         <v>净卖: -3736.61万</v>
       </c>
       <c r="E23">
@@ -6882,38 +6882,38 @@
       <c r="I23" s="281">
         <v>9.88</v>
       </c>
-      <c r="J23" s="276">
+      <c r="J23" s="285">
         <v>10.74</v>
       </c>
-      <c r="K23" s="283">
+      <c r="K23" s="274">
         <v>9.35</v>
       </c>
-      <c r="L23" s="284">
+      <c r="L23" s="286">
         <v>3.52</v>
       </c>
-      <c r="M23" s="285">
+      <c r="M23" s="275">
         <v>24.21</v>
       </c>
-      <c r="N23" s="286">
+      <c r="N23" s="276">
         <v>22.11</v>
       </c>
       <c r="O23" s="282">
         <v>18.38</v>
       </c>
-      <c r="P23" s="279">
+      <c r="P23" s="277">
         <v>18.81</v>
       </c>
-      <c r="Q23" s="277">
+      <c r="Q23" s="278">
         <v>13.69</v>
       </c>
-      <c r="R23" s="280">
+      <c r="R23" s="283">
         <v>10.24</v>
       </c>
-      <c r="S23" s="278">
+      <c r="S23" s="284">
         <v>8</v>
       </c>
-      <c r="T23" s="274">
-        <v>-3.48</v>
+      <c r="T23" s="279">
+        <v>-6.19</v>
       </c>
     </row>
     <row r="24">
@@ -6926,7 +6926,7 @@
       <c r="C24" t="str">
         <v>300409</v>
       </c>
-      <c r="D24" s="288" t="str">
+      <c r="D24" s="291" t="str">
         <v>净卖: -2006.10万</v>
       </c>
       <c r="E24">
@@ -6941,41 +6941,41 @@
       <c r="H24">
         <v>1.68</v>
       </c>
-      <c r="I24" s="297">
+      <c r="I24" s="292">
         <v>18</v>
       </c>
-      <c r="J24" s="289">
+      <c r="J24" s="287">
         <v>16.01</v>
       </c>
-      <c r="K24" s="290">
+      <c r="K24" s="288">
         <v>12.46</v>
       </c>
-      <c r="L24" s="295">
+      <c r="L24" s="293">
         <v>12.87</v>
       </c>
-      <c r="M24" s="298">
+      <c r="M24" s="296">
         <v>8</v>
       </c>
-      <c r="N24" s="291">
+      <c r="N24" s="294">
         <v>4.73</v>
       </c>
-      <c r="O24" s="292">
+      <c r="O24" s="299">
         <v>2.6</v>
       </c>
-      <c r="P24" s="293">
+      <c r="P24" s="297">
         <v>1.82</v>
       </c>
-      <c r="Q24" s="296">
+      <c r="Q24" s="289">
         <v>2.36</v>
       </c>
-      <c r="R24" s="299">
+      <c r="R24" s="298">
         <v>8.11</v>
       </c>
-      <c r="S24" s="287">
+      <c r="S24" s="295">
         <v>5.67</v>
       </c>
-      <c r="T24" s="294">
-        <v>-8.31</v>
+      <c r="T24" s="290">
+        <v>-10.87</v>
       </c>
     </row>
     <row r="25">
@@ -7037,37 +7037,37 @@
       <c r="F26" t="str"/>
       <c r="G26" t="str"/>
       <c r="H26" t="str"/>
-      <c r="I26" s="306">
+      <c r="I26" s="310">
         <v>52.17</v>
       </c>
-      <c r="J26" s="308">
+      <c r="J26" s="301">
         <v>52.17</v>
       </c>
       <c r="K26" s="307">
         <v>52.17</v>
       </c>
-      <c r="L26" s="302">
+      <c r="L26" s="311">
         <v>47.83</v>
       </c>
-      <c r="M26" s="310">
+      <c r="M26" s="300">
         <v>43.48</v>
       </c>
-      <c r="N26" s="311">
+      <c r="N26" s="302">
         <v>39.13</v>
       </c>
       <c r="O26" s="303">
         <v>34.78</v>
       </c>
-      <c r="P26" s="300">
+      <c r="P26" s="305">
         <v>39.13</v>
       </c>
-      <c r="Q26" s="301">
+      <c r="Q26" s="304">
         <v>39.13</v>
       </c>
-      <c r="R26" s="304">
+      <c r="R26" s="306">
         <v>39.13</v>
       </c>
-      <c r="S26" s="305">
+      <c r="S26" s="308">
         <v>39.13</v>
       </c>
       <c r="T26" s="309">
@@ -7085,41 +7085,41 @@
       <c r="F27" t="str"/>
       <c r="G27" t="str"/>
       <c r="H27" t="str"/>
-      <c r="I27" s="318">
+      <c r="I27" s="317">
         <v>3.46</v>
       </c>
-      <c r="J27" s="320">
+      <c r="J27" s="315">
         <v>2.89</v>
       </c>
-      <c r="K27" s="321">
+      <c r="K27" s="322">
         <v>0.67</v>
       </c>
-      <c r="L27" s="315">
+      <c r="L27" s="323">
         <v>-0.46</v>
       </c>
-      <c r="M27" s="322">
+      <c r="M27" s="312">
         <v>-1.36</v>
       </c>
-      <c r="N27" s="319">
+      <c r="N27" s="313">
         <v>-0.02</v>
       </c>
-      <c r="O27" s="312">
+      <c r="O27" s="318">
         <v>-1.62</v>
       </c>
-      <c r="P27" s="316">
+      <c r="P27" s="319">
         <v>-2.08</v>
       </c>
-      <c r="Q27" s="317">
+      <c r="Q27" s="316">
         <v>-2.45</v>
       </c>
-      <c r="R27" s="323">
+      <c r="R27" s="314">
         <v>-2.62</v>
       </c>
-      <c r="S27" s="313">
+      <c r="S27" s="320">
         <v>-1.7</v>
       </c>
-      <c r="T27" s="314">
-        <v>26.09</v>
+      <c r="T27" s="321">
+        <v>23.23</v>
       </c>
     </row>
   </sheetData>
